--- a/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼BODY(집행단계-첨부폴더)v8/매뉴얼 BODY (집행단계)v8.xlsx
+++ b/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼BODY(집행단계-첨부폴더)v8/매뉴얼 BODY (집행단계)v8.xlsx
@@ -32,6 +32,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'신호'!$A$1:$S$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'전기'!$A$1:$S$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'통신'!$A$1:$S$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'기계'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'기계'!$A$1:$S$37</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -42,7 +44,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="21">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -203,46 +205,8 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="000F172A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="000F172A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00047857"/>
-      <sz val="9"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="000284C7"/>
-      <sz val="9"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00D97706"/>
-      <sz val="9"/>
-      <u val="single"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -267,20 +231,8 @@
         <bgColor rgb="FF0F172A"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -357,25 +309,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -625,69 +563,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4534,4189 +4409,4256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PR46"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="8"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" style="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="36" customWidth="1" style="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" style="1" min="19" max="19"/>
-    <col width="32" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="9" bestFit="1" customWidth="1" style="4" min="1" max="2"/>
+    <col width="13.19921875" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
+    <col width="11.19921875" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
+    <col width="16" customWidth="1" style="2" min="5" max="6"/>
+    <col width="30.3984375" customWidth="1" style="4" min="7" max="7"/>
+    <col width="23.296875" customWidth="1" style="4" min="8" max="8"/>
+    <col width="21.69921875" customWidth="1" style="4" min="9" max="9"/>
+    <col width="38" customWidth="1" style="3" min="10" max="10"/>
+    <col width="52" customWidth="1" style="3" min="11" max="11"/>
+    <col width="19.3984375" customWidth="1" style="4" min="12" max="12"/>
+    <col width="53" customWidth="1" style="3" min="13" max="13"/>
+    <col width="14.69921875" customWidth="1" style="3" min="14" max="14"/>
+    <col width="45" customWidth="1" style="3" min="15" max="15"/>
+    <col width="15.796875" customWidth="1" style="3" min="16" max="16"/>
+    <col width="45" customWidth="1" style="3" min="17" max="17"/>
+    <col width="16.09765625" customWidth="1" style="27" min="18" max="18"/>
+    <col width="15.796875" customWidth="1" style="3" min="19" max="19"/>
+    <col width="45" customWidth="1" style="27" min="20" max="20"/>
+    <col width="22" customWidth="1" style="27" min="21" max="21"/>
+    <col width="45" customWidth="1" style="3" min="22" max="38"/>
+    <col width="8.796875" customWidth="1" style="3" min="39" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="86" t="inlineStr">
+    <row r="1" ht="57.6" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>L2 코드</t>
         </is>
       </c>
-      <c r="B1" s="86" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>L3 코드</t>
         </is>
       </c>
-      <c r="C1" s="86" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>L3 대공종명</t>
         </is>
       </c>
-      <c r="D1" s="86" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>L4 코드</t>
         </is>
       </c>
-      <c r="E1" s="86" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>선행</t>
         </is>
       </c>
-      <c r="F1" s="86" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>후행</t>
         </is>
       </c>
-      <c r="G1" s="86" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>작업단위 (Level 4 Task/Activity)</t>
         </is>
       </c>
-      <c r="H1" s="86" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>일정 (D-Day)</t>
         </is>
       </c>
-      <c r="I1" s="86" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>주관</t>
         </is>
       </c>
-      <c r="J1" s="86" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>목적</t>
         </is>
       </c>
-      <c r="K1" s="86" t="inlineStr">
+      <c r="K1" s="20" t="inlineStr">
         <is>
           <t>방법</t>
         </is>
       </c>
-      <c r="L1" s="86" t="inlineStr">
+      <c r="L1" s="20" t="inlineStr">
         <is>
           <t>산출물(결과)</t>
         </is>
       </c>
-      <c r="M1" s="86" t="inlineStr">
+      <c r="M1" s="20" t="inlineStr">
         <is>
           <t>표준서 (Standard) 요약</t>
         </is>
       </c>
-      <c r="N1" s="86" t="inlineStr">
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>표준서 파일 (HTML)</t>
         </is>
       </c>
-      <c r="O1" s="86" t="inlineStr">
+      <c r="O1" s="20" t="inlineStr">
         <is>
           <t>수행지침 (Guideline) 요약</t>
         </is>
       </c>
-      <c r="P1" s="86" t="inlineStr">
+      <c r="P1" s="13" t="inlineStr">
         <is>
           <t>수행지침 파일 (HTML)</t>
         </is>
       </c>
-      <c r="Q1" s="86" t="inlineStr">
+      <c r="Q1" s="20" t="inlineStr">
         <is>
           <t>체크리스트 (Checklist) 요약</t>
         </is>
       </c>
-      <c r="R1" s="86" t="inlineStr">
+      <c r="R1" s="21" t="inlineStr">
         <is>
           <t>체크리스트 파일 (HTML)</t>
         </is>
       </c>
-      <c r="S1" s="86" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="T1" s="86" t="inlineStr">
+      <c r="T1" s="11" t="inlineStr">
         <is>
           <t>첨부서류 연계 상세 설계기준</t>
         </is>
       </c>
-      <c r="U1" s="86" t="inlineStr">
+      <c r="U1" s="11" t="inlineStr">
         <is>
           <t>집행단계 리스크 체크리스트</t>
         </is>
       </c>
-      <c r="V1" s="86" t="inlineStr">
+      <c r="V1" s="11" t="inlineStr">
         <is>
           <t>협력사 시공/공사관리 자문</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="87" t="inlineStr">
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B2" s="87" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C2" s="87" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D2" s="88" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>9000-8-1</t>
         </is>
       </c>
-      <c r="E2" s="89" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="90" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>9000-8-2</t>
         </is>
       </c>
-      <c r="G2" s="91" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>설계 적정성 검토</t>
         </is>
       </c>
-      <c r="H2" s="90" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>D-117</t>
         </is>
       </c>
-      <c r="I2" s="89" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J2" s="92" t="inlineStr">
-        <is>
-          <t>동탄도시철도(트램) 기계설비(HVAC, 급배수, 위생, 오폐수, 승강기) 및 소방설비(소화, 제연, 경보)의 착공 전 설계도서(도면·시방서·수량산출서·내역서)의 적격성을 검토하고, 지하 및 지상 정거장, 변전소, 차량기지 내 법적 기준 충족 및 시공성을 사전 확보한다.</t>
-        </is>
-      </c>
-      <c r="K2" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 설계도서 및 계산서 총괄 수집, STEP 2: 삼각 교차 대조 및 물량 정합성 검증 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L2" s="93" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
+        <is>
+          <t>기계·소방설비 설계도서(도면/시방/계산서)의 KDS 47 및 NFTC 기준 적합성과 시공성·경제성 사전 검증</t>
+        </is>
+      </c>
+      <c r="K2" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (설계도서 삼각 대조): KDS 47/NFTC 기준에 따라 공조/환기 부하계산서, 설계도면, 수량산출서 1:1 정합성 검증
+2) STEP 2 (주요 장비 용량 검토): 변전소 PAC(3대), 고내열 제연팬(250℃/1h), 인버터 펌프 정격 양정/유량 시방 일치성 확인
+3) STEP 3 (인터페이스 및 개선안 도출): 건축 슬리브, 전기 NFR-8 내화배선, 신호 배수공동구 연계성 검토 및 설계변경안 감리 승인</t>
+        </is>
+      </c>
+      <c r="L2" s="17" t="inlineStr">
         <is>
           <t>설계 적정성 검토 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M2" s="93" t="inlineStr">
+      <c r="M2" s="26" t="inlineStr">
         <is>
           <t>1) 설계 적정성 검토 (9000-8-1) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) KDS 47 철도설계기준 및 KCS 41 건축설계기준에 따른 기계·소방설비 설계도서 삼각 대조 및 부하계산서 정밀 검증을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N2" s="94">
+      <c r="N2" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\1_설계 적정성 검토\표준서\1_설계 적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O2" s="93" t="inlineStr">
+      <c r="O2" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 설계도서 및 계산서 총괄 수집: 기계/소방 설계도면, 특기시방서, 부하계산서, 장비일람표 수집
 2) STEP 2: 삼각 교차 대조 및 물량 정합성 검증: 도면 ↔ 수량산출서 ↔ 내역서 불일치 전수 색출</t>
         </is>
       </c>
-      <c r="P2" s="95">
+      <c r="P2" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\1_설계 적정성 검토\수행지침\1_설계 적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q2" s="93" t="inlineStr">
+      <c r="Q2" s="26" t="inlineStr">
         <is>
           <t>1) 공조부하 계산 시방 및 정거장 및 변전소 냉난방 부하계산서 대조 기준을 100% 충족하였는가?
 2) 소방설비 법적기준 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R2" s="96">
+      <c r="R2" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\1_설계 적정성 검토\체크리스트\1_설계 적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S2" s="89" t="inlineStr">
+      <c r="S2" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T2" s="93" t="inlineStr">
+      <c r="T2" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U2" s="87" t="inlineStr">
+      <c r="U2" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V2" s="93" t="inlineStr">
+      <c r="V2" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="97" t="inlineStr">
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B3" s="97" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C3" s="97" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D3" s="98" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>9000-8-2</t>
         </is>
       </c>
-      <c r="E3" s="99" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>9000-8-1</t>
         </is>
       </c>
-      <c r="F3" s="99" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>9000-8-3</t>
         </is>
       </c>
-      <c r="G3" s="100" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>발주전략 KOM</t>
         </is>
       </c>
-      <c r="H3" s="99" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>D-114</t>
         </is>
       </c>
-      <c r="I3" s="101" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J3" s="102" t="inlineStr">
-        <is>
-          <t>기계 및 소방공사의 성공적인 수행을 위해 발주처, 책임감리단, 원도급사, 전문협력업체가 참여하는 Kick-Off Meeting을 개최하여 중점 품질관리 항목, 법적 인허가 일정, 장비 제작납기 및 자재 승인 프로세스를 일괄 확정한다.</t>
-        </is>
-      </c>
-      <c r="K3" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: KOM 킥오프 회의 소집 및 R&amp;R 확정, STEP 2: 주요 장비 제작 및 조달 계획 수립 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L3" s="102" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>기계·소방 공종 3자(발주처-감리-시공) 킥오프를 통한 주요 자재 조달 라인 및 4대 공정 마일스톤 확정</t>
+        </is>
+      </c>
+      <c r="K3" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (3자 협의체 구성): 발주처, 책임감리단, 기계/소방 협력사 간 공정·품질·안전 관리체계 및 업무 R&amp;R 확정
+2) STEP 2 (주요 자재 수급선 검토): STS 강관, 덕트, 펌프, 승강기 등 장납기 자재의 공장 승인 및 납품 스케줄 동기화
+3) STEP 3 (핵심 마일스톤 수립): 3D BIM 간섭해소, FAT 공장검수, 수압시험, 소방 완공검사 등 공정 임계경로(CP) 관리</t>
+        </is>
+      </c>
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t>발주전략 KOM 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M3" s="102" t="inlineStr">
+      <c r="M3" s="26" t="inlineStr">
         <is>
           <t>1) 발주전략 KOM (9000-8-2) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 감리단-시공사-기계/소방 전문협력사 3자 착수회의(KOM) 및 공종별 핵심 마일스톤 확정을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N3" s="103">
+      <c r="N3" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\2_발주전략 KOM\표준서\2_발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O3" s="102" t="inlineStr">
+      <c r="O3" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: KOM 킥오프 회의 소집 및 R&amp;R 확정: 착수 협의체 가동 및 공종별 책임 범위 규정
 2) STEP 2: 주요 장비 제작 및 조달 계획 수립: 공조기, 소방펌프, 인승용/화물용 승강기 납기 확정</t>
         </is>
       </c>
-      <c r="P3" s="104">
+      <c r="P3" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\2_발주전략 KOM\수행지침\2_발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q3" s="102" t="inlineStr">
+      <c r="Q3" s="26" t="inlineStr">
         <is>
           <t>1) 협력체계 구축 시방 및 감리-시공-협력사 정기 협의체 구성 기준을 100% 충족하였는가?
 2) 장비 발주계획 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R3" s="105">
+      <c r="R3" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\2_발주전략 KOM\체크리스트\2_발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S3" s="101" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T3" s="102" t="inlineStr">
+      <c r="T3" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U3" s="97" t="inlineStr">
+      <c r="U3" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V3" s="102" t="inlineStr">
+      <c r="V3" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="87" t="inlineStr">
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B4" s="87" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C4" s="87" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D4" s="88" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>9000-8-3</t>
         </is>
       </c>
-      <c r="E4" s="89" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>9000-8-2</t>
         </is>
       </c>
-      <c r="F4" s="90" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>9000-8-4</t>
         </is>
       </c>
-      <c r="G4" s="91" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>3D BIM 기계_소방 간섭 검토</t>
         </is>
       </c>
-      <c r="H4" s="90" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>D-111</t>
         </is>
       </c>
-      <c r="I4" s="89" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J4" s="92" t="inlineStr">
-        <is>
-          <t>지하 정거장 천장 및 기계실, 차량기지 검수고 등 배관·덕트 밀집 구역에 대해 3D BIM(LOD 350) 통합 모델링을 수행하여 타 공종(건축, 전기, 신호, 궤도)과의 물리적 간섭을 착공 전 100% 제거하고 최적의 시공 동선을 도출한다.</t>
-        </is>
-      </c>
-      <c r="K4" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 3D BIM 기계/소방 상세 모델링 (LOD 350), STEP 2: 다공종 통합 모델 합성 및 간섭 체크 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L4" s="93" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>LOD 350 기반 3D BIM을 활용하여 기계덕트·소화배관·전기트레이 간 Hard Clash 0건 달성 및 CSD 승인</t>
+        </is>
+      </c>
+      <c r="K4" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (LOD 350 3D 모델링): 기계 공조덕트, 소화배관, 위생배관 및 전기 트레이의 3D 통합 모델 구축
+2) STEP 2 (복합 간섭체크 실행): Navisworks 간섭 체크 엔진을 가동하여 배관 교차 및 건축 골조 간섭(Clash) 전수 색출
+3) STEP 3 (시공상세도 CSD 확정): 정거장 유효 천장고(CH ≥ 2.7m) 확보를 위한 배관 입체 재배치 및 감리단 CSD 최종 승인</t>
+        </is>
+      </c>
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>3D BIM 기계_소방 간섭 검토 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M4" s="93" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t>1) 3D BIM 기계_소방 간섭 검토 (9000-8-3) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) LOD 350 기반 기계덕트/배관↔전기트레이/건축골조/신호공동구 3D 공간 간섭 100% 제거을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N4" s="94">
+      <c r="N4" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\3_3D BIM 기계_소방 간섭 검토\표준서\3_3D BIM 기계_소방 간섭 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O4" s="93" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 3D BIM 기계/소방 상세 모델링 (LOD 350): 배관 구배, 덕트 엘보, 장비 외형 정밀 모델링
 2) STEP 2: 다공종 통합 모델 합성 및 간섭 체크: 건축/구조/전기/통신/신호 3D 모델 통합 검사</t>
         </is>
       </c>
-      <c r="P4" s="95">
+      <c r="P4" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\3_3D BIM 기계_소방 간섭 검토\수행지침\3_3D BIM 기계_소방 간섭 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q4" s="93" t="inlineStr">
+      <c r="Q4" s="26" t="inlineStr">
         <is>
           <t>1) 간섭 클러스터 분석 시방 및 Autodesk Navisworks 기반 Clash Detection 기준을 100% 충족하였는가?
 2) 천장 공간 배분 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R4" s="96">
+      <c r="R4" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\3_3D BIM 기계_소방 간섭 검토\체크리스트\3_3D BIM 기계_소방 간섭 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S4" s="89" t="inlineStr">
+      <c r="S4" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T4" s="93" t="inlineStr">
+      <c r="T4" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U4" s="87" t="inlineStr">
+      <c r="U4" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V4" s="93" t="inlineStr">
+      <c r="V4" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="97" t="inlineStr">
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B5" s="97" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D5" s="98" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>9000-8-4</t>
         </is>
       </c>
-      <c r="E5" s="106" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>9000-8-3</t>
         </is>
       </c>
-      <c r="F5" s="99" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>9000-8-5</t>
         </is>
       </c>
-      <c r="G5" s="100" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>소방 및 환경 인허가</t>
         </is>
       </c>
-      <c r="H5" s="99" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>D-108</t>
         </is>
       </c>
-      <c r="I5" s="101" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J5" s="102" t="inlineStr">
-        <is>
-          <t>소방시설공사업법 및 물환경보전법에 따라 공사 착공 전 관할 소방서로부터 소방시설 시공 동의 및 착공신고를 득하고, 차량기지 위험물 저장소, 비상발전기 유류탱크, 오수처리시설 인허가를 적기에 완료하여 법적 리스크를 제거한다.</t>
-        </is>
-      </c>
-      <c r="K5" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 소방시설 착공신고서 작성 및 도서 구비, STEP 2: 소방시설 건축동의 및 기술 검토 보완 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L5" s="102" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>소방시설공사업법 제13조에 따른 착공신고 및 위험물·오폐수 환경 인허가 적기 득</t>
+        </is>
+      </c>
+      <c r="K5" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (소방 착공신고): 소방기술자/감리원 배치신고서 및 소방 설계도서를 관할 화성소방서에 제출하여 착공필증 수령
+2) STEP 2 (위험물 저장 승인): 비상발전기 유류탱크(경유) 저장소 설치허가 및 방유제(용량 110%) 안전기준 검증
+3) STEP 3 (환경 인허가 완료): 차량기지 오폐수배출시설 설치신고 및 수질 TMS 연동 계획 관할 지자체 승인</t>
+        </is>
+      </c>
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t>소방 및 환경 인허가 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M5" s="102" t="inlineStr">
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t>1) 소방 및 환경 인허가 (9000-8-4) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 관할 소방서 소방시설 착공신고/동의, 위험물 저장소 인허가 및 오수정화시설 신고을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N5" s="103">
+      <c r="N5" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\4_소방 및 환경 인허가\표준서\4_소방 및 환경 인허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O5" s="102" t="inlineStr">
+      <c r="O5" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 소방시설 착공신고서 작성 및 도서 구비: 설계도면, 소방시설 내역서, 시공사 면허 첨부
 2) STEP 2: 소방시설 건축동의 및 기술 검토 보완: 소방서 보완 요구사항 신속 조치 및 승인</t>
         </is>
       </c>
-      <c r="P5" s="104">
+      <c r="P5" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\4_소방 및 환경 인허가\수행지침\4_소방 및 환경 인허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q5" s="102" t="inlineStr">
+      <c r="Q5" s="26" t="inlineStr">
         <is>
           <t>1) 소방시설 착공신고 시방 및 소방시설공사업법 제13조에 따른 착공계 제출 기준을 100% 충족하였는가?
 2) 소방공사 감리원 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R5" s="105">
+      <c r="R5" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\4_소방 및 환경 인허가\체크리스트\4_소방 및 환경 인허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S5" s="101" t="inlineStr">
+      <c r="S5" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T5" s="102" t="inlineStr">
+      <c r="T5" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U5" s="97" t="inlineStr">
+      <c r="U5" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V5" s="102" t="inlineStr">
+      <c r="V5" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="87" t="inlineStr">
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B6" s="87" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C6" s="87" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D6" s="88" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>9000-8-5</t>
         </is>
       </c>
-      <c r="E6" s="89" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>9000-8-4</t>
         </is>
       </c>
-      <c r="F6" s="90" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>9000-8-6</t>
         </is>
       </c>
-      <c r="G6" s="91" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>장비 반입동선 및 야적장 계획</t>
         </is>
       </c>
-      <c r="H6" s="90" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>D-105</t>
         </is>
       </c>
-      <c r="I6" s="89" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J6" s="92" t="inlineStr">
-        <is>
-          <t>지하 정거장 기계실 및 차량기지 종합검수동에 설치되는 대형 중량물(공기조화기, 냉동기, 소방펌프, 열교환기)의 반입 개구부, 수직 인양 동선, 양중 크레인 작업 반경 및 현장 자재 야적장 보관 관리 계획을 수립한다.</t>
-        </is>
-      </c>
-      <c r="K6" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 중량 장비 제원 및 반입 경로 실측, STEP 2: 양중 크레인 작업 계획 및 안전성 검토 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L6" s="93" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>지하 기계실 대형 장비(AHU, 펌프 등)의 DA 개구부 양중 및 안전 반입 동선 확보</t>
+        </is>
+      </c>
+      <c r="K6" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (양중 크레인 계획): 50ton 하이드로 크레인 작업반경 설정, 복공판 하부 지지력(K30 ≥ 150) 및 아웃트리거 보강
+2) STEP 2 (개구부 통과 검토): 장비 분할 치수와 DA 개구부(W2.5m x L4.0m) 유효 통과폭 대조 및 호이스트/체인블록 가설
+3) STEP 3 (수평 인입 및 안착): 운반 롤러 및 레일 시스템을 이용하여 기계실 기초 패드 위로 유도 후 레벨링 및 앵커링</t>
+        </is>
+      </c>
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>장비 반입동선 및 야적장 계획 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M6" s="93" t="inlineStr">
+      <c r="M6" s="26" t="inlineStr">
         <is>
           <t>1) 장비 반입동선 및 야적장 계획 (9000-8-5) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 대형 공조기(AHU), 냉동기, 소방펌프 반입구 크기 및 크레인 인양 작업반경 사전 검토을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N6" s="94">
+      <c r="N6" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\5_장비 반입동선 및 야적장 계획\표준서\5_장비 반입동선 및 야적장 계획_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O6" s="93" t="inlineStr">
+      <c r="O6" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 중량 장비 제원 및 반입 경로 실측: 장비 외형 치수, 중량, 반입구 크기 대조
 2) STEP 2: 양중 크레인 작업 계획 및 안전성 검토: 크레인 전도 방지 및 슬래브 지지력 계산</t>
         </is>
       </c>
-      <c r="P6" s="95">
+      <c r="P6" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\5_장비 반입동선 및 야적장 계획\수행지침\5_장비 반입동선 및 야적장 계획_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q6" s="93" t="inlineStr">
+      <c r="Q6" s="26" t="inlineStr">
         <is>
           <t>1) 장비 반입구 시방 및 지하 기계실 장비 반입구(DA) 크기 및 해치 확인 기준을 100% 충족하였는가?
 2) 양중 크레인 계획 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R6" s="96">
+      <c r="R6" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\5_장비 반입동선 및 야적장 계획\체크리스트\5_장비 반입동선 및 야적장 계획_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S6" s="89" t="inlineStr">
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T6" s="93" t="inlineStr">
+      <c r="T6" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U6" s="87" t="inlineStr">
+      <c r="U6" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V6" s="93" t="inlineStr">
+      <c r="V6" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="97" t="inlineStr">
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B7" s="97" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D7" s="98" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>9000-8-6</t>
         </is>
       </c>
-      <c r="E7" s="101" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>9000-8-5</t>
         </is>
       </c>
-      <c r="F7" s="99" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>9000-8-7</t>
         </is>
       </c>
-      <c r="G7" s="100" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>Big Room 인터페이스 회의</t>
         </is>
       </c>
-      <c r="H7" s="99" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>D-102</t>
         </is>
       </c>
-      <c r="I7" s="101" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J7" s="102" t="inlineStr">
-        <is>
-          <t>동탄트램 복합 공정의 성공을 위해 기계·소방 분야와 6대 연관 공종(토목 노반, 궤도 콘크리트도상, 건축 구조/마감, 전기 수변전, 신호 연동, 통신 LTE-R) 간의 주간 Big Room 합동 회의를 운영하여 시공 오차 및 인터페이스 누락을 원천 차단한다.</t>
-        </is>
-      </c>
-      <c r="K7" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: Big Room 합동 회의 안건 도출 및 3D 모델 준비, STEP 2: 7대 공종 합동 기술 조율 및 대안 확정 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L7" s="102" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>건축, 전기, 통신, 신호, 궤도 등 타 공종과의 시공 간섭 배제 및 시공 우선순위 룰 확립</t>
+        </is>
+      </c>
+      <c r="K7" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (Big Room 정례협의): 7대 공종 합동 주간 인터페이스 회의를 운영하여 주배관과 타 공종 지장물 간섭 해소
+2) STEP 2 (시공 우선순위 확정): 슬리브 선매립(건축) ⟶ 대형 풍도/주배관(기계) ⟶ 케이블트레이(전기) 순차 시공 룰 적용
+3) STEP 3 (인터페이스 체크시트 발행): 상호 인계인수 전 슬리브 위치, 방화구획, 배수구 트렌치 시공 상태 합동 서명 검측</t>
+        </is>
+      </c>
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>Big Room 인터페이스 회의 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M7" s="102" t="inlineStr">
+      <c r="M7" s="26" t="inlineStr">
         <is>
           <t>1) Big Room 인터페이스 회의 (9000-8-6) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 토목·궤도·건축·전기·신호·통신·기계 7대 공종 합동 간섭 조정 및 시공 우선순위 확정을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N7" s="103">
+      <c r="N7" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\6_Big Room 인터페이스 회의\표준서\6_Big Room 인터페이스 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O7" s="102" t="inlineStr">
+      <c r="O7" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: Big Room 합동 회의 안건 도출 및 3D 모델 준비: 공종간 충돌 부위 및 시공 간섭 이슈 리스트업
 2) STEP 2: 7대 공종 합동 기술 조율 및 대안 확정: 현장 시공성 기반 최적 경로 협의 및 의사결정</t>
         </is>
       </c>
-      <c r="P7" s="104">
+      <c r="P7" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\6_Big Room 인터페이스 회의\수행지침\6_Big Room 인터페이스 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q7" s="102" t="inlineStr">
+      <c r="Q7" s="26" t="inlineStr">
         <is>
           <t>1) 7대 공종 합동 검토 시방 및 기계/소방↔토목/궤도/건축/전기/신호/통신 연계 기준을 100% 충족하였는가?
 2) 관통 슬리브 확정 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R7" s="105">
+      <c r="R7" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\6_Big Room 인터페이스 회의\체크리스트\6_Big Room 인터페이스 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S7" s="101" t="inlineStr">
+      <c r="S7" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T7" s="102" t="inlineStr">
+      <c r="T7" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U7" s="97" t="inlineStr">
+      <c r="U7" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V7" s="102" t="inlineStr">
+      <c r="V7" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="87" t="inlineStr">
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B8" s="87" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C8" s="87" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D8" s="88" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>9000-8-7</t>
         </is>
       </c>
-      <c r="E8" s="89" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>9000-8-6</t>
         </is>
       </c>
-      <c r="F8" s="90" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>9000-8-8</t>
         </is>
       </c>
-      <c r="G8" s="91" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>지하매설 기계배관 협의</t>
         </is>
       </c>
-      <c r="H8" s="90" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>D-99</t>
         </is>
       </c>
-      <c r="I8" s="89" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J8" s="92" t="inlineStr">
-        <is>
-          <t>트램 본선 도로 하부 및 정거장 외부 인입 구역에 매설되는 기계배관(상수도 급수관, 지열 집열관, 오배수 연결관)에 대해 지자체(화성시), 도로관리청 및 한국전력·가스·통신 유관기관과 지장물 이설 및 도로굴착 점용 협의를 수행한다.</t>
-        </is>
-      </c>
-      <c r="K8" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 지하 지장물 매설도 수집 및 3D GPR 탐사, STEP 2: 유관기관 협의 및 도로굴착점용 허가 획득 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L8" s="93" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>트램 본선 도로 하부 지중매설 배관(상수도, 지열, 우오수)과 지하 지장물 간 안전 이격거리 확보</t>
+        </is>
+      </c>
+      <c r="K8" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (3D 지하매설물 탐사): GPR 탐사 및 줄파기를 통해 기존 가스관, 한전관로, 통신관로 심도와 좌표 정밀 확인
+2) STEP 2 (안전 이격거리 유지): 타 지장물과 최소 300mm 이상 이격 배치하고 고저차 간섭 시 강관 보호공(Casing) 적용
+3) STEP 3 (모래부설 및 다짐): 배관 주위 양질의 모래(두께 100mm) 부설 후 되메우기 층별 다짐(다짐도 ≥ 95%) 및 경고테이프 매설</t>
+        </is>
+      </c>
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t>지하매설 기계배관 협의 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M8" s="93" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t>1) 지하매설 기계배관 협의 (9000-8-7) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 도로 하부 상수도 인입관, 지열 PE배관, 오우수 관로 지장물 이설 및 도로점용 협의을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N8" s="94">
+      <c r="N8" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\7_지하매설 기계배관 협의\표준서\7_지하매설 기계배관 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O8" s="93" t="inlineStr">
+      <c r="O8" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 지하 지장물 매설도 수집 및 3D GPR 탐사: 도로 하부 8대 지하매설물 도면 대조
 2) STEP 2: 유관기관 협의 및 도로굴착점용 허가 획득: 지자체 및 관리기관 합동 현장 실사</t>
         </is>
       </c>
-      <c r="P8" s="95">
+      <c r="P8" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\7_지하매설 기계배관 협의\수행지침\7_지하매설 기계배관 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q8" s="93" t="inlineStr">
+      <c r="Q8" s="26" t="inlineStr">
         <is>
           <t>1) 지하관로 탐사 시방 및 3D GPR 지하 레이더 탐사 및 인력 줄파기 기준을 100% 충족하였는가?
 2) 상수도 인입 협의 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R8" s="96">
+      <c r="R8" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\7_지하매설 기계배관 협의\체크리스트\7_지하매설 기계배관 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S8" s="89" t="inlineStr">
+      <c r="S8" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T8" s="93" t="inlineStr">
+      <c r="T8" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U8" s="87" t="inlineStr">
+      <c r="U8" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V8" s="93" t="inlineStr">
+      <c r="V8" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="97" t="inlineStr">
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B9" s="97" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D9" s="98" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>9000-8-8</t>
         </is>
       </c>
-      <c r="E9" s="101" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>9000-8-7</t>
         </is>
       </c>
-      <c r="F9" s="99" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>9000-8-9</t>
         </is>
       </c>
-      <c r="G9" s="100" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>기계설비 시공계획서 수립</t>
         </is>
       </c>
-      <c r="H9" s="99" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>D-96</t>
         </is>
       </c>
-      <c r="I9" s="101" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J9" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41(건축기계설비공사 표준시방서) 및 KDS 47(철도설계기준)에 의거하여 기계·소방설비의 단계별 세부 시공 방법, 동원 인원 및 장비 계획, 용접 절차서(WPS), 비파괴검사(NDT), 수압시험 및 품질·안전관리 종합 시공계획서를 작성하여 감리단 승인을 득한다.</t>
-        </is>
-      </c>
-      <c r="K9" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 공종별 세부 시공 방법 및 절차서 작성, STEP 2: 자재 시험 및 품질관리 계획서 수립 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L9" s="102" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>KCS 41 시방 기준 준수, 유자격 용접사 WPS 승인 및 밀폐공간 안전보건 체계 확립</t>
+        </is>
+      </c>
+      <c r="K9" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (공종별 절차서 수립): 배관, 덕트, 장비설치 등 세부 작업별 인원·장비·공정 계획 및 위험성평가서 작성
+2) STEP 2 (WPS 용접절차 승인): 배관 재질별(STS, 탄소강) 용접절차시방서(WPS) 수립 및 유자격 용접사 시험편 PQR 검증
+3) STEP 3 (밀폐공간 안전관리): 지하 집수조/탱크 작업 시 복합가스(산소, 황화수소) 측정, 송기마스크 착용 및 감시원 상주</t>
+        </is>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>기계설비 시공계획서 수립 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M9" s="102" t="inlineStr">
+      <c r="M9" s="26" t="inlineStr">
         <is>
           <t>1) 기계설비 시공계획서 수립 (9000-8-8) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) KCS 41 건축기계시방 기준 장비투입, 용접/비파괴검사, 수압시험 및 안전관리 마스터 플랜을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N9" s="103">
+      <c r="N9" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\8_기계설비 시공계획서 수립\표준서\8_기계설비 시공계획서 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O9" s="102" t="inlineStr">
+      <c r="O9" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 공종별 세부 시공 방법 및 절차서 작성: 공조, 배관, 덕트, 소방, 자동제어 작업 기준
 2) STEP 2: 자재 시험 및 품질관리 계획서 수립: 수압시험, 기밀시험, 비파괴검사(NDT) 빈도 확정</t>
         </is>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\8_기계설비 시공계획서 수립\수행지침\8_기계설비 시공계획서 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q9" s="102" t="inlineStr">
+      <c r="Q9" s="26" t="inlineStr">
         <is>
           <t>1) 시공 방법 기술 시방 및 공조/위생/소방/오폐수/승강기 공종별 시공 절차 기준을 100% 충족하였는가?
 2) 용접 절차서(WPS) 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R9" s="105">
+      <c r="R9" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\8_기계설비 시공계획서 수립\체크리스트\8_기계설비 시공계획서 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S9" s="101" t="inlineStr">
+      <c r="S9" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T9" s="102" t="inlineStr">
+      <c r="T9" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U9" s="97" t="inlineStr">
+      <c r="U9" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V9" s="102" t="inlineStr">
+      <c r="V9" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="87" t="inlineStr">
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B10" s="87" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C10" s="87" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D10" s="88" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>9000-8-9</t>
         </is>
       </c>
-      <c r="E10" s="89" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>9000-8-8</t>
         </is>
       </c>
-      <c r="F10" s="90" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>9000-8-10</t>
         </is>
       </c>
-      <c r="G10" s="91" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>주요 기계_소방 기자재 검수</t>
         </is>
       </c>
-      <c r="H10" s="90" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>D-93</t>
         </is>
       </c>
-      <c r="I10" s="89" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J10" s="92" t="inlineStr">
-        <is>
-          <t>현장에 반입되는 배관용 스테인리스 강관, 인버터 가압 부스터펌프, 옥내소화전함, 밸브류, 공조기 등 주요 기자재에 대해 KS 인증서, 공인기관 시험성적서(밀시트), 공장검수(FAT) 성적을 1:1 대조하여 불량 자재의 현장 반입을 원천 차단한다.</t>
-        </is>
-      </c>
-      <c r="K10" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 자재 공급원 승인 요청서(MAR) 접수 및 검토, STEP 2: 주요 대형 장비 공장검수(FAT) 수행 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L10" s="93" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>배관, 밸브, 펌프 등 주요 기계·소방 기자재의 KS/KFI 규격 검증 및 공장 시험(FAT) 수행</t>
+        </is>
+      </c>
+      <c r="K10" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (공장검수 FAT 실시): 인버터 부스터펌프, 공조기 공장을 방문하여 모터 효율, 정격 양정·유량, 소음·진동 시험 입회
+2) STEP 2 (자재 현장 반입 검수): 밀시트(Mill Sheet), KS/KFI 인증서 확인 및 STS 강관 두께·진원도 마이크로미터 정밀 검측
+3) STEP 3 (자재 보관 및 불합격 통제): 배관 단부 보호캡 체결, 옥내 전용 적치장 보관 및 불합격 자재 24시간 이내 반출 조치</t>
+        </is>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>주요 기계_소방 기자재 검수 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M10" s="93" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t>1) 주요 기계_소방 기자재 검수 (9000-8-9) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) STS 강관(KSD 3576/3595), 인버터 부스터펌프, 호스릴 소화전함 KS 규격 및 공장검수(FAT)을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N10" s="94">
+      <c r="N10" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\9_주요 기계_소방 기자재 검수\표준서\9_주요 기계_소방 기자재 검수_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O10" s="93" t="inlineStr">
+      <c r="O10" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 자재 공급원 승인 요청서(MAR) 접수 및 검토: 제조사 공장등록증, KS인증서, 시험성적서
 2) STEP 2: 주요 대형 장비 공장검수(FAT) 수행: 공조기, 부스터펌프 제작 공장 방문 입회 시험</t>
         </is>
       </c>
-      <c r="P10" s="95">
+      <c r="P10" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\9_주요 기계_소방 기자재 검수\수행지침\9_주요 기계_소방 기자재 검수_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q10" s="93" t="inlineStr">
+      <c r="Q10" s="26" t="inlineStr">
         <is>
           <t>1) STS 강관 검수 시방 및 KSD 3576(배관용), KSD 3595(일반배관용) 두께/외경 기준을 100% 충족하였는가?
 2) 부스터펌프 검수 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R10" s="96">
+      <c r="R10" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\9_주요 기계_소방 기자재 검수\체크리스트\9_주요 기계_소방 기자재 검수_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S10" s="89" t="inlineStr">
+      <c r="S10" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T10" s="93" t="inlineStr">
+      <c r="T10" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U10" s="87" t="inlineStr">
+      <c r="U10" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V10" s="93" t="inlineStr">
+      <c r="V10" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="97" t="inlineStr">
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B11" s="97" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D11" s="98" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>9000-8-10</t>
         </is>
       </c>
-      <c r="E11" s="101" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>9000-8-9</t>
         </is>
       </c>
-      <c r="F11" s="99" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>9000-8-11</t>
         </is>
       </c>
-      <c r="G11" s="100" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>방화구획 내화채움구조 시공</t>
         </is>
       </c>
-      <c r="H11" s="99" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>D-90</t>
         </is>
       </c>
-      <c r="I11" s="101" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J11" s="102" t="inlineStr">
-        <is>
-          <t>건축물의 피난·방화구조 등의 기준에 관한 규칙에 따라 방화벽, 바닥 슬래브를 관통하는 기계 배관, 냉매관, 공조 덕트 주변의 관통 틈새에 대해 화재안전연구원 공인 인증을 득한 내화채움재(내화패드, 방화실란트, 차염/차열재)를 100% 밀폐 시공하여 화염 및 유독가스 층간 전파를 원천 차단한다.</t>
-        </is>
-      </c>
-      <c r="K11" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 관통부 틈새 청소 및 공인 내화구조 매핑, STEP 2: 내부 불연재(미네랄울) 고밀도 충진 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L11" s="102" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>콘크리트 골조 타설 전 관통 슬리브 선매립 및 2시간 차열·차염 내화채움구조 시공</t>
+        </is>
+      </c>
+      <c r="K11" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (골조 슬리브 선매립): 구조체 철근 배근 시 배관경 대비 1~2규격 큰 강관/PVC 슬리브 설치 및 단단히 고정
+2) STEP 2 (관통 틈새 내화충진): 배관 설치 후 슬리브 틈새에 고밀도 미네랄울(밀도 ≥ 100kg/㎥) 충진 및 방화실란트 15mm 도포
+3) STEP 3 (내화성능 확인): 공인기관 2시간 차열·차염 성적서 확인 및 우레탄폼 등 가연성 자재 사용 전면 금지 검측</t>
+        </is>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>방화구획 내화채움구조 시공 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M11" s="102" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t>1) 방화구획 내화채움구조 시공 (9000-8-10) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 슬래브 및 방화벽체 관통 덕트·배관 틈새 법정 공인 내화충진재 100% 밀폐 시공을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N11" s="103">
+      <c r="N11" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\10_방화구획 내화채움구조 시공\표준서\10_방화구획 내화채움구조 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O11" s="102" t="inlineStr">
+      <c r="O11" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 관통부 틈새 청소 및 공인 내화구조 매핑: 슬리브 내부 이물질, 분진 제거 및 성적서 대조
 2) STEP 2: 내부 불연재(미네랄울) 고밀도 충진: 규정 밀도(100kg/㎥ 이상) 준수 다짐 충진</t>
         </is>
       </c>
-      <c r="P11" s="104">
+      <c r="P11" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\10_방화구획 내화채움구조 시공\수행지침\10_방화구획 내화채움구조 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q11" s="102" t="inlineStr">
+      <c r="Q11" s="26" t="inlineStr">
         <is>
           <t>1) 공인 성적서 확인 시방 및 한국건설기술연구원 인정 내화채움구조 성적서 기준을 100% 충족하였는가?
 2) 암면/미네랄울 충진 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R11" s="105">
+      <c r="R11" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\10_방화구획 내화채움구조 시공\체크리스트\10_방화구획 내화채움구조 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S11" s="101" t="inlineStr">
+      <c r="S11" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T11" s="102" t="inlineStr">
+      <c r="T11" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U11" s="97" t="inlineStr">
+      <c r="U11" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V11" s="102" t="inlineStr">
+      <c r="V11" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="87" t="inlineStr">
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B12" s="87" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C12" s="87" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D12" s="88" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>9000-8-11</t>
         </is>
       </c>
-      <c r="E12" s="89" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>9000-8-10</t>
         </is>
       </c>
-      <c r="F12" s="90" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>9000-8-12</t>
         </is>
       </c>
-      <c r="G12" s="91" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>선로전환기 배수공동구 연계</t>
         </is>
       </c>
-      <c r="H12" s="90" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>D-87</t>
         </is>
       </c>
-      <c r="I12" s="89" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J12" s="92" t="inlineStr">
-        <is>
-          <t>트램 본선 궤도 분기부 및 차량기지 내 총 143개소의 핵심 선로전환기(Point Machine)와 열차 위치 검지용 차축검지기(Axle Counter) 구역의 침수 불량 및 동절기 결빙 사고를 원천 방지하기 위하여 궤도 콘크리트 타설 전 하부 횡단 배수용 파이프 및 전선관로 공동구를 정밀 선시공한다.</t>
-        </is>
-      </c>
-      <c r="K12" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 신호·궤도팀 합동 분기기 143개소 좌표 실측, STEP 2: 횡단 배수관로 매설 및 지지틀 고정 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L12" s="93" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>본선 및 차량기지 143개소 선로전환기 하부 배수관로 선시공으로 동절기 결빙 및 침수 방지</t>
+        </is>
+      </c>
+      <c r="K12" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (드레인 피트 가설): 선로전환기 구동부 하부에 침전 드레인 피트 및 STS 타공 스트레이너 설치
+2) STEP 2 (횡단 배수관로 연결): 도상 횡단 배수관(D100/150)을 자연유하 구배(i ≥ 1.0%)로 선로변 주 집수정까지 직결
+3) STEP 3 (궤도 타설 전 통수시험): 궤도 콘크리트 타설 전 통수 및 수압시험을 실시하여 관로 막힘 및 누수 0건 최종 확인</t>
+        </is>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t>선로전환기 배수공동구 연계 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M12" s="93" t="inlineStr">
+      <c r="M12" s="26" t="inlineStr">
         <is>
           <t>1) 선로전환기 배수공동구 연계 (9000-8-11) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 본선 및 차량기지 143개소 선로전환기 및 Axle Counter 하부 배수관로 공동구 선시공을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N12" s="94">
+      <c r="N12" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\11_선로전환기 배수공동구 연계\표준서\11_선로전환기 배수공동구 연계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O12" s="93" t="inlineStr">
+      <c r="O12" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 신호·궤도팀 합동 분기기 143개소 좌표 실측: 선로전환기 하부 배수구 위치 3D 확정
 2) STEP 2: 횡단 배수관로 매설 및 지지틀 고정: D100/150 고강도 배수관 가설 및 앵커링</t>
         </is>
       </c>
-      <c r="P12" s="95">
+      <c r="P12" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\11_선로전환기 배수공동구 연계\수행지침\11_선로전환기 배수공동구 연계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q12" s="93" t="inlineStr">
+      <c r="Q12" s="26" t="inlineStr">
         <is>
           <t>1) 배수관 위치 정합 시방 및 신호 선로전환기 143개소 설치 좌표와 1:1 대조 기준을 100% 충족하였는가?
 2) 배수관경 및 재질 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R12" s="96">
+      <c r="R12" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\11_선로전환기 배수공동구 연계\체크리스트\11_선로전환기 배수공동구 연계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S12" s="89" t="inlineStr">
+      <c r="S12" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T12" s="93" t="inlineStr">
+      <c r="T12" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U12" s="87" t="inlineStr">
+      <c r="U12" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V12" s="93" t="inlineStr">
+      <c r="V12" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="97" t="inlineStr">
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B13" s="97" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D13" s="98" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>9000-8-12</t>
         </is>
       </c>
-      <c r="E13" s="101" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>9000-8-11</t>
         </is>
       </c>
-      <c r="F13" s="99" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>9000-8-13</t>
         </is>
       </c>
-      <c r="G13" s="100" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>소방 기계 전원 간선 연계</t>
         </is>
       </c>
-      <c r="H13" s="99" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>D-84</t>
         </is>
       </c>
-      <c r="I13" s="101" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J13" s="102" t="inlineStr">
-        <is>
-          <t>화재안전기술기준(NFTC) 및 전기설비기술기준에 따라 소방펌프실 주펌프, 충압펌프, 지하차도 및 역사 제연팬에 공급되는 비상 전원 간선에 대해 최고 수준의 고내열 내화성능을 갖춘 NFR-8(또는 F-FR-8) 내화케이블을 전용 배관으로 포설하고, 전기분야 비상발전기·MCC반과 무결점 인터페이스를 완료한다.</t>
-        </is>
-      </c>
-      <c r="K13" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 소방 기계 부하 용량(kW) 산정 및 전기팀 통보, STEP 2: NFR-8 고내열 내화케이블 전용 관로 시공 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L13" s="102" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>소방펌프, 제연팬 등 소방설비의 10초 이내 비상전원 절환 및 NFR-8 내화배선 무중단 공급</t>
+        </is>
+      </c>
+      <c r="K13" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (비상전원 ATS 연계): 상용전원 정전 시 10초 이내 비상발전기 전원으로 자동 절환되는 ATS 인터록 구축
+2) STEP 2 (NFR-8 내화케이블 포설): 소방용 동력 간선에 고내열 NFR-8 케이블을 전용 금속관에 단독 배선하여 850℃ 내열 확보
+3) STEP 3 (MCC 제어반 세팅): 소방펌프 전용 MCC 제어반의 과부하 트립 기능을 배제(경보만 발생)하여 화재 시 연속 가동 보장</t>
+        </is>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
         <is>
           <t>소방 기계 전원 간선 연계 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M13" s="102" t="inlineStr">
+      <c r="M13" s="26" t="inlineStr">
         <is>
           <t>1) 소방 기계 전원 간선 연계 (9000-8-12) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 소방펌프, 제연팬용 전원선로 NFR-8/F-FR-8 내화케이블 적용 및 전기팀 인터페이스을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N13" s="103">
+      <c r="N13" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\12_소방 기계 전원 간선 연계\표준서\12_소방 기계 전원 간선 연계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O13" s="102" t="inlineStr">
+      <c r="O13" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 소방 기계 부하 용량(kW) 산정 및 전기팀 통보: 소방펌프, 충압펌프, 제연팬 기동 전류 대조
 2) STEP 2: NFR-8 고내열 내화케이블 전용 관로 시공: 일반 전선과 분리된 내화 배관 가설</t>
         </is>
       </c>
-      <c r="P13" s="104">
+      <c r="P13" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\12_소방 기계 전원 간선 연계\수행지침\12_소방 기계 전원 간선 연계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q13" s="102" t="inlineStr">
+      <c r="Q13" s="26" t="inlineStr">
         <is>
           <t>1) 내화케이블 규격 시방 및 KS C IEC 60331 내화성능 공인 인증(NFR-8/F-FR-8) 기준을 100% 충족하였는가?
 2) 소방 간선 전용화 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R13" s="105">
+      <c r="R13" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\12_소방 기계 전원 간선 연계\체크리스트\12_소방 기계 전원 간선 연계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S13" s="101" t="inlineStr">
+      <c r="S13" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T13" s="102" t="inlineStr">
+      <c r="T13" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U13" s="97" t="inlineStr">
+      <c r="U13" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V13" s="102" t="inlineStr">
+      <c r="V13" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="87" t="inlineStr">
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B14" s="87" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C14" s="87" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D14" s="88" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>9000-8-13</t>
         </is>
       </c>
-      <c r="E14" s="89" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>9000-8-12</t>
         </is>
       </c>
-      <c r="F14" s="90" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>9000-8-14</t>
         </is>
       </c>
-      <c r="G14" s="91" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>저수조 사수방지 흡입배관</t>
         </is>
       </c>
-      <c r="H14" s="90" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>D-81</t>
         </is>
       </c>
-      <c r="I14" s="89" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J14" s="92" t="inlineStr">
-        <is>
-          <t>정거장 및 차량기지 지하 저수조 내에서 생활위생용수와 소화용수가 장기간 정체되어 발생하는 사수(死水, 물고임 부패) 현상을 방지하기 위하여, 급수펌프 흡입배관의 최저점을 소화용수 유효수위 상향으로 확보하고, 저수조 내부에 유지관리용 칸막이 1개소를 설치하는 고도화 수배관 시스템을 시공한다.</t>
-        </is>
-      </c>
-      <c r="K14" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 저수조 용량 및 소화수 유효수위 계산, STEP 2: STS 패널형 저수조 조립 및 칸막이 가설 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L14" s="93" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>위생적인 STS304 패널형 저수조 설치, 생활용수 사수 방지 배관 및 소화수 유효용량 상시 확보</t>
+        </is>
+      </c>
+      <c r="K14" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (STS 패널 조립 용접): STS304 패널 아르곤(TIG) 용접 조립 후 액체침투탐상(PT)으로 용접부 결함 100% 색출
+2) STEP 2 (사수방지 흡입배관 분리): 급수펌프 흡입관은 소화수위 상단에, 소방펌프 흡입관은 바닥 최하단에 분리 배치
+3) STEP 3 (만수 수밀시험): 저수조 만수 후 24시간 동안 수위 강하 및 외부 누수 유무를 정밀 측정하여 감리단 합격 승인</t>
+        </is>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t>저수조 사수방지 흡입배관 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M14" s="93" t="inlineStr">
+      <c r="M14" s="26" t="inlineStr">
         <is>
           <t>1) 저수조 사수방지 흡입배관 (9000-8-13) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 소화용수 유효수위 상향 흡입배관 및 중앙 1개소 칸막이 적용 위생수질 오염 원천 방지을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N14" s="94">
+      <c r="N14" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\13_저수조 사수방지 흡입배관\표준서\13_저수조 사수방지 흡입배관_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O14" s="93" t="inlineStr">
+      <c r="O14" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 저수조 용량 및 소화수 유효수위 계산: 위생수량과 법정 소화수량(옥내소화전/스프링클러) 분리
 2) STEP 2: STS 패널형 저수조 조립 및 칸막이 가설: 용접부 비파괴검사 및 내식 보강</t>
         </is>
       </c>
-      <c r="P14" s="95">
+      <c r="P14" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\13_저수조 사수방지 흡입배관\수행지침\13_저수조 사수방지 흡입배관_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q14" s="93" t="inlineStr">
+      <c r="Q14" s="26" t="inlineStr">
         <is>
           <t>1) 흡입배관 레벨 시방 및 급수펌프 흡입관 최저점을 소화수 유효높이 상단에 배치 기준을 100% 충족하였는가?
 2) 사수방지 칸막이 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R14" s="96">
+      <c r="R14" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\13_저수조 사수방지 흡입배관\체크리스트\13_저수조 사수방지 흡입배관_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S14" s="89" t="inlineStr">
+      <c r="S14" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T14" s="93" t="inlineStr">
+      <c r="T14" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U14" s="87" t="inlineStr">
+      <c r="U14" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V14" s="93" t="inlineStr">
+      <c r="V14" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="97" t="inlineStr">
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B15" s="97" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D15" s="98" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>9000-8-14</t>
         </is>
       </c>
-      <c r="E15" s="101" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>9000-8-13</t>
         </is>
       </c>
-      <c r="F15" s="99" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>9000-8-15</t>
         </is>
       </c>
-      <c r="G15" s="100" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>지열 신재생에너지 배관 매설</t>
         </is>
       </c>
-      <c r="H15" s="99" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>D-78</t>
         </is>
       </c>
-      <c r="I15" s="101" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J15" s="102" t="inlineStr">
-        <is>
-          <t>신에너지 및 재생에너지 개발·이용·보급 촉진법 및 친환경 녹색건축물 인증 기준에 따라 차량기지 및 정거장에 지중 열교환용 고밀도 폴리에틸렌관(HDPE, KSM 3408)을 지하 150~200m 깊이로 천공 매설하고, 전기융착(EF) 접합 및 1.0MPa 수압시험, 친환경 벤토나이트 그라우팅을 완벽 시공한다.</t>
-        </is>
-      </c>
-      <c r="K15" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 지열 천공 지점 측량 및 천공기 가설, STEP 2: U-Tube PE 열교환관 조립 및 1차 수압시험 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L15" s="102" t="inlineStr">
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>수직 밀폐형 지열 U-Tube(심도 150m) 시공 및 친환경 지열 히트펌프 연계 열교환 극대화</t>
+        </is>
+      </c>
+      <c r="K15" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (천공 및 U-Tube 삽입): 직경 150mm x 심도 150m 천공 후 고밀도 PE 파이프(KSM 3408, SDR11) U-Tube 삽입
+2) STEP 2 (열전도 그라우팅): 천공 하부부터 지표면까지 벤토나이트 혼합 그라우트재(열전도도 ≥ 1.8 W/m·K)를 가압 연속 주입
+3) STEP 3 (수압시험 및 헤더 연결): 1.0 MPa 수압으로 2시간 동안 압력 유지 확인 후 기계실 지열 헤더 매니폴드 연결</t>
+        </is>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>지열 신재생에너지 배관 매설 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M15" s="102" t="inlineStr">
+      <c r="M15" s="26" t="inlineStr">
         <is>
           <t>1) 지열 신재생에너지 배관 매설 (9000-8-14) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 옥외 지열 천공(150~200m), 고밀도 PE관(KSM 3408) 열교환기 융착 및 1.0MPa 수압시험을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N15" s="103">
+      <c r="N15" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\14_지열 신재생에너지 배관 매설\표준서\14_지열 신재생에너지 배관 매설_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O15" s="102" t="inlineStr">
+      <c r="O15" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 지열 천공 지점 측량 및 천공기 가설: 지하 지장물 이격거리 확보 및 지중 천공
 2) STEP 2: U-Tube PE 열교환관 조립 및 1차 수압시험: U-Bend 헤드 융착 및 지상 수압 검측</t>
         </is>
       </c>
-      <c r="P15" s="104">
+      <c r="P15" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\14_지열 신재생에너지 배관 매설\수행지침\14_지열 신재생에너지 배관 매설_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q15" s="102" t="inlineStr">
+      <c r="Q15" s="26" t="inlineStr">
         <is>
           <t>1) 지열 천공 심도 시방 및 지중 150~200m 수직 천공 및 공벽 붕괴 방지 기준을 100% 충족하였는가?
 2) PE관 재질 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R15" s="105">
+      <c r="R15" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\14_지열 신재생에너지 배관 매설\체크리스트\14_지열 신재생에너지 배관 매설_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S15" s="101" t="inlineStr">
+      <c r="S15" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T15" s="102" t="inlineStr">
+      <c r="T15" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U15" s="97" t="inlineStr">
+      <c r="U15" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V15" s="102" t="inlineStr">
+      <c r="V15" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="87" t="inlineStr">
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B16" s="87" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C16" s="87" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D16" s="88" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>9000-8-15</t>
         </is>
       </c>
-      <c r="E16" s="89" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>9000-8-14</t>
         </is>
       </c>
-      <c r="F16" s="90" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>9000-8-16</t>
         </is>
       </c>
-      <c r="G16" s="91" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>정거장_변전소 환기덕트 시공</t>
         </is>
       </c>
-      <c r="H16" s="90" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>D-75</t>
         </is>
       </c>
-      <c r="I16" s="89" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J16" s="92" t="inlineStr">
-        <is>
-          <t>지하 정거장 대합실/승강장 및 변전실·전기실의 쾌적한 실내 환경 유지와 전기기기 발열 배출을 위해 KCS 41 시방서에 맞춰 아연도금강판(GI) 공조덕트를 시공하며, 변전실 시간당 10회 환기, 화장실 15~20회 음압 배기 및 동절기 외기 역류 방지용 B.D.D(기류역류방지댐퍼)를 완벽 가설한다.</t>
-        </is>
-      </c>
-      <c r="K16" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 덕트 제작 치수 검수 및 아연도금강판 가공, STEP 2: 풍도 댐퍼 및 B.D.D 기류역류방지댐퍼 조립 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L16" s="93" t="inlineStr">
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>변전실 1종 급기가압(10회/h, 실온 ≤40℃) 및 화장실 3종 음압 환기, 역류방지(B.D.D) 구축</t>
+        </is>
+      </c>
+      <c r="K16" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (아연도강판 덕트 제작): KCS 41 시방 기준에 따라 아연도강판(GI) 피츠버그 록 성형 및 기밀 실링 시공
+2) STEP 2 (방진행거 및 댐퍼 취부): 덕트 하중 지지를 위한 방진스프링 행거(간격 ≤ 2.0m) 및 역류방지 댐퍼(B.D.D) 체결
+3) STEP 3 (덕트 누기시험): 연기발생기 및 차압계를 이용하여 허용 누기량(클래스 3 이하) 만족 여부 정밀 측정</t>
+        </is>
+      </c>
+      <c r="L16" s="17" t="inlineStr">
         <is>
           <t>정거장_변전소 환기덕트 시공 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M16" s="93" t="inlineStr">
+      <c r="M16" s="26" t="inlineStr">
         <is>
           <t>1) 정거장_변전소 환기덕트 시공 (9000-8-15) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 전기실 1종 정압(10회/h, 실온≤40℃), 화장실 3종 음압(15~20회/h) 및 B.D.D 기류역류방지댐퍼을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N16" s="94">
+      <c r="N16" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\15_정거장_변전소 환기덕트 시공\표준서\15_정거장_변전소 환기덕트 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O16" s="93" t="inlineStr">
+      <c r="O16" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 덕트 제작 치수 검수 및 아연도금강판 가공: 자동 절단/절곡기를 통한 각형 덕트 정밀 제작
 2) STEP 2: 풍도 댐퍼 및 B.D.D 기류역류방지댐퍼 조립: 외기 침입 차단 및 풍량 조절 장치 가설</t>
         </is>
       </c>
-      <c r="P16" s="95">
+      <c r="P16" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\15_정거장_변전소 환기덕트 시공\수행지침\15_정거장_변전소 환기덕트 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q16" s="93" t="inlineStr">
+      <c r="Q16" s="26" t="inlineStr">
         <is>
           <t>1) 덕트 판두께 시방 및 아연도금강판(KSD 3506) 장변 크기별 규격 두께 준수 기준을 100% 충족하였는가?
 2) 기류역류방지댐퍼 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R16" s="96">
+      <c r="R16" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\15_정거장_변전소 환기덕트 시공\체크리스트\15_정거장_변전소 환기덕트 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S16" s="89" t="inlineStr">
+      <c r="S16" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T16" s="93" t="inlineStr">
+      <c r="T16" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U16" s="87" t="inlineStr">
+      <c r="U16" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V16" s="93" t="inlineStr">
+      <c r="V16" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="97" t="inlineStr">
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B17" s="97" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C17" s="97" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D17" s="98" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>9000-8-16</t>
         </is>
       </c>
-      <c r="E17" s="101" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>9000-8-15</t>
         </is>
       </c>
-      <c r="F17" s="99" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>9000-8-17</t>
         </is>
       </c>
-      <c r="G17" s="100" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>고내열(250℃) 제연팬_풍도</t>
         </is>
       </c>
-      <c r="H17" s="99" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>D-72</t>
         </is>
       </c>
-      <c r="I17" s="101" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J17" s="102" t="inlineStr">
-        <is>
-          <t>도시철도건설규칙 및 화재안전기준(NFTC 501)에 따라 화재 시 발생하는 고온의 유독가스를 신속히 배출하기 위해, 250℃ 고온에서 1시간 이상 연속 운전이 가능한 공인 시험기관 인증 제연팬(Axial Fan), 내화 풍도, 1.5mm 아연도 강판 덕트 및 불연 내열 캔버스를 완벽 시공한다.</t>
-        </is>
-      </c>
-      <c r="K17" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 250℃ 고내열 제연팬 사양 검토 및 반입 검수, STEP 2: 1.5mm 이상 고강도 제연 풍도 및 내진 지지대 시공 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L17" s="102" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>KFI 공인 250℃ 1시간 연속운전 고내열 제연팬 및 1.5mm 내화풍도 시공으로 화재 유독가스 배출</t>
+        </is>
+      </c>
+      <c r="K17" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (고내열 제연팬 거치): KFI 250℃/1h 내열인증 H종 절연 제연팬을 방진 스프링 베이스 위에 수평 거치
+2) STEP 2 (내화 제연덕트 체결): 1.5mm 이상 두꺼운 강판 덕트에 1,000℃ 세라믹 불연 가스켓을 삽입하여 고장력 볼트 체결
+3) STEP 3 (내진 브레이싱 및 기동 시험): 종·횡방향 내진 버팀대(간격 9m/4.5m) 시공 후 화재 신호 수신 시 30초 내 기동 검증</t>
+        </is>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>고내열(250℃) 제연팬_풍도 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M17" s="102" t="inlineStr">
+      <c r="M17" s="26" t="inlineStr">
         <is>
           <t>1) 고내열(250℃) 제연팬_풍도 (9000-8-16) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 최고 250℃에서 1시간 이상 연속운전 공인 내열 제연팬, 풍도 댐퍼 및 고내열 캔버스 가설을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N17" s="103">
+      <c r="N17" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\16_고내열(250℃) 제연팬_풍도\표준서\16_고내열(250℃) 제연팬_풍도_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O17" s="102" t="inlineStr">
+      <c r="O17" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 250℃ 고내열 제연팬 사양 검토 및 반입 검수: 내열 모터, KFI 내열 인증서, 블레이드 점검
 2) STEP 2: 1.5mm 이상 고강도 제연 풍도 및 내진 지지대 시공: 두꺼운 강판 용접 및 불연 가스켓 체결</t>
         </is>
       </c>
-      <c r="P17" s="104">
+      <c r="P17" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\16_고내열(250℃) 제연팬_풍도\수행지침\16_고내열(250℃) 제연팬_풍도_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q17" s="102" t="inlineStr">
+      <c r="Q17" s="26" t="inlineStr">
         <is>
           <t>1) 제연팬 공인인증 시방 및 한국소방산업기술원(KFI) 250℃/1h 내열 성적서 기준을 100% 충족하였는가?
 2) 풍도 강판 두께 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R17" s="105">
+      <c r="R17" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\16_고내열(250℃) 제연팬_풍도\체크리스트\16_고내열(250℃) 제연팬_풍도_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S17" s="101" t="inlineStr">
+      <c r="S17" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T17" s="102" t="inlineStr">
+      <c r="T17" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U17" s="97" t="inlineStr">
+      <c r="U17" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V17" s="102" t="inlineStr">
+      <c r="V17" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="87" t="inlineStr">
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B18" s="87" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C18" s="87" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D18" s="88" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>9000-8-17</t>
         </is>
       </c>
-      <c r="E18" s="89" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>9000-8-16</t>
         </is>
       </c>
-      <c r="F18" s="90" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>9000-8-18</t>
         </is>
       </c>
-      <c r="G18" s="91" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>검수고 국부 냉난방 가설</t>
         </is>
       </c>
-      <c r="H18" s="90" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>D-69</t>
         </is>
       </c>
-      <c r="I18" s="89" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J18" s="92" t="inlineStr">
-        <is>
-          <t>차량기지 종합검수고동 등 층고가 높고 체적이 거대한 대공간을 전면 냉난방하는 에너지 비효율성을 방지하기 위하여, 정비원이 실제 작업하는 핏트(Pit) 및 차체 검수 구역에 이동식 에어컨과 원적외선 전기히터를 국부 배치하고, 변전소 전기실에는 패키지 에어컨(PAC)을 정밀 가설한다.</t>
-        </is>
-      </c>
-      <c r="K18" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 대공간 국부 작업 구역 부하 분석 및 장비 선정, STEP 2: 변전실 패키지 에어컨(PAC) 3대 정합성 가설 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L18" s="93" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>대공간 검수고 작업자 중심 국부 냉난방(이동식 에어컨/원적외선) 및 변전소 전용 PAC 3대 배치</t>
+        </is>
+      </c>
+      <c r="K18" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (변전소 PAC 3대 설치): 변전소별 패키지 에어컨(PAC) 3대를 등간격 배치하고 R-410A 냉매배관 기밀시험(3.8MPa)
+2) STEP 2 (검수고 국부 냉난방 가설): 정비 피트 및 작업대 위치에 이동식 플렉시블 토출 에어컨과 고효율 원적외선 난방기 설치
+3) STEP 3 (시운전 및 온습도 측정): 실별 자동온도조절기(TC) 세팅 및 24시간 연속 운전을 통해 실온 ≤ 28℃ 유지 성능 검증</t>
+        </is>
+      </c>
+      <c r="L18" s="17" t="inlineStr">
         <is>
           <t>검수고 국부 냉난방 가설 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M18" s="93" t="inlineStr">
+      <c r="M18" s="26" t="inlineStr">
         <is>
           <t>1) 검수고 국부 냉난방 가설 (9000-8-17) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 차량기지 종합검수고 대공간 에너지 절감 이동식 에어컨/히터 및 변전실 PAC 가설을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N18" s="94">
+      <c r="N18" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\17_검수고 국부 냉난방 가설\표준서\17_검수고 국부 냉난방 가설_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O18" s="93" t="inlineStr">
+      <c r="O18" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 대공간 국부 작업 구역 부하 분석 및 장비 선정: 정비원 상주 위치 및 작업 패턴 맞춤 설계
 2) STEP 2: 변전실 패키지 에어컨(PAC) 3대 정합성 가설: 내역서/도면 수량 일치 및 실내외기 배관</t>
         </is>
       </c>
-      <c r="P18" s="95">
+      <c r="P18" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\17_검수고 국부 냉난방 가설\수행지침\17_검수고 국부 냉난방 가설_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q18" s="93" t="inlineStr">
+      <c r="Q18" s="26" t="inlineStr">
         <is>
           <t>1) 국부 장비 배치 시방 및 종합검수고 하부 피트 및 측면 작업대 전용 배치 기준을 100% 충족하였는가?
 2) 이동식 에어컨 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R18" s="96">
+      <c r="R18" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\17_검수고 국부 냉난방 가설\체크리스트\17_검수고 국부 냉난방 가설_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S18" s="89" t="inlineStr">
+      <c r="S18" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T18" s="93" t="inlineStr">
+      <c r="T18" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U18" s="87" t="inlineStr">
+      <c r="U18" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V18" s="93" t="inlineStr">
+      <c r="V18" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="97" t="inlineStr">
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B19" s="97" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C19" s="97" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D19" s="98" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>9000-8-18</t>
         </is>
       </c>
-      <c r="E19" s="101" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>9000-8-17</t>
         </is>
       </c>
-      <c r="F19" s="99" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>9000-8-19</t>
         </is>
       </c>
-      <c r="G19" s="100" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>냉온수_냉각수 배관 용접</t>
         </is>
       </c>
-      <c r="H19" s="99" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>D-66</t>
         </is>
       </c>
-      <c r="I19" s="101" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J19" s="102" t="inlineStr">
-        <is>
-          <t>중앙 기계실 냉동기, 열교환기, 펌프와 공조기를 연결하는 냉온수 및 냉각수 주배관에 대해 KCS 41 시방 기준에 따라 숙련된 유자격 용접사가 맞대기 아크용접 및 TIG 용접을 수행하고, 용접부 비파괴검사(RT ≥ 10%), 설계압력 1.5배 수압시험, 방청 도장 및 보온 단열재를 완벽 시공한다.</t>
-        </is>
-      </c>
-      <c r="K19" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 배관 절단 및 개선(Beveling) 가공, STEP 2: 가접 및 다층 맞대기 용접(WPS 준수) 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L19" s="102" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>KSD 3562 탄소강관 맞대기 용접, 비파괴검사(RT ≥ 10%) 및 1.5MPa 수압시험을 통한 누수 Zero</t>
+        </is>
+      </c>
+      <c r="K19" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (그루브 가공 및 맞대기 용접): 배관 단부 30~35° 베벨 가공 후 TIG 루트패스 및 아크 다층 맞대기 용접
+2) STEP 2 (방사선 비파괴검사 RT): 용접부의 10% 이상을 무작위 추출하여 방사선 투과 촬영(RT) 및 결함(기공, 슬래그) 100% 판독
+3) STEP 3 (1.5배 수압시험 및 보온): 설계압력 1.5배(1.5MPa) 60분 무누수 확인 후 난연 고무발포 단열재(40mm) 밀착 시공</t>
+        </is>
+      </c>
+      <c r="L19" s="17" t="inlineStr">
         <is>
           <t>냉온수_냉각수 배관 용접 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M19" s="102" t="inlineStr">
+      <c r="M19" s="26" t="inlineStr">
         <is>
           <t>1) 냉온수_냉각수 배관 용접 (9000-8-18) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 배관용 탄소강관(KSD 3507/3562) 아크용접, 비파괴검사(RT/UT) 및 1.5배 수압시험을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N19" s="103">
+      <c r="N19" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\18_냉온수_냉각수 배관 용접\표준서\18_냉온수_냉각수 배관 용접_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O19" s="102" t="inlineStr">
+      <c r="O19" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 배관 절단 및 개선(Beveling) 가공: 자동 파이프 절단기 및 그라인더 개선각(30~35°) 가공
 2) STEP 2: 가접 및 다층 맞대기 용접(WPS 준수): 루트 패스 TIG 용접 + 캡 패스 아크용접</t>
         </is>
       </c>
-      <c r="P19" s="104">
+      <c r="P19" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\18_냉온수_냉각수 배관 용접\수행지침\18_냉온수_냉각수 배관 용접_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q19" s="102" t="inlineStr">
+      <c r="Q19" s="26" t="inlineStr">
         <is>
           <t>1) 용접사 자격 검증 시방 및 국가기술자격(용접기능사 이상) 및 기량 시험 합격 기준을 100% 충족하였는가?
 2) 용접부 비파괴(NDT) 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R19" s="105">
+      <c r="R19" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\18_냉온수_냉각수 배관 용접\체크리스트\18_냉온수_냉각수 배관 용접_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S19" s="101" t="inlineStr">
+      <c r="S19" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T19" s="102" t="inlineStr">
+      <c r="T19" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U19" s="97" t="inlineStr">
+      <c r="U19" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V19" s="102" t="inlineStr">
+      <c r="V19" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="87" t="inlineStr">
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B20" s="87" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C20" s="87" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D20" s="88" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>9000-8-19</t>
         </is>
       </c>
-      <c r="E20" s="89" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>9000-8-18</t>
         </is>
       </c>
-      <c r="F20" s="90" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>9000-8-20</t>
         </is>
       </c>
-      <c r="G20" s="91" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>능동지하차도 전용터널 제연</t>
         </is>
       </c>
-      <c r="H20" s="90" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>D-63</t>
         </is>
       </c>
-      <c r="I20" s="89" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J20" s="92" t="inlineStr">
-        <is>
-          <t>도시철도건설규칙 제67조에 따라 능동지하차도 트램 전용터널 통과 구간에 화재 발생 시 승객의 안전 피난 방향으로 연기 유동을 제어(임계풍속 ≥ 2.5m/s 확보)하는 제연설비, 건식 연결송수관 및 CFD 컴퓨터 화재 수치해석 시뮬레이션을 완벽 시공·검증한다.</t>
-        </is>
-      </c>
-      <c r="K20" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 3D CFD 화재 및 피난 시뮬레이션 모델링, STEP 2: 터널 천장 제연팬(Jet Fan) 앵커링 및 내진 시공 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L20" s="93" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>지하차도 트램 전용터널 제연(Jet Fan 임계풍속 ≥ 2.5m/s) 및 50m 간격 건식 연결송수관 구축</t>
+        </is>
+      </c>
+      <c r="K20" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (Jet Fan 천장 앵커링): 터널 천장부에 진동 감쇠 방진행거 및 고장력 케미컬 앵커로 Jet Fan 안전 체결
+2) STEP 2 (3D CFD 풍속 검증): 터널 화재 시뮬레이션 기반 임계풍속(2.5m/s) 도출 및 연기 역류(Backlayering) 차단 검증
+3) STEP 3 (건식 연결송수관 시공): 50m 간격 방수구함(D100 Sch40) 설치 및 2.0MPa 고압 수압시험을 통한 배관 내력 확인</t>
+        </is>
+      </c>
+      <c r="L20" s="17" t="inlineStr">
         <is>
           <t>능동지하차도 전용터널 제연 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M20" s="93" t="inlineStr">
+      <c r="M20" s="26" t="inlineStr">
         <is>
           <t>1) 능동지하차도 전용터널 제연 (9000-8-19) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 트램 전용터널 제연팬, 건식 연결송수관 및 CFD 수치해석 시뮬레이션 기반 피난기류 검증을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N20" s="94">
+      <c r="N20" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\19_능동지하차도 전용터널 제연\표준서\19_능동지하차도 전용터널 제연_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O20" s="93" t="inlineStr">
+      <c r="O20" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 3D CFD 화재 및 피난 시뮬레이션 모델링: 화재 열방출률(HRR), 연기 확산 및 가시거리 해석
 2) STEP 2: 터널 천장 제연팬(Jet Fan) 앵커링 및 내진 시공: 콘크리트 케미컬 앵커 및 방진 스프링</t>
         </is>
       </c>
-      <c r="P20" s="95">
+      <c r="P20" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\19_능동지하차도 전용터널 제연\수행지침\19_능동지하차도 전용터널 제연_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q20" s="93" t="inlineStr">
+      <c r="Q20" s="26" t="inlineStr">
         <is>
           <t>1) CFD 화재 시뮬레이션 시방 및 화재 강도(5~10MW) 및 승객 피난 시뮬레이션 기준을 100% 충족하였는가?
 2) 터널 제연팬(Jet Fan) 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R20" s="96">
+      <c r="R20" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\19_능동지하차도 전용터널 제연\체크리스트\19_능동지하차도 전용터널 제연_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S20" s="89" t="inlineStr">
+      <c r="S20" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T20" s="93" t="inlineStr">
+      <c r="T20" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U20" s="87" t="inlineStr">
+      <c r="U20" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V20" s="93" t="inlineStr">
+      <c r="V20" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="97" t="inlineStr">
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B21" s="97" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C21" s="97" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D21" s="98" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>9000-8-20</t>
         </is>
       </c>
-      <c r="E21" s="101" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>9000-8-19</t>
         </is>
       </c>
-      <c r="F21" s="99" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>9000-8-21</t>
         </is>
       </c>
-      <c r="G21" s="100" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>공기조화기(AHU_PAC) 거치</t>
         </is>
       </c>
-      <c r="H21" s="99" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>D-60</t>
         </is>
       </c>
-      <c r="I21" s="101" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J21" s="102" t="inlineStr">
-        <is>
-          <t>지하 정거장 공조기계실 및 전기실에 대형 공기조화기(AHU)와 항온항습기(PAC)를 반입하여 기초 콘크리트 패드 위에 거치하고, 기계 가동 진동이 건축 구조물로 전파되는 것을 차단하는 방진스프링 마운트(정적변위 25~50mm), 드레인 트랩 및 수평도(±1mm)를 완벽 시공한다.</t>
-        </is>
-      </c>
-      <c r="K21" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 기초 콘크리트 패드 검측 및 기준선 마킹, STEP 2: AHU 분할 반입 및 블록 조립 결속 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L21" s="102" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>공조기 케이싱 수평 거치, 방진마운트(정적변위 ≥ 25mm) 진동 차단 및 딥 U-Trap 배수</t>
+        </is>
+      </c>
+      <c r="K21" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (기초 패드 및 방진마운트): 콘크리트 패드 위에 정적 변위 25mm 밀폐형 스프링 방진기 설치 및 수평 레벨링
+2) STEP 2 (불연 캔버스 연결): 송풍기 토출구와 덕트 사이에 실리콘 코팅 불연 캔버스를 주름 없이 견고히 체결
+3) STEP 3 (딥 U-Trap 드레인 시공): 흡입 부압에 견디도록 유효 봉수 100mm 이상의 드레인 트랩 시공 후 배수 통수시험</t>
+        </is>
+      </c>
+      <c r="L21" s="17" t="inlineStr">
         <is>
           <t>공기조화기(AHU_PAC) 거치 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M21" s="102" t="inlineStr">
+      <c r="M21" s="26" t="inlineStr">
         <is>
           <t>1) 공기조화기(AHU_PAC) 거치 (9000-8-20) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 공조기계실 AHU, 전기실 항온항습기(PAC) 방진스프링 방진가대 가설 및 수평도 검측을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N21" s="103">
+      <c r="N21" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\20_공기조화기(AHU_PAC) 거치\표준서\20_공기조화기(AHU_PAC) 거치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O21" s="102" t="inlineStr">
+      <c r="O21" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 기초 콘크리트 패드 검측 및 기준선 마킹: 기계실 바닥 패드 높이, 수평도, 앵커 위치 실측
 2) STEP 2: AHU 분할 반입 및 블록 조립 결속: 송풍기부, 코일부, 필터부 정밀 밀착 체결</t>
         </is>
       </c>
-      <c r="P21" s="104">
+      <c r="P21" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\20_공기조화기(AHU_PAC) 거치\수행지침\20_공기조화기(AHU_PAC) 거치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q21" s="102" t="inlineStr">
+      <c r="Q21" s="26" t="inlineStr">
         <is>
           <t>1) 기초 패드 검측 시방 및 콘크리트 패드 강도(≥24MPa), 수평도 및 배근 기준을 100% 충족하였는가?
 2) 방진 마운트 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R21" s="105">
+      <c r="R21" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\20_공기조화기(AHU_PAC) 거치\체크리스트\20_공기조화기(AHU_PAC) 거치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S21" s="101" t="inlineStr">
+      <c r="S21" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T21" s="102" t="inlineStr">
+      <c r="T21" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U21" s="97" t="inlineStr">
+      <c r="U21" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V21" s="102" t="inlineStr">
+      <c r="V21" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="87" t="inlineStr">
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B22" s="87" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C22" s="87" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D22" s="88" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>9000-8-21</t>
         </is>
       </c>
-      <c r="E22" s="89" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>9000-8-20</t>
         </is>
       </c>
-      <c r="F22" s="90" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>9000-8-22</t>
         </is>
       </c>
-      <c r="G22" s="91" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>급수_급탕 STS 배관 시공</t>
         </is>
       </c>
-      <c r="H22" s="90" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>D+5</t>
         </is>
       </c>
-      <c r="I22" s="89" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J22" s="92" t="inlineStr">
-        <is>
-          <t>정거장 및 차량기지 관리동의 위생적인 음용수 및 급탕 공급을 위하여 KSD 3595(일반배관용 스테인리스 강관) 및 KSD 3576(배관용 스테인리스 강관)을 적용하고, 전용 전동 압착공구를 사용한 무용접 프레스 조인트 시공, 1.0MPa 수압시험, 배관 내부 염소 소독 세척을 완벽 수행한다.</t>
-        </is>
-      </c>
-      <c r="K22" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: STS 파이프 정밀 절단 및 단부 버(Burr) 제거, STEP 2: 피팅 삽입 깊이 마킹 및 전동 압착 체결 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L22" s="93" t="inlineStr">
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>STS304 강관 무용접 프레스 피팅 전동 압착, 1.0MPa 수압시험 및 위생 염소소독 완료</t>
+        </is>
+      </c>
+      <c r="K22" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (관 절단 및 프레스 압착): 롤러 커터로 관 직각 절단, 리머 버 제거, EPDM 오링 삽입 후 전동 압착공구 체결
+2) STEP 2 (육각 게이지 전수 검측): 전용 판정 게이지(Go/No-Go)를 결합부에 밀착하여 압착 치수 정밀도 100% 전수 검사
+3) STEP 3 (수압시험 및 차아염소산 소독): 1.0MPa 60분 수압 무누수 확인 후 50ppm 염소수로 24시간 통수 살균 및 수질검사</t>
+        </is>
+      </c>
+      <c r="L22" s="17" t="inlineStr">
         <is>
           <t>급수_급탕 STS 배관 시공 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M22" s="93" t="inlineStr">
+      <c r="M22" s="26" t="inlineStr">
         <is>
           <t>1) 급수_급탕 STS 배관 시공 (9000-8-21) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) KSD 3595 무용접 프레스 압착이음/용접이음, 배관 세척 소독 및 1.0MPa 수압시험을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N22" s="94">
+      <c r="N22" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\21_급수_급탕 STS 배관 시공\표준서\21_급수_급탕 STS 배관 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O22" s="93" t="inlineStr">
+      <c r="O22" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: STS 파이프 정밀 절단 및 단부 버(Burr) 제거: 전용 롤러 커터 절단 및 리머 내·외부 모따기
 2) STEP 2: 피팅 삽입 깊이 마킹 및 전동 압착 체결: 삽입선 마킹 확인 및 전용 조(Jaw) 압착</t>
         </is>
       </c>
-      <c r="P22" s="95">
+      <c r="P22" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\21_급수_급탕 STS 배관 시공\수행지침\21_급수_급탕 STS 배관 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q22" s="93" t="inlineStr">
+      <c r="Q22" s="26" t="inlineStr">
         <is>
           <t>1) STS 파이프 규격 시방 및 KSD 3595 SU 파이프 및 KSD 3576 Sch 10S/20S 기준을 100% 충족하였는가?
 2) 무용접 프레스 압착 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R22" s="96">
+      <c r="R22" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\21_급수_급탕 STS 배관 시공\체크리스트\21_급수_급탕 STS 배관 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S22" s="89" t="inlineStr">
+      <c r="S22" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T22" s="93" t="inlineStr">
+      <c r="T22" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U22" s="87" t="inlineStr">
+      <c r="U22" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V22" s="93" t="inlineStr">
+      <c r="V22" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="97" t="inlineStr">
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B23" s="97" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C23" s="97" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D23" s="98" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>9000-8-22</t>
         </is>
       </c>
-      <c r="E23" s="101" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>9000-8-21</t>
         </is>
       </c>
-      <c r="F23" s="99" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>9000-8-23</t>
         </is>
       </c>
-      <c r="G23" s="100" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>오배수관 및 집수조 배수펌프</t>
         </is>
       </c>
-      <c r="H23" s="99" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>D+10</t>
         </is>
       </c>
-      <c r="I23" s="101" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J23" s="102" t="inlineStr">
-        <is>
-          <t>정거장 화장실 오수, 바닥 잡배수 및 지하 침출수를 신속하고 안전하게 배출하기 위해, 오배수 배관의 자연유하 구배(1/50~1/100)를 확보하고, 지하 최하층 집수조에 고효율 수중 카터/오수 배수펌프 2대(1대 상용, 1대 예비)와 수위센서 연동 자동 교번 운전 제어반을 완벽 시공한다.</t>
-        </is>
-      </c>
-      <c r="K23" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 오배수 배관 라인 먹매김 및 구배 계획, STEP 2: 주철관/PVC관 포설 및 배관 행거 고정 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L23" s="102" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>오배수관 자연유하 구배(i ≥ 1/100) 유지 및 집수조 수중배수펌프 자동교번 4단 수위제어</t>
+        </is>
+      </c>
+      <c r="K23" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (자연유하 구배 시공): 레이저 레벨기를 이용하여 오수관 1/100, 배수관 1/50 구배를 철저히 유지하며 배관 포설
+2) STEP 2 (수중펌프 자동교번 안착): 집수조 바닥에 상용 및 예비 수중펌프 2대를 자동탈착 가이드레일 방식으로 거치
+3) STEP 3 (4단 전극봉 수위 인터록): 정지(LWL), 교번기동(HWL), 동시기동(E-HWL), 고수위경보(Alarm) 4단 센서 작동 검증</t>
+        </is>
+      </c>
+      <c r="L23" s="17" t="inlineStr">
         <is>
           <t>오배수관 및 집수조 배수펌프 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M23" s="102" t="inlineStr">
+      <c r="M23" s="26" t="inlineStr">
         <is>
           <t>1) 오배수관 및 집수조 배수펌프 (9000-8-22) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 오배수 주철관/PVC관 구배(1/100) 시공, 집수조 수위센서 연동 자동교번 배수펌프 가설을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N23" s="103">
+      <c r="N23" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\22_오배수관 및 집수조 배수펌프\표준서\22_오배수관 및 집수조 배수펌프_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O23" s="102" t="inlineStr">
+      <c r="O23" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 오배수 배관 라인 먹매김 및 구배 계획: 자연유하 구배(1/100) 및 슬리브 높이 대조
 2) STEP 2: 주철관/PVC관 포설 및 배관 행거 고정: 무소음 내화 PVC관 및 원터치 클램프 체결</t>
         </is>
       </c>
-      <c r="P23" s="104">
+      <c r="P23" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\22_오배수관 및 집수조 배수펌프\수행지침\22_오배수관 및 집수조 배수펌프_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q23" s="102" t="inlineStr">
+      <c r="Q23" s="26" t="inlineStr">
         <is>
           <t>1) 오배수관 구배 시방 및 관경 D75 이하 1/50, D100 이상 1/100 자연유하 기준을 100% 충족하였는가?
 2) 통기관(Vent) 시공 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R23" s="105">
+      <c r="R23" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\22_오배수관 및 집수조 배수펌프\체크리스트\22_오배수관 및 집수조 배수펌프_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S23" s="101" t="inlineStr">
+      <c r="S23" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T23" s="102" t="inlineStr">
+      <c r="T23" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U23" s="97" t="inlineStr">
+      <c r="U23" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V23" s="102" t="inlineStr">
+      <c r="V23" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="87" t="inlineStr">
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B24" s="87" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C24" s="87" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D24" s="88" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>9000-8-23</t>
         </is>
       </c>
-      <c r="E24" s="89" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>9000-8-22</t>
         </is>
       </c>
-      <c r="F24" s="90" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>9000-8-24</t>
         </is>
       </c>
-      <c r="G24" s="91" t="inlineStr">
+      <c r="G24" s="17" t="inlineStr">
         <is>
           <t>차량기지 오폐수처리장(90㎡)</t>
         </is>
       </c>
-      <c r="H24" s="90" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>D+15</t>
         </is>
       </c>
-      <c r="I24" s="89" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J24" s="92" t="inlineStr">
-        <is>
-          <t>차량기지 중정비 공장(대차도장, 대차세척, 부품세척 등 23.314 ㎥/일), 경정비 공장(4.054 ㎥/일) 및 청소선에서 발생하는 고농도 유기계·유류 폐수를 법정 환경 기준 이하로 정화 배출하기 위해 기지 외곽에 연면적 90㎡ 규모의 전용 가설 폐수처리장, 유수분리기, 화학응집침전조 및 활성탄 흡착탑을 완벽 시공한다.</t>
-        </is>
-      </c>
-      <c r="K24" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 폐수처리장(90㎡) 토목 구조물 및 방수 검측, STEP 2: 유수분리기 및 원수 수집조 설비 설치 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L24" s="93" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>중정비·경정비 발생 오폐수(35㎥/일)의 유수분리, 화학응집, 활성탄 흡착 및 수질 TMS 원격 방류</t>
+        </is>
+      </c>
+      <c r="K24" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (유수분리기 설치): 차량 정비 폐수의 비중차 유분 분리조 및 오일 스키머 설치로 유분 농도 90% 이상 제거
+2) STEP 2 (응집 침전 및 가압부상): PAC 응집제 및 폴리머 자동 주입기를 통해 플록(Floc) 침전 및 슬러지 탈수기 케이크 처리
+3) STEP 3 (활성탄 흡착 및 TMS 연동): 2단 활성탄 흡착탑 정화 후 BOD/COD ≤ 20mg/L 수질 TMS 데이터 환경청 자동 전송</t>
+        </is>
+      </c>
+      <c r="L24" s="17" t="inlineStr">
         <is>
           <t>차량기지 오폐수처리장(90㎡) 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M24" s="93" t="inlineStr">
+      <c r="M24" s="26" t="inlineStr">
         <is>
           <t>1) 차량기지 오폐수처리장(90㎡) (9000-8-23) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 중정비(23.3㎥/일) 및 경정비 폐수 수집조, 화학 침전, 유수분리기 및 악취방지 덮개을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N24" s="94">
+      <c r="N24" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\23_차량기지 오폐수처리장(90㎡)\표준서\23_차량기지 오폐수처리장(90㎡)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O24" s="93" t="inlineStr">
+      <c r="O24" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 폐수처리장(90㎡) 토목 구조물 및 방수 검측: 내화학 콘크리트 및 에폭시 3회 라이닝
 2) STEP 2: 유수분리기 및 원수 수집조 설비 설치: 비중차 유수분리 스크린 및 오일 스키머</t>
         </is>
       </c>
-      <c r="P24" s="95">
+      <c r="P24" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\23_차량기지 오폐수처리장(90㎡)\수행지침\23_차량기지 오폐수처리장(90㎡)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q24" s="93" t="inlineStr">
+      <c r="Q24" s="26" t="inlineStr">
         <is>
           <t>1) 폐수 수집 관로 시방 및 내약품성 고밀도 PE관 및 내식성 이중배관 기준을 100% 충족하였는가?
 2) 유수분리기(API/CPI) 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R24" s="96">
+      <c r="R24" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\23_차량기지 오폐수처리장(90㎡)\체크리스트\23_차량기지 오폐수처리장(90㎡)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S24" s="89" t="inlineStr">
+      <c r="S24" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T24" s="93" t="inlineStr">
+      <c r="T24" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U24" s="87" t="inlineStr">
+      <c r="U24" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V24" s="93" t="inlineStr">
+      <c r="V24" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="97" t="inlineStr">
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B25" s="97" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C25" s="97" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D25" s="98" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>9000-8-24</t>
         </is>
       </c>
-      <c r="E25" s="101" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>9000-8-23</t>
         </is>
       </c>
-      <c r="F25" s="99" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>9000-8-25</t>
         </is>
       </c>
-      <c r="G25" s="100" t="inlineStr">
+      <c r="G25" s="17" t="inlineStr">
         <is>
           <t>차체 자동세척설비(세차기)</t>
         </is>
       </c>
-      <c r="H25" s="99" t="inlineStr">
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>D+20</t>
         </is>
       </c>
-      <c r="I25" s="101" t="inlineStr">
+      <c r="I25" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J25" s="102" t="inlineStr">
-        <is>
-          <t>동탄트램 차량의 청결 상태를 유지하기 위해 차량기지 청소선에 트램 전용 갠트리식 자동세척설비(차체 전·측·후면 브러시, 세제 분사 펌프, 린스 노즐, 윈드 블로워 송풍 건조기, 폐수 회수 집수 트렌치)를 시공하고, 열차 진입 감지 센서 연동 100% 자동 세척 시퀀스를 완성한다.</t>
-        </is>
-      </c>
-      <c r="K25" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 청소선 궤도 건축한계 대조 및 기초 앵커 시공, STEP 2: 세차기 메인 갠트리 프레임 및 브러시 조립 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L25" s="102" t="inlineStr">
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>트램 전동차 청소선 세차 갠트리, EVA 무스크래치 브러시 및 세척수 85% 회수 재활용</t>
+        </is>
+      </c>
+      <c r="K25" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (세차 갠트리 프레임 가설): 청소선 궤도 상부에 고압 노즐 파이프 및 갠트리 구조물 용접 앵커링
+2) STEP 2 (EVA 브러시 및 약품 분사): 전동차 차체 도장 손상을 방지하는 초미세 발포 EVA 브러시 및 중성 세제 분사 노즐 세팅
+3) STEP 3 (세척수 회수 트렌치 통수): 하부 STS 그레이팅 트렌치를 통해 세척수 85% 이상 회수 및 순환 정화조 인입 검측</t>
+        </is>
+      </c>
+      <c r="L25" s="17" t="inlineStr">
         <is>
           <t>차체 자동세척설비(세차기) 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M25" s="102" t="inlineStr">
+      <c r="M25" s="26" t="inlineStr">
         <is>
           <t>1) 차체 자동세척설비(세차기) (9000-8-24) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 청소선 대형 갠트리 세차기, 세제/린스 분사 노즐, 회전 브러시 및 폐수 회수 드레인을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N25" s="103">
+      <c r="N25" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\24_차체 자동세척설비(세차기)\표준서\24_차체 자동세척설비(세차기)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O25" s="102" t="inlineStr">
+      <c r="O25" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 청소선 궤도 건축한계 대조 및 기초 앵커 시공: 열차 통과 한계선 및 세차기 중심선 측량
 2) STEP 2: 세차기 메인 갠트리 프레임 및 브러시 조립: EVA 무스크래치 브러시 및 실린더 가설</t>
         </is>
       </c>
-      <c r="P25" s="104">
+      <c r="P25" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\24_차체 자동세척설비(세차기)\수행지침\24_차체 자동세척설비(세차기)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q25" s="102" t="inlineStr">
+      <c r="Q25" s="26" t="inlineStr">
         <is>
           <t>1) 세차기 프레임 시방 및 용융아연도금 및 STS304 내식성 갠트리 구조물 기준을 100% 충족하였는가?
 2) 회전 브러시 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R25" s="105">
+      <c r="R25" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\24_차체 자동세척설비(세차기)\체크리스트\24_차체 자동세척설비(세차기)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S25" s="101" t="inlineStr">
+      <c r="S25" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T25" s="102" t="inlineStr">
+      <c r="T25" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U25" s="97" t="inlineStr">
+      <c r="U25" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V25" s="102" t="inlineStr">
+      <c r="V25" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="87" t="inlineStr">
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B26" s="87" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C26" s="87" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D26" s="88" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>9000-8-25</t>
         </is>
       </c>
-      <c r="E26" s="89" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>9000-8-24</t>
         </is>
       </c>
-      <c r="F26" s="90" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>9000-8-26</t>
         </is>
       </c>
-      <c r="G26" s="91" t="inlineStr">
+      <c r="G26" s="17" t="inlineStr">
         <is>
           <t>정화조 음압 탈취설비 시공</t>
         </is>
       </c>
-      <c r="H26" s="90" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>D+25</t>
         </is>
       </c>
-      <c r="I26" s="89" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J26" s="92" t="inlineStr">
-        <is>
-          <t>차량기지 종합관리동 및 정거장 정화조 수조에서 발생하는 황화수소(H2S), 암모니아(NH3), 메탄(CH4) 등 유해·악취 가스가 지상 역사 및 근무 공간으로 확산되는 것을 원천 차단하기 위해, 정화조실 내부를 3종 음압으로 유지하는 내식성 FRP 탈취 덕트, 약액세정식 2단 탈취탑 및 복합가스 감지 센서를 시공한다.</t>
-        </is>
-      </c>
-      <c r="K26" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 정화조실 음압 환기량 및 유해가스 농도 계산, STEP 2: 내식성 FRP 탈취 덕트 및 배기팬 가설 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L26" s="93" t="inlineStr">
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>정화조실 3종 음압(-20Pa) 유지 및 2단 약액세정탑(산/알칼리)+첨착활성탄 복합 탈취</t>
+        </is>
+      </c>
+      <c r="K26" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (음압 덕트 및 후드 설치): 정화조 발생원 상부에 내식성 FRP 배기 후드 및 전용 음압 배기팬(15~20회/h) 가설
+2) STEP 2 (2단 스크러버 약액 세정): 산(H2SO4) 및 알칼리(NaOH) 세정탑 순환 펌프와 노즐을 통해 황화수소(H2S) 99% 중화
+3) STEP 3 (첨착 활성탄 흡착 배출): 최종 첨착 활성탄 흡착탑을 거쳐 복합악취 희석배수 ≤ 500 이하 기준 충족 확인</t>
+        </is>
+      </c>
+      <c r="L26" s="17" t="inlineStr">
         <is>
           <t>정화조 음압 탈취설비 시공 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M26" s="93" t="inlineStr">
+      <c r="M26" s="26" t="inlineStr">
         <is>
           <t>1) 정화조 음압 탈취설비 시공 (9000-8-25) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 정화조 관리층 유해/가연성 가스 배출용 약액세정식 탈취장치, 덕트 부압 및 가스센서을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N26" s="94">
+      <c r="N26" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\25_정화조 음압 탈취설비 시공\표준서\25_정화조 음압 탈취설비 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O26" s="93" t="inlineStr">
+      <c r="O26" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 정화조실 음압 환기량 및 유해가스 농도 계산: 시간당 20회 배기량 및 수조 포집 후드 설계
 2) STEP 2: 내식성 FRP 탈취 덕트 및 배기팬 가설: FRP 플랜지 체결 및 내화학 내식 송풍기</t>
         </is>
       </c>
-      <c r="P26" s="95">
+      <c r="P26" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\25_정화조 음압 탈취설비 시공\수행지침\25_정화조 음압 탈취설비 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q26" s="93" t="inlineStr">
+      <c r="Q26" s="26" t="inlineStr">
         <is>
           <t>1) 탈취탑 방식 시방 및 약액세정식(산/알칼리 세정) + 활성탄 2단 흡착 기준을 100% 충족하였는가?
 2) 탈취 배기덕트 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R26" s="96">
+      <c r="R26" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\25_정화조 음압 탈취설비 시공\체크리스트\25_정화조 음압 탈취설비 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S26" s="89" t="inlineStr">
+      <c r="S26" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T26" s="93" t="inlineStr">
+      <c r="T26" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U26" s="87" t="inlineStr">
+      <c r="U26" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V26" s="93" t="inlineStr">
+      <c r="V26" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="97" t="inlineStr">
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B27" s="97" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C27" s="97" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D27" s="98" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>9000-8-26</t>
         </is>
       </c>
-      <c r="E27" s="101" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>9000-8-25</t>
         </is>
       </c>
-      <c r="F27" s="99" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>9000-8-27</t>
         </is>
       </c>
-      <c r="G27" s="100" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>호스릴 옥내소화전설비 시공</t>
         </is>
       </c>
-      <c r="H27" s="99" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>D+30</t>
         </is>
       </c>
-      <c r="I27" s="101" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J27" s="102" t="inlineStr">
-        <is>
-          <t>화재안전기술기준(NFTC 102) 및 시방서 개선 사항에 따라 일반인이 혼자서도 손쉽게 당겨서 방수할 수 있는 고성능 '호스릴 옥내소화전(STS304 외함, 25mm 고무호스 릴, 분말소화기 3.3kg 2대 내장형)'을 정거장 및 차량기지 전 구역에 보행거리 25m 이내로 배치하고, 방수압력(0.17~0.7MPa) 및 방수량(130L/min)을 완벽 시공한다.</t>
-        </is>
-      </c>
-      <c r="K27" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 소화전함 설치 위치 먹매김 및 배관 인입선 실측, STEP 2: 배관 가설 및 그루브 조인트(Grooved Joint) 체결 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L27" s="102" t="inlineStr">
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>STS304 호스릴 옥내소화전(보행거리 25m 이내, 방수압 0.17~0.7MPa) 1인 조작 화재 진압</t>
+        </is>
+      </c>
+      <c r="K27" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (STS304 소화전함 매립): 정거장 및 역사 벽체에 STS304 방청 소화전함을 수직·수평 정밀 매립
+2) STEP 2 (25m 호스릴 및 밸브 체결): 1인 전개 인장력 5kgf 이하의 원형 회전 드럼식 25m 경량 호스릴 및 감압 앵글밸브 설치
+3) STEP 3 (방수압력 및 방수량 실측): 피토게이지를 이용하여 노즐 방수압 0.17~0.7MPa 및 방수량 ≥ 130L/min 20분간 방수 실측</t>
+        </is>
+      </c>
+      <c r="L27" s="17" t="inlineStr">
         <is>
           <t>호스릴 옥내소화전설비 시공 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M27" s="102" t="inlineStr">
+      <c r="M27" s="26" t="inlineStr">
         <is>
           <t>1) 호스릴 옥내소화전설비 시공 (9000-8-26) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) STS 호스릴 소화전(분말소화기 내장), 방수압(≥0.17MPa), 노출/매립 STS 외함 완벽 시공을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N27" s="103">
+      <c r="N27" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\26_호스릴 옥내소화전설비 시공\표준서\26_호스릴 옥내소화전설비 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O27" s="102" t="inlineStr">
+      <c r="O27" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 소화전함 설치 위치 먹매김 및 배관 인입선 실측: 보행거리 25m 이내 및 바닥고 1.5m 준수
 2) STEP 2: 배관 가설 및 그루브 조인트(Grooved Joint) 체결: 용접 없는 기계적 이음 및 지진방지 버팀대</t>
         </is>
       </c>
-      <c r="P27" s="104">
+      <c r="P27" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\26_호스릴 옥내소화전설비 시공\수행지침\26_호스릴 옥내소화전설비 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q27" s="102" t="inlineStr">
+      <c r="Q27" s="26" t="inlineStr">
         <is>
           <t>1) 소화전함 규격 시방 및 STS304 두께 1.5mm, 분말소화기 일체형 외함 기준을 100% 충족하였는가?
 2) 호스릴 릴 뭉치 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R27" s="105">
+      <c r="R27" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\26_호스릴 옥내소화전설비 시공\체크리스트\26_호스릴 옥내소화전설비 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S27" s="101" t="inlineStr">
+      <c r="S27" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T27" s="102" t="inlineStr">
+      <c r="T27" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U27" s="97" t="inlineStr">
+      <c r="U27" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V27" s="102" t="inlineStr">
+      <c r="V27" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="87" t="inlineStr">
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B28" s="87" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C28" s="87" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D28" s="88" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>9000-8-27</t>
         </is>
       </c>
-      <c r="E28" s="89" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>9000-8-26</t>
         </is>
       </c>
-      <c r="F28" s="90" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>9000-8-28</t>
         </is>
       </c>
-      <c r="G28" s="91" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>연결송수관-스프링클러 주배관 분리</t>
         </is>
       </c>
-      <c r="H28" s="90" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>D+35</t>
         </is>
       </c>
-      <c r="I28" s="89" t="inlineStr">
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J28" s="92" t="inlineStr">
-        <is>
-          <t>화재안전기술기준(NFTC 103, 502) 개정 법령에 따라 과거 겸용으로 시공되던 '연결송수관설비'와 '스프링클러설비'의 수직 주배관 및 옥외 소방차 연결 송수구를 물리적으로 각각 100% 완전 분리 시공하여, 화재 시 소방차 고압 가압에 따른 스프링클러 배관 파손을 막고 소화 수압 안정성을 극대화한다.</t>
-        </is>
-      </c>
-      <c r="K28" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 개정 화재안전기술기준 설계도서 대조 및 입상 경로 분리, STEP 2: 연결송수관 전용 고압 배관 시공 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L28" s="93" t="inlineStr">
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>개정 화재안전기준에 따른 연결송수관과 스프링클러설비의 주배관 및 옥외 송수구 완전 물리적 분리</t>
+        </is>
+      </c>
+      <c r="K28" s="33" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (독립 배관 라인 포설): 연결송수관(고압 Sch40)과 스프링클러 알람밸브 2차측 배관을 완전 독립 경로로 가설
+2) STEP 2 (쌍구형 송수구 분리 설치): 옥외 소방차 진입로에 연결송수관용 및 스프링클러용 쌍구형 송수구를 명판과 함께 분리 취부
+3) STEP 3 (2.0MPa 고압 내압시험): 소방차 직결 가압을 상정하여 2.0MPa 압력으로 30분간 내압시험을 실시해 관로 안전성 입증</t>
+        </is>
+      </c>
+      <c r="L28" s="17" t="inlineStr">
         <is>
           <t>연결송수관-스프링클러 주배관 분리 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M28" s="93" t="inlineStr">
+      <c r="M28" s="26" t="inlineStr">
         <is>
           <t>1) 연결송수관-스프링클러 주배관 분리 (9000-8-27) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 소방법 개정 기준 반영, 연결송수관설비와 스프링클러설비의 주배관 및 송수구 물리적 완전 분리을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N28" s="94">
+      <c r="N28" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\27_연결송수관-스프링클러 주배관 분리\표준서\27_연결송수관-스프링클러 주배관 분리_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O28" s="93" t="inlineStr">
+      <c r="O28" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 개정 화재안전기술기준 설계도서 대조 및 입상 경로 분리: 겸용 배관 여부 색출 및 독립 2열 배관 설계
 2) STEP 2: 연결송수관 전용 고압 배관 시공: 압력배관용 탄소강관(KSD 3562, Sch 40) 용접/그루브</t>
         </is>
       </c>
-      <c r="P28" s="95">
+      <c r="P28" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\27_연결송수관-스프링클러 주배관 분리\수행지침\27_연결송수관-스프링클러 주배관 분리_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q28" s="93" t="inlineStr">
+      <c r="Q28" s="26" t="inlineStr">
         <is>
           <t>1) 주배관 독립 관로 시방 및 연결송수관 전용 Sch40 배관 &amp; 스프링클러 전용 배관 기준을 100% 충족하였는가?
 2) 옥외 송수구 분리 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R28" s="96">
+      <c r="R28" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\27_연결송수관-스프링클러 주배관 분리\체크리스트\27_연결송수관-스프링클러 주배관 분리_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S28" s="89" t="inlineStr">
+      <c r="S28" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T28" s="93" t="inlineStr">
+      <c r="T28" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U28" s="87" t="inlineStr">
+      <c r="U28" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V28" s="93" t="inlineStr">
+      <c r="V28" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="97" t="inlineStr">
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B29" s="97" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C29" s="97" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D29" s="98" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>9000-8-28</t>
         </is>
       </c>
-      <c r="E29" s="101" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>9000-8-27</t>
         </is>
       </c>
-      <c r="F29" s="99" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>9000-8-29</t>
         </is>
       </c>
-      <c r="G29" s="100" t="inlineStr">
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>큐비클 가스계_에어로졸 소화</t>
         </is>
       </c>
-      <c r="H29" s="99" t="inlineStr">
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>D+40</t>
         </is>
       </c>
-      <c r="I29" s="101" t="inlineStr">
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J29" s="102" t="inlineStr">
-        <is>
-          <t>전기 스파크 및 과부하로 인한 전기화재 위험이 높은 차량기지 변전소, 트램 배터리 충전 전기실, 종합관리동 및 본선 31개소 정거장의 특고압/저압 수배전반 큐비클(Cubicle) 내부에 KFI 형식승인을 득한 소공간용 고체에어로졸 자동소화장치를 1:1 취부하여 판넬 내부 화재를 3초 이내에 국부 진압한다.</t>
-        </is>
-      </c>
-      <c r="K29" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 수배전반 큐비클 체적(㎥) 및 소화약제량 산정, STEP 2: 고체에어로졸 소화장치 브라켓 고정 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L29" s="102" t="inlineStr">
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>특고압/저압 수배전반 판넬 내부 KFI 인증 소공간 고체에어로졸 설치 및 3초 내 초기 진압</t>
+        </is>
+      </c>
+      <c r="K29" s="34" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (큐비클 내부 브래킷 고정): 수배전반 상단 발화 예상 지점에 내진 브래킷을 이용하여 에어로졸 소화장치 취부
+2) STEP 2 (열감지선 및 기폭선 결선): 105℃ 정온식 열감지선을 판넬 내부 주요 부스바 주변에 포설하고 제어부 결선
+3) STEP 3 (ACB 차단기 인터록 연동): 화재 감지 및 소화기 기폭 신호 출력 즉시 주차단기(ACB)가 자동 트립되는 인터록 검증</t>
+        </is>
+      </c>
+      <c r="L29" s="17" t="inlineStr">
         <is>
           <t>큐비클 가스계_에어로졸 소화 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M29" s="102" t="inlineStr">
+      <c r="M29" s="26" t="inlineStr">
         <is>
           <t>1) 큐비클 가스계_에어로졸 소화 (9000-8-28) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 변전소, 충전 전기실, 정거장 31개소 특고압/저압 배전반 내부 고체에어로졸 자동소화장치을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N29" s="103">
+      <c r="N29" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\28_큐비클 가스계_에어로졸 소화\표준서\28_큐비클 가스계_에어로졸 소화_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O29" s="102" t="inlineStr">
+      <c r="O29" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 수배전반 큐비클 체적(㎥) 및 소화약제량 산정: 판넬 내부 공간 체적 및 발열 부품 조사
 2) STEP 2: 고체에어로졸 소화장치 브라켓 고정: 판넬 천장부 내열 브라켓 볼트 체결</t>
         </is>
       </c>
-      <c r="P29" s="104">
+      <c r="P29" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\28_큐비클 가스계_에어로졸 소화\수행지침\28_큐비클 가스계_에어로졸 소화_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q29" s="102" t="inlineStr">
+      <c r="Q29" s="26" t="inlineStr">
         <is>
           <t>1) 에어로졸 소화기 시방 및 KFI 인증 소공간용 고체에어로졸 자동소화장치 기준을 100% 충족하였는가?
 2) 화재 감지 와이어 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R29" s="105">
+      <c r="R29" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\28_큐비클 가스계_에어로졸 소화\체크리스트\28_큐비클 가스계_에어로졸 소화_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S29" s="101" t="inlineStr">
+      <c r="S29" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T29" s="102" t="inlineStr">
+      <c r="T29" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U29" s="97" t="inlineStr">
+      <c r="U29" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V29" s="102" t="inlineStr">
+      <c r="V29" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="87" t="inlineStr">
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B30" s="87" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C30" s="87" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D30" s="88" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>9000-8-29</t>
         </is>
       </c>
-      <c r="E30" s="89" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>9000-8-28</t>
         </is>
       </c>
-      <c r="F30" s="90" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>9000-8-30</t>
         </is>
       </c>
-      <c r="G30" s="91" t="inlineStr">
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>가스소화구역 과압배출구(P.R.D)</t>
         </is>
       </c>
-      <c r="H30" s="90" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>D+45</t>
         </is>
       </c>
-      <c r="I30" s="89" t="inlineStr">
+      <c r="I30" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J30" s="92" t="inlineStr">
-        <is>
-          <t>차량기지 주변전소, 정거장 변전실 등 가스계 소화설비(HFC-125, Novec 1230 등)가 적용된 밀폐 방호구역에 소화가스 방출 시 순간적인 압력 상승으로 인한 방화벽체, 출입문 및 유리창의 파손을 방지하기 위하여, 설정 압력(150~300Pa) 이상에서 자동으로 개방되는 과압배출구(P.R.D, Pressure Relief Damper)를 벽체에 완벽 가설한다.</t>
-        </is>
-      </c>
-      <c r="K30" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 가스 방출 압력 상승치 및 P.R.D 배출 면적 계산, STEP 2: 방화벽체 개구부 타공 및 STS 프레임 가설 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L30" s="93" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>가스소화약제 방출 시 실내 과압(200Pa) 자동 해소 및 자중 폐쇄를 통한 10분 설계농도 유지</t>
+        </is>
+      </c>
+      <c r="K30" s="35" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (방화벽체 개구부 프레임 취부): 변전실 외벽 또는 복도측 방화벽체에 P.R.D 댐퍼 프레임 수평 매립 고정
+2) STEP 2 (카운터웨이트 개방압 세팅): 실내 압력이 200Pa에 도달할 때 블레이드가 정확히 열리도록 카운터웨이트 추 정밀 교정
+3) STEP 3 (자중 폐쇄 및 기밀도 검측): 압력 해소 후 중력으로 완벽히 닫혀 소화가스 누출(약제 설계농도 10분 유지) 방지 검증</t>
+        </is>
+      </c>
+      <c r="L30" s="17" t="inlineStr">
         <is>
           <t>가스소화구역 과압배출구(P.R.D) 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M30" s="93" t="inlineStr">
+      <c r="M30" s="26" t="inlineStr">
         <is>
           <t>1) 가스소화구역 과압배출구(P.R.D) (9000-8-29) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 변전소 가스소화약제 방출 시 방화벽체 풍압 파손 방지용 P.R.D(과압배출) 댐퍼 규격 시공을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N30" s="94">
+      <c r="N30" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\29_가스소화구역 과압배출구(P.R.D)\표준서\29_가스소화구역 과압배출구(P.R.D)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O30" s="93" t="inlineStr">
+      <c r="O30" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 가스 방출 압력 상승치 및 P.R.D 배출 면적 계산: NFPA 2001 및 소방 시방 계산 공식 검토
 2) STEP 2: 방화벽체 개구부 타공 및 STS 프레임 가설: 건축 개구부 치수 대조 및 방화 슬리브 시공</t>
         </is>
       </c>
-      <c r="P30" s="95">
+      <c r="P30" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\29_가스소화구역 과압배출구(P.R.D)\수행지침\29_가스소화구역 과압배출구(P.R.D)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q30" s="93" t="inlineStr">
+      <c r="Q30" s="26" t="inlineStr">
         <is>
           <t>1) P.R.D 댐퍼 면적 시방 및 소화약제 방출량 대비 과압배출 면적(㎡) 계산서 기준을 100% 충족하였는가?
 2) 블레이드 밸런싱 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R30" s="96">
+      <c r="R30" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\29_가스소화구역 과압배출구(P.R.D)\체크리스트\29_가스소화구역 과압배출구(P.R.D)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S30" s="89" t="inlineStr">
+      <c r="S30" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T30" s="93" t="inlineStr">
+      <c r="T30" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U30" s="87" t="inlineStr">
+      <c r="U30" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V30" s="93" t="inlineStr">
+      <c r="V30" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="97" t="inlineStr">
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B31" s="97" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C31" s="97" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D31" s="98" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>9000-8-30</t>
         </is>
       </c>
-      <c r="E31" s="101" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>9000-8-29</t>
         </is>
       </c>
-      <c r="F31" s="99" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>9000-8-31</t>
         </is>
       </c>
-      <c r="G31" s="100" t="inlineStr">
+      <c r="G31" s="17" t="inlineStr">
         <is>
           <t>소방펌프실 가설 및 성능시험</t>
         </is>
       </c>
-      <c r="H31" s="99" t="inlineStr">
+      <c r="H31" s="17" t="inlineStr">
         <is>
           <t>D+50</t>
         </is>
       </c>
-      <c r="I31" s="101" t="inlineStr">
+      <c r="I31" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J31" s="102" t="inlineStr">
-        <is>
-          <t>화재안전기술기준(NFTC 102, 103)에 따라 정거장 및 차량기지 지하 소방펌프실에 주펌프(전기모터 구동), 보조 충압펌프, 성능시험배관, 압력챔버(또는 전자식 압력스위치), 순환배관 및 릴리프밸브를 가설하고, 3대 필수 성능시험(체절운전 시험, 정격부하 시험, 150% 최대부하 시험)을 완벽 수행한다.</t>
-        </is>
-      </c>
-      <c r="K31" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 소방펌프 콘크리트 기초 패드 및 방진가대 시공, STEP 2: 흡입·토출 배관, 플렉시블 조인트 및 밸브류 체결 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L31" s="102" t="inlineStr">
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>소방펌프실 주/충압펌프 거치 및 체절압력(≤140%), 정격(100%), 150% 부하(≥65%) 법정 성능시험</t>
+        </is>
+      </c>
+      <c r="K31" s="35" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (펌프 기초 및 방진가설): 콘크리트 패드 위에 다단원심 소방 주펌프 및 충압펌프 방진마운트 거치 및 축정렬
+2) STEP 2 (성능시험 배관 및 유량계): 주배관에서 분기된 오리피스 차압식 유량계 배관 및 순환배관 릴리프밸브 설치
+3) STEP 3 (3대 법정 성능시험 입회): 감리원 입회 하에 체절운전(정격 140% 이하), 100% 정격부하, 150% 피크부하 곡선 검증</t>
+        </is>
+      </c>
+      <c r="L31" s="17" t="inlineStr">
         <is>
           <t>소방펌프실 가설 및 성능시험 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M31" s="102" t="inlineStr">
+      <c r="M31" s="26" t="inlineStr">
         <is>
           <t>1) 소방펌프실 가설 및 성능시험 (9000-8-30) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 소방 주펌프(100%), 충압펌프, 체절압력(≤140%), 150% 유량 성능시험배관 및 릴리프밸브을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N31" s="103">
+      <c r="N31" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\30_소방펌프실 가설 및 성능시험\표준서\30_소방펌프실 가설 및 성능시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O31" s="102" t="inlineStr">
+      <c r="O31" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 소방펌프 콘크리트 기초 패드 및 방진가대 시공: 방진스프링 마운트 거치 및 축정렬(Alignment)
 2) STEP 2: 흡입·토출 배관, 플렉시블 조인트 및 밸브류 체결: 편심 레듀샤, 버터플라이 밸브(OS&amp;Y), 스트레이너</t>
         </is>
       </c>
-      <c r="P31" s="104">
+      <c r="P31" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\30_소방펌프실 가설 및 성능시험\수행지침\30_소방펌프실 가설 및 성능시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q31" s="102" t="inlineStr">
+      <c r="Q31" s="26" t="inlineStr">
         <is>
           <t>1) 소방 주펌프 시방 및 다단 원심펌프(정격유량/양정 시방 부합, IE3 모터) 기준을 100% 충족하였는가?
 2) 성능시험배관 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R31" s="105">
+      <c r="R31" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\30_소방펌프실 가설 및 성능시험\체크리스트\30_소방펌프실 가설 및 성능시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S31" s="101" t="inlineStr">
+      <c r="S31" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T31" s="102" t="inlineStr">
+      <c r="T31" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U31" s="97" t="inlineStr">
+      <c r="U31" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V31" s="102" t="inlineStr">
+      <c r="V31" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="87" t="inlineStr">
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B32" s="87" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C32" s="87" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D32" s="88" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>9000-8-31</t>
         </is>
       </c>
-      <c r="E32" s="89" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>9000-8-30</t>
         </is>
       </c>
-      <c r="F32" s="90" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>9000-8-32</t>
         </is>
       </c>
-      <c r="G32" s="91" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>정거장 인승용 승강기(17_24인승)</t>
         </is>
       </c>
-      <c r="H32" s="90" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>D+55</t>
         </is>
       </c>
-      <c r="I32" s="89" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J32" s="92" t="inlineStr">
-        <is>
-          <t>교통약자의 수직 이동권 및 환승 편의를 보장하기 위해 정거장 외부 환승 동선에 17인승/24인승 MRL(기계실 없는) 인승용 엘리베이터를 설치하고, 승강로 수직도(±5mm), 가이드레일 브라켓, 도어 다점 적외선 안전센서, 비상통화장치 및 한국승강기안전공단 완성검사를 100% 합격 완료한다.</t>
-        </is>
-      </c>
-      <c r="K32" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 승강로 골조 치수, 피트 깊이 및 수직도 실측, STEP 2: 가이드레일 브라켓 및 T형 레일 조립 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L32" s="93" t="inlineStr">
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>정거장 MRL(기계실 없는) 인승용 승강기 설치 및 KoELSA 완성검사 필증 획득</t>
+        </is>
+      </c>
+      <c r="K32" s="35" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (승강로 수직도 및 레일 조립): 승강로 수직도(오차 ≤ ±5mm) 실측 후 13K 가이드레일 브래킷 앵커링 및 조립
+2) STEP 2 (PMSM 권상기 및 카 조립): PMSM 영구자석 기어리스 권상기 안착, 메인로프(안전율 ≥ 12) 텐션 조정 및 카 조립
+3) STEP 3 (KoELSA 법정 완성검사): 128채널 3D 도어센서, 정전 시 ARD 구출장치, 조속기 비상정지장치 실부하 시험 100% 합격</t>
+        </is>
+      </c>
+      <c r="L32" s="17" t="inlineStr">
         <is>
           <t>정거장 인승용 승강기(17_24인승) 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M32" s="93" t="inlineStr">
+      <c r="M32" s="26" t="inlineStr">
         <is>
           <t>1) 정거장 인승용 승강기(17_24인승) (9000-8-31) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 승강로 수직도(±5mm), 도어 다점 안전센서, 비상통화장치 및 한국승강기안전공단(KoELSA) 검사을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N32" s="94">
+      <c r="N32" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\31_정거장 인승용 승강기(17_24인승)\표준서\31_정거장 인승용 승강기(17_24인승)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O32" s="93" t="inlineStr">
+      <c r="O32" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 승강로 골조 치수, 피트 깊이 및 수직도 실측: 레이저 수직 측정기를 이용한 오차 검측
 2) STEP 2: 가이드레일 브라켓 및 T형 레일 조립: 레일 브라켓 앵커링 및 조인트 플레이트 체결</t>
         </is>
       </c>
-      <c r="P32" s="95">
+      <c r="P32" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\31_정거장 인승용 승강기(17_24인승)\수행지침\31_정거장 인승용 승강기(17_24인승)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q32" s="93" t="inlineStr">
+      <c r="Q32" s="26" t="inlineStr">
         <is>
           <t>1) MRL 권상기 시방 및 영구자석 동기전동기(PMSM) 기어리스 권상기 기준을 100% 충족하였는가?
 2) 가이드 레일 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R32" s="96">
+      <c r="R32" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\31_정거장 인승용 승강기(17_24인승)\체크리스트\31_정거장 인승용 승강기(17_24인승)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S32" s="89" t="inlineStr">
+      <c r="S32" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T32" s="93" t="inlineStr">
+      <c r="T32" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U32" s="87" t="inlineStr">
+      <c r="U32" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V32" s="93" t="inlineStr">
+      <c r="V32" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="97" t="inlineStr">
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B33" s="97" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C33" s="97" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D33" s="98" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>9000-8-32</t>
         </is>
       </c>
-      <c r="E33" s="101" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>9000-8-31</t>
         </is>
       </c>
-      <c r="F33" s="99" t="inlineStr">
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>9000-8-33</t>
         </is>
       </c>
-      <c r="G33" s="100" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>검수고 관통형 화물용 EV</t>
         </is>
       </c>
-      <c r="H33" s="99" t="inlineStr">
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>D+60</t>
         </is>
       </c>
-      <c r="I33" s="101" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J33" s="102" t="inlineStr">
-        <is>
-          <t>차량기지 종합검수고동 내 무거운 트램 부품, 대차 예비품 및 정비 공구의 층간 수직 이동을 전담하기 위해 3~5ton급 대용량 '관통형(양방향 도어 개폐형) 화물용 엘리베이터'를 설치하고, 지게차 진입 충격에 견디는 바닥 하중 보강, 도어 씰(Sill) 보강 및 화물 전용 안전장치를 완벽 시공한다.</t>
-        </is>
-      </c>
-      <c r="K33" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 대형 화물용 승강로 구조 및 지게차 동선 검토, STEP 2: 대형 H형강 카 프레임 및 중량 레일 가설 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L33" s="102" t="inlineStr">
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>차량기지 종합검수고 관통형(양방향 도어) 3~5ton 화물용 승강기 가설 및 지게차 진입 바닥 보강</t>
+        </is>
+      </c>
+      <c r="K33" s="35" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (중하중 승강로 구조 보강): 지게차(자중 4.5ton) 진입 하중을 견디도록 카 바닥 H형강 및 4.5T 체크플레이트 보강
+2) STEP 2 (관통형 양방향 도어 인터록): 1층 전면 도어와 2층 후면 도어가 동시 개방되지 않도록 안전 인터록 릴레이 구축
+3) STEP 3 (125% 과부하 하중시험): 정격 적재하중의 125%(6.25ton) 추를 탑재하여 권상 제동력 및 슬립 유무 정밀 안전검사</t>
+        </is>
+      </c>
+      <c r="L33" s="17" t="inlineStr">
         <is>
           <t>검수고 관통형 화물용 EV 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M33" s="102" t="inlineStr">
+      <c r="M33" s="26" t="inlineStr">
         <is>
           <t>1) 검수고 관통형 화물용 EV (9000-8-32) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 차량기지 종합검수고 대형 중정비 자재 운반용 관통형(앞뒤 개폐) 화물 EV, 바닥 하중보강을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N33" s="103">
+      <c r="N33" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\32_검수고 관통형 화물용 EV\표준서\32_검수고 관통형 화물용 EV_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O33" s="102" t="inlineStr">
+      <c r="O33" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 대형 화물용 승강로 구조 및 지게차 동선 검토: 카 내부 치수(W2.5m x D3.5m 이상) 및 하중 대조
 2) STEP 2: 대형 H형강 카 프레임 및 중량 레일 가설: T형 중량 가이드레일(24K/30K) 및 브라켓 체결</t>
         </is>
       </c>
-      <c r="P33" s="104">
+      <c r="P33" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\32_검수고 관통형 화물용 EV\수행지침\32_검수고 관통형 화물용 EV_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q33" s="102" t="inlineStr">
+      <c r="Q33" s="26" t="inlineStr">
         <is>
           <t>1) 화물 적재 용량 시방 및 정격 적재 하중 3,000kg ~ 5,000kg 대형 카 기준을 100% 충족하였는가?
 2) 관통형 도어(Through) 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R33" s="105">
+      <c r="R33" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\32_검수고 관통형 화물용 EV\체크리스트\32_검수고 관통형 화물용 EV_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S33" s="101" t="inlineStr">
+      <c r="S33" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T33" s="102" t="inlineStr">
+      <c r="T33" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U33" s="97" t="inlineStr">
+      <c r="U33" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V33" s="102" t="inlineStr">
+      <c r="V33" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="87" t="inlineStr">
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B34" s="87" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C34" s="87" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D34" s="88" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>9000-8-33</t>
         </is>
       </c>
-      <c r="E34" s="89" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>9000-8-32</t>
         </is>
       </c>
-      <c r="F34" s="90" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>9000-8-34</t>
         </is>
       </c>
-      <c r="G34" s="91" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>DDC_IP DDC 자동제어 백업 이중화</t>
         </is>
       </c>
-      <c r="H34" s="90" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>D+65</t>
         </is>
       </c>
-      <c r="I34" s="89" t="inlineStr">
+      <c r="I34" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J34" s="92" t="inlineStr">
-        <is>
-          <t>정거장 및 차량기지 내 모든 기계설비(공조기, 환기팬, 펌프, 댐퍼, 밸브, 저수조, 전력계)의 실시간 원격 감시 및 에너지 최적 제어를 위해 직접디지털제어(DDC/IP DDC) 패널을 가설하고, 개방형 BACnet/Modbus 프로토콜 적용 및 메인 서버 장애 시 0초 무중단 자동 절환되는 Backup Server 이중화 시스템을 완벽 구축한다.</t>
-        </is>
-      </c>
-      <c r="K34" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 자동제어 I/O 포인트 일람표 및 통신 선로 설계 대조, STEP 2: 기계실 IP DDC 패널 가설 및 필드 센서/밸브 배선 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L34" s="93" t="inlineStr">
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>기계설비 직접디지털제어(IP DDC) 판넬 설치, BACnet 국제표준 통신 및 관제서버 무중단 이중화</t>
+        </is>
+      </c>
+      <c r="K34" s="35" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (IP DDC 필드 제어반 결선): 기계실 및 공조실 DDC 판넬에 아날로그(AI/AO), 디지털(DI/DO) 센서·밸브 케이블 결선
+2) STEP 2 (BACnet 통신 루프 구축): 개방형 BACnet/IP 프로토콜을 적용하여 중앙 방재실 관제 컴퓨터와 실시간 데이터 통신 연동
+3) STEP 3 (서버 0초 이중화 절환 시험): 메인 관제 서버 강제 다운 시 대기 중인 백업 서버로 데이터 손실 없이 0초 절환 검증</t>
+        </is>
+      </c>
+      <c r="L34" s="17" t="inlineStr">
         <is>
           <t>DDC_IP DDC 자동제어 백업 이중화 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M34" s="93" t="inlineStr">
+      <c r="M34" s="26" t="inlineStr">
         <is>
           <t>1) DDC_IP DDC 자동제어 백업 이중화 (9000-8-33) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 원격 관제 DDC 패널, BACnet 표준 통신, 메인/백업 중앙 감시 서버 무중단 절환 체계을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N34" s="94">
+      <c r="N34" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\33_DDC_IP DDC 자동제어 백업 이중화\표준서\33_DDC_IP DDC 자동제어 백업 이중화_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O34" s="93" t="inlineStr">
+      <c r="O34" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 자동제어 I/O 포인트 일람표 및 통신 선로 설계 대조: 수천 개 감시/제어 포인트 1:1 매핑
 2) STEP 2: 기계실 IP DDC 패널 가설 및 필드 센서/밸브 배선: 온습도센서, 차압스위치, 비례제어밸브 결선</t>
         </is>
       </c>
-      <c r="P34" s="95">
+      <c r="P34" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\33_DDC_IP DDC 자동제어 백업 이중화\수행지침\33_DDC_IP DDC 자동제어 백업 이중화_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q34" s="93" t="inlineStr">
+      <c r="Q34" s="26" t="inlineStr">
         <is>
           <t>1) IP DDC 제어반 시방 및 32비트 고성능 마이크로프로세서 DDC 패널 기준을 100% 충족하였는가?
 2) 개방형 프로토콜 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R34" s="96">
+      <c r="R34" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\33_DDC_IP DDC 자동제어 백업 이중화\체크리스트\33_DDC_IP DDC 자동제어 백업 이중화_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S34" s="89" t="inlineStr">
+      <c r="S34" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T34" s="93" t="inlineStr">
+      <c r="T34" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U34" s="87" t="inlineStr">
+      <c r="U34" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V34" s="93" t="inlineStr">
+      <c r="V34" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="97" t="inlineStr">
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B35" s="97" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C35" s="97" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D35" s="98" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>9000-8-34</t>
         </is>
       </c>
-      <c r="E35" s="101" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>9000-8-33</t>
         </is>
       </c>
-      <c r="F35" s="99" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>9000-8-35</t>
         </is>
       </c>
-      <c r="G35" s="100" t="inlineStr">
+      <c r="G35" s="17" t="inlineStr">
         <is>
           <t>화재연동 인터록 실부하 시험</t>
         </is>
       </c>
-      <c r="H35" s="99" t="inlineStr">
+      <c r="H35" s="17" t="inlineStr">
         <is>
           <t>D+70</t>
         </is>
       </c>
-      <c r="I35" s="101" t="inlineStr">
+      <c r="I35" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J35" s="102" t="inlineStr">
-        <is>
-          <t>화재안전기술기준 및 철도 방재 매뉴얼에 따라 화재 발생 시 연기가 공조 덕트를 타고 다른 구역으로 확산되는 대형 참사를 막기 위해, 화재수신반 경보 발생 즉시 공조기·냉난방기 마그네틱 전원을 100% 강제 차단하고, 해당 제연구역의 제연팬을 비상 배연 모드로 가동하는 방재 인터록 실부하 시험을 수행한다.</t>
-        </is>
-      </c>
-      <c r="K35" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 화재 연동 방재 매트릭스(Cause &amp; Effect) 수립, STEP 2: 공조기 MCC 정지 접점 및 제연팬 기동 결선 점검 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L35" s="102" t="inlineStr">
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>화재 수신반 신호 수신 즉시 공조기 100% 강제 정지 및 제연팬 배연 모드 자동 인터록</t>
+        </is>
+      </c>
+      <c r="K35" s="35" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (하드와이어드 인터록 회로 구성): 화재수신반 경보 접점을 공조기 MCC 조작전원 차단 계전기(B접점)와 직결
+2) STEP 2 (제연댐퍼 및 팬 시퀀스 연동): 화재 구역 제연 풍도 댐퍼가 완전 개방된 후 리미트 스위치 신호로 제연팬 자동 가동
+3) STEP 3 (실부하 화재 모의시험): 연기감지기 실발화 시험을 실시하여 3초 이내 공조기 정지 및 제연팬 정상 기동 확인</t>
+        </is>
+      </c>
+      <c r="L35" s="17" t="inlineStr">
         <is>
           <t>화재연동 인터록 실부하 시험 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M35" s="102" t="inlineStr">
+      <c r="M35" s="26" t="inlineStr">
         <is>
           <t>1) 화재연동 인터록 실부하 시험 (9000-8-34) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 화재수신반 경보 시 공조기 즉시 정지, 제연팬 배연 모드 자동 전환 및 방화댐퍼 연동을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N35" s="103">
+      <c r="N35" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\34_화재연동 인터록 실부하 시험\표준서\34_화재연동 인터록 실부하 시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O35" s="102" t="inlineStr">
+      <c r="O35" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 화재 연동 방재 매트릭스(Cause &amp; Effect) 수립: 구역별 화재 시나리오 및 인터록 시퀀스 확정
 2) STEP 2: 공조기 MCC 정지 접점 및 제연팬 기동 결선 점검: 하드와이어드(Hardwired) 안전 인터록 확인</t>
         </is>
       </c>
-      <c r="P35" s="104">
+      <c r="P35" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\34_화재연동 인터록 실부하 시험\수행지침\34_화재연동 인터록 실부하 시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q35" s="102" t="inlineStr">
+      <c r="Q35" s="26" t="inlineStr">
         <is>
           <t>1) 화재 감지기 연동 시방 및 광전식 연기감지기/차동식 열감지기 화재 신호 기준을 100% 충족하였는가?
 2) 공조기 전원 차단 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R35" s="105">
+      <c r="R35" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\34_화재연동 인터록 실부하 시험\체크리스트\34_화재연동 인터록 실부하 시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S35" s="101" t="inlineStr">
+      <c r="S35" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T35" s="102" t="inlineStr">
+      <c r="T35" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U35" s="97" t="inlineStr">
+      <c r="U35" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V35" s="102" t="inlineStr">
+      <c r="V35" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="87" t="inlineStr">
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B36" s="87" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C36" s="87" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D36" s="88" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>9000-8-35</t>
         </is>
       </c>
-      <c r="E36" s="89" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>9000-8-34</t>
         </is>
       </c>
-      <c r="F36" s="90" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>9000-8-36</t>
         </is>
       </c>
-      <c r="G36" s="91" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr">
         <is>
           <t>TAB(풍량_수량 밸런싱) 측정</t>
         </is>
       </c>
-      <c r="H36" s="90" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>D+75</t>
         </is>
       </c>
-      <c r="I36" s="89" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J36" s="92" t="inlineStr">
-        <is>
-          <t>공조 및 배관 시스템의 완성도를 입증하고 실내 쾌적 환경과 에너지를 최적화하기 위해, 국가공인 TAB(Testing, Adjusting, Balancing) 전문기관에 의뢰하여 정거장 및 차량기지 전 구역의 공조 덕트 풍량, 디퓨저 취출 기류, 냉온수 배관 유량 및 실내 소음·차압을 정밀 측정하고 설계치 대비 오차 ±10% 이내로 균일 밸런싱한다.</t>
-        </is>
-      </c>
-      <c r="K36" s="93" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: TAB 사전 검토 및 측정 계획서 수립, STEP 2: 공조 덕트 주풍량 및 디퓨저 풍량 측정·조정 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L36" s="93" t="inlineStr">
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>공조 덕트 풍량(오차 ±10% 이내) 및 수배관 유량 정밀 측정·조정(TAB)으로 쾌적성 확보</t>
+        </is>
+      </c>
+      <c r="K36" s="35" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (공조 덕트 풍량 TAB): 피토관 및 플로우 후드를 이용하여 주덕트와 각 디퓨저 취출 풍량을 설계치 ±10%로 교정
+2) STEP 2 (수배관 유량 TAB): 초음파 비파괴 유량계로 냉온수 배관 순환 유량을 측정하고 밸런싱 밸브 차압(ΔP) 정밀 조정
+3) STEP 3 (소음 및 온습도 검증): 정거장 실내 소음(NC 35~40) 및 실별 온·습도 분포도를 24시간 연속 측정하여 TAB 성적서 발급</t>
+        </is>
+      </c>
+      <c r="L36" s="17" t="inlineStr">
         <is>
           <t>TAB(풍량_수량 밸런싱) 측정 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M36" s="93" t="inlineStr">
+      <c r="M36" s="26" t="inlineStr">
         <is>
           <t>1) TAB(풍량_수량 밸런싱) 측정 (9000-8-35) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 실별 설계 풍량/수량 정밀 측정, 디퓨저 풍량비 ±10% 및 밸런싱 밸브 오차 조정을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N36" s="94">
+      <c r="N36" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\35_TAB(풍량_수량 밸런싱) 측정\표준서\35_TAB(풍량_수량 밸런싱) 측정_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O36" s="93" t="inlineStr">
+      <c r="O36" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: TAB 사전 검토 및 측정 계획서 수립: 설계 도면, 장비 사양서, 계통도 사전 분석
 2) STEP 2: 공조 덕트 주풍량 및 디퓨저 풍량 측정·조정: 피토관 및 플로우 후드를 이용한 비례조정</t>
         </is>
       </c>
-      <c r="P36" s="95">
+      <c r="P36" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\35_TAB(풍량_수량 밸런싱) 측정\수행지침\35_TAB(풍량_수량 밸런싱) 측정_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q36" s="93" t="inlineStr">
+      <c r="Q36" s="26" t="inlineStr">
         <is>
           <t>1) 덕트 풍량 밸런싱 시방 및 주덕트 피토관 다점 측정 및 볼륨댐퍼(VD) 조정 기준을 100% 충족하였는가?
 2) 디퓨저 취출 풍량 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R36" s="96">
+      <c r="R36" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\35_TAB(풍량_수량 밸런싱) 측정\체크리스트\35_TAB(풍량_수량 밸런싱) 측정_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S36" s="89" t="inlineStr">
+      <c r="S36" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T36" s="93" t="inlineStr">
+      <c r="T36" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U36" s="87" t="inlineStr">
+      <c r="U36" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V36" s="93" t="inlineStr">
+      <c r="V36" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="97" t="inlineStr">
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="B37" s="97" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>9000-8</t>
         </is>
       </c>
-      <c r="C37" s="97" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>기계설비·소방설비</t>
         </is>
       </c>
-      <c r="D37" s="98" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>9000-8-36</t>
         </is>
       </c>
-      <c r="E37" s="101" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>9000-8-35</t>
         </is>
       </c>
-      <c r="F37" s="99" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="100" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>소방 완공검사 및 종합인계</t>
         </is>
       </c>
-      <c r="H37" s="99" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>D+80</t>
         </is>
       </c>
-      <c r="I37" s="101" t="inlineStr">
+      <c r="I37" s="17" t="inlineStr">
         <is>
           <t>기계/소방팀</t>
         </is>
       </c>
-      <c r="J37" s="102" t="inlineStr">
-        <is>
-          <t>동탄트램 기계설비 및 소방공사의 최종 마무리를 위해 관할 소방서(화성소방서 등)의 엄격한 현장 실사를 통해 '소방시설 완공검사증명서(소방필증)'를 획득하고, 준공도면(As-Built), 장비 매뉴얼, 예비품 목록, 종합시운전 성적서를 완비하여 화성도시공사 기계·소방 운영유지관리팀에 무결점 종합 인수인계를 완료한다.</t>
-        </is>
-      </c>
-      <c r="K37" s="102" t="inlineStr">
-        <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 소방시설 완공검사 신청서 제출 및 사전 자체 점검, STEP 2: 관할 소방서 합동 현장 실사 및 성능 시연 절차서 준수 시공</t>
-        </is>
-      </c>
-      <c r="L37" s="102" t="inlineStr">
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>관할 소방서 완공검사필증 획득, As-Built 준공도서 편찬 및 운영사(화성도시공사) 무결점 인수인계</t>
+        </is>
+      </c>
+      <c r="K37" s="35" t="inlineStr">
+        <is>
+          <t>1) STEP 1 (관할 소방서 완공 실사): 소방감리원 및 소방관 합동 현장 실사를 통해 소화·경보·피난설비 전수 작동 검사
+2) STEP 2 (소방완공검사필증 수령): 지적사항 0건으로 소방시설 완공검사증명서(필증)를 정식 교부받아 법적 준공 완료
+3) STEP 3 (준공도서 및 운영자 교육): 3D As-Built 준공도면, 시운전 성적서, 2년분 예비품을 인계하고 운영팀 40시간 기술교육 이수</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="inlineStr">
         <is>
           <t>소방 완공검사 및 종합인계 시공계획서, 검측요청서 및 공인 시험성적서</t>
         </is>
       </c>
-      <c r="M37" s="102" t="inlineStr">
+      <c r="M37" s="26" t="inlineStr">
         <is>
           <t>1) 소방 완공검사 및 종합인계 (9000-8-36) 과업 달성을 위해 KDS 47 철도설계기준 및 NFTC 화재안전기준을 100% 충족한다.
 2) 관할 소방서 현장 실사 완공필증 획득, 시운전 성적서 및 기계/소방 시설물 종합 인수인계을 엄격히 완수하여 책임감리원 최종 승인을 획득한다.</t>
         </is>
       </c>
-      <c r="N37" s="103">
+      <c r="N37" s="75">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\36_소방 완공검사 및 종합인계\표준서\36_소방 완공검사 및 종합인계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
-      <c r="O37" s="102" t="inlineStr">
+      <c r="O37" s="26" t="inlineStr">
         <is>
           <t>1) STEP 1: 소방시설 완공검사 신청서 제출 및 사전 자체 점검: 모든 소방 설비 100% 작동 사전 리허설
 2) STEP 2: 관할 소방서 합동 현장 실사 및 성능 시연: 소방관 입회 옥내소화전 방수 및 제연 시험</t>
         </is>
       </c>
-      <c r="P37" s="104">
+      <c r="P37" s="76">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\36_소방 완공검사 및 종합인계\수행지침\36_소방 완공검사 및 종합인계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
-      <c r="Q37" s="102" t="inlineStr">
+      <c r="Q37" s="26" t="inlineStr">
         <is>
           <t>1) 소방 완공검사 시방 및 관할 소방서 공무원 입회 현장 실사 및 성능 시험 기준을 100% 충족하였는가?
 2) 준공도서(As-Built) 검측 및 불합격 요소를 전면 차단하였는가?</t>
         </is>
       </c>
-      <c r="R37" s="105">
+      <c r="R37" s="77">
         <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"10.기계분야\36_소방 완공검사 및 종합인계\체크리스트\36_소방 완공검사 및 종합인계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
-      <c r="S37" s="101" t="inlineStr">
+      <c r="S37" s="22" t="inlineStr">
         <is>
           <t>기계·소방 복합 시방 준수</t>
         </is>
       </c>
-      <c r="T37" s="102" t="inlineStr">
+      <c r="T37" s="74" t="inlineStr">
         <is>
           <t>● KDS 47 철도설계기준, KCS 41 건축기계시방 및 NFTC/NFPC 화재안전기술기준 100% 준수</t>
         </is>
       </c>
-      <c r="U37" s="97" t="inlineStr">
+      <c r="U37" s="73" t="inlineStr">
         <is>
           <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
-      <c r="V37" s="102" t="inlineStr">
+      <c r="V37" s="25" t="inlineStr">
         <is>
           <t>기계설비·소방 전문 감리 및 시공 기술자문단 상시 운영</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
+    <row r="38" ht="19.2" customHeight="1"/>
+    <row r="39" ht="19.2" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="8" verticalDpi="0"/>
+  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="35" verticalDpi="0"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="19" min="0" max="1048575" man="1"/>
+  </colBreaks>
 </worksheet>
 </file>
 
@@ -8814,8 +8756,8 @@
     <col width="45" customWidth="1" style="54" min="21" max="21"/>
     <col width="22" customWidth="1" style="54" min="22" max="22"/>
     <col width="22" customWidth="1" style="42" min="23" max="38"/>
-    <col width="8.796875" customWidth="1" style="42" min="39" max="74"/>
-    <col width="8.796875" customWidth="1" style="42" min="75" max="16384"/>
+    <col width="8.796875" customWidth="1" style="42" min="39" max="75"/>
+    <col width="8.796875" customWidth="1" style="42" min="76" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="46.8" customHeight="1">
@@ -12220,8 +12162,8 @@
     <col width="45" customWidth="1" style="54" min="20" max="20"/>
     <col width="22" customWidth="1" style="54" min="21" max="21"/>
     <col width="22" customWidth="1" style="42" min="22" max="37"/>
-    <col width="8.796875" customWidth="1" style="42" min="38" max="66"/>
-    <col width="8.796875" customWidth="1" style="42" min="67" max="16384"/>
+    <col width="8.796875" customWidth="1" style="42" min="38" max="67"/>
+    <col width="8.796875" customWidth="1" style="42" min="68" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="46.8" customHeight="1">
@@ -16657,8 +16599,8 @@
     <col width="11.8984375" customWidth="1" style="42" min="18" max="18"/>
     <col width="18.09765625" customWidth="1" style="42" min="19" max="19"/>
     <col width="45" customWidth="1" style="42" min="20" max="34"/>
-    <col width="8.796875" customWidth="1" style="42" min="35" max="70"/>
-    <col width="8.796875" customWidth="1" style="42" min="71" max="16384"/>
+    <col width="8.796875" customWidth="1" style="42" min="35" max="71"/>
+    <col width="8.796875" customWidth="1" style="42" min="72" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="76.8" customFormat="1" customHeight="1" s="22">
@@ -19974,8 +19916,8 @@
     <col width="12.296875" customWidth="1" style="54" min="18" max="18"/>
     <col hidden="1" width="11.8984375" customWidth="1" style="42" min="19" max="19"/>
     <col width="11.8984375" customWidth="1" style="54" min="20" max="21"/>
-    <col width="11.8984375" customWidth="1" style="42" min="22" max="55"/>
-    <col width="11.8984375" customWidth="1" style="42" min="56" max="16384"/>
+    <col width="11.8984375" customWidth="1" style="42" min="22" max="56"/>
+    <col width="11.8984375" customWidth="1" style="42" min="57" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="46.8" customHeight="1">
@@ -22784,8 +22726,8 @@
     <col width="45" customWidth="1" style="46" min="20" max="20"/>
     <col width="22" customWidth="1" style="46" min="21" max="21"/>
     <col width="45" customWidth="1" style="42" min="22" max="38"/>
-    <col width="8.796875" customWidth="1" style="42" min="39" max="74"/>
-    <col width="8.796875" customWidth="1" style="42" min="75" max="16384"/>
+    <col width="8.796875" customWidth="1" style="42" min="39" max="75"/>
+    <col width="8.796875" customWidth="1" style="42" min="76" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="38.4" customHeight="1">
@@ -27969,8 +27911,8 @@
     <col width="45" customWidth="1" style="30" min="20" max="20"/>
     <col width="22" customWidth="1" style="30" min="21" max="21"/>
     <col width="45" customWidth="1" style="1" min="22" max="38"/>
-    <col width="8.796875" customWidth="1" style="1" min="39" max="74"/>
-    <col width="8.796875" customWidth="1" style="1" min="75" max="16384"/>
+    <col width="8.796875" customWidth="1" style="1" min="39" max="75"/>
+    <col width="8.796875" customWidth="1" style="1" min="76" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.2" customHeight="1">
@@ -30768,8 +30710,8 @@
     <col width="11.19921875" customWidth="1" style="30" min="18" max="18"/>
     <col width="16.69921875" customWidth="1" style="1" min="19" max="19"/>
     <col width="45" customWidth="1" style="1" min="20" max="38"/>
-    <col width="8.796875" customWidth="1" style="1" min="39" max="74"/>
-    <col width="8.796875" customWidth="1" style="1" min="75" max="16384"/>
+    <col width="8.796875" customWidth="1" style="1" min="39" max="75"/>
+    <col width="8.796875" customWidth="1" style="1" min="76" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.2" customHeight="1">
@@ -34332,8 +34274,8 @@
     <col width="45" customWidth="1" style="27" min="20" max="20"/>
     <col width="22" customWidth="1" style="27" min="21" max="21"/>
     <col width="45" customWidth="1" style="3" min="22" max="38"/>
-    <col width="8.796875" customWidth="1" style="3" min="39" max="74"/>
-    <col width="8.796875" customWidth="1" style="3" min="75" max="16384"/>
+    <col width="8.796875" customWidth="1" style="3" min="39" max="75"/>
+    <col width="8.796875" customWidth="1" style="3" min="76" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="57.6" customHeight="1">

--- a/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼BODY(집행단계-첨부폴더)v8/매뉴얼 BODY (집행단계)v8.xlsx
+++ b/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼BODY(집행단계-첨부폴더)v8/매뉴얼 BODY (집행단계)v8.xlsx
@@ -44,7 +44,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="27">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -205,8 +205,46 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -231,8 +269,20 @@
         <bgColor rgb="FF0F172A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -309,11 +359,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -563,6 +627,51 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8669,56 +8778,3336 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:KI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col width="29.69921875" customWidth="1" style="66" min="1" max="1"/>
+    <col width="10" customWidth="1" style="66" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="54" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="36" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="32" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="67" t="inlineStr">
-        <is>
-          <t>창릉역</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="67" t="inlineStr">
-        <is>
-          <t>현장매뉴얼</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="67" t="inlineStr">
-        <is>
-          <t>트램특성적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>위례 계획 보고서</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="67" t="inlineStr">
-        <is>
-          <t>도로신호,기본설계보고서 참조</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="67" t="inlineStr">
-        <is>
-          <t>GTX A 전체본 (김영환 부장)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="67" t="n"/>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>L2 코드</t>
+        </is>
+      </c>
+      <c r="B1" s="86" t="inlineStr">
+        <is>
+          <t>L3 코드</t>
+        </is>
+      </c>
+      <c r="C1" s="86" t="inlineStr">
+        <is>
+          <t>L3 대공종명</t>
+        </is>
+      </c>
+      <c r="D1" s="86" t="inlineStr">
+        <is>
+          <t>L4 코드</t>
+        </is>
+      </c>
+      <c r="E1" s="86" t="inlineStr">
+        <is>
+          <t>선행</t>
+        </is>
+      </c>
+      <c r="F1" s="86" t="inlineStr">
+        <is>
+          <t>후행</t>
+        </is>
+      </c>
+      <c r="G1" s="86" t="inlineStr">
+        <is>
+          <t>작업단위 (Level 4 Task/Activity)</t>
+        </is>
+      </c>
+      <c r="H1" s="86" t="inlineStr">
+        <is>
+          <t>일정 (D-Day)</t>
+        </is>
+      </c>
+      <c r="I1" s="86" t="inlineStr">
+        <is>
+          <t>주관</t>
+        </is>
+      </c>
+      <c r="J1" s="86" t="inlineStr">
+        <is>
+          <t>목적</t>
+        </is>
+      </c>
+      <c r="K1" s="86" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="L1" s="86" t="inlineStr">
+        <is>
+          <t>산출물(결과)</t>
+        </is>
+      </c>
+      <c r="M1" s="86" t="inlineStr">
+        <is>
+          <t>표준서 (Standard) 요약</t>
+        </is>
+      </c>
+      <c r="N1" s="86" t="inlineStr">
+        <is>
+          <t>표준서 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="O1" s="86" t="inlineStr">
+        <is>
+          <t>수행지침 (Guideline) 요약</t>
+        </is>
+      </c>
+      <c r="P1" s="86" t="inlineStr">
+        <is>
+          <t>수행지침 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="Q1" s="86" t="inlineStr">
+        <is>
+          <t>체크리스트 (Checklist) 요약</t>
+        </is>
+      </c>
+      <c r="R1" s="86" t="inlineStr">
+        <is>
+          <t>체크리스트 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="S1" s="86" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="T1" s="86" t="inlineStr">
+        <is>
+          <t>첨부서류 연계 상세 설계기준</t>
+        </is>
+      </c>
+      <c r="U1" s="86" t="inlineStr">
+        <is>
+          <t>집행단계 리스크 체크리스트</t>
+        </is>
+      </c>
+      <c r="V1" s="86" t="inlineStr">
+        <is>
+          <t>협력사 시공/공사관리 자문</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B2" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C2" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D2" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-1</t>
+        </is>
+      </c>
+      <c r="E2" s="88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-2</t>
+        </is>
+      </c>
+      <c r="G2" s="89" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전검토</t>
+        </is>
+      </c>
+      <c r="H2" s="88" t="inlineStr">
+        <is>
+          <t>D-60</t>
+        </is>
+      </c>
+      <c r="I2" s="88" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J2" s="90" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 분석 및 3단계 종합시험운행 추진체계 사전 검토</t>
+        </is>
+      </c>
+      <c r="K2" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 법정 기준 및 절차 분석 (철도안전법 제38조(종합시험운행) 및 국토교통부 고시 철도종합시험운행 시행지침의 단계별 필수 검증 항목을 분석합니다.)
+2) STEP 2: 시험운행 단계별(사전점검·시설물검증·영업시운전) 마일스톤 도출 (사전점검(60일), 시설물검증시험(30일), 영업시운전(30일)에 필요한 최소 시험기간 및 법정 선행조건을 수립합니다.)
+3) STEP 3: 철도종합시험운행 사전검토서 편찬 및 승인 (사업단 개통운영팀 주관으로 전 공종(토목, 궤도, 건축, 기계, 전기, 신호, 통신, 차량) 검토의견을 취합하여 사전검토서를 확정합니다.)</t>
+        </is>
+      </c>
+      <c r="L2" s="90" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전검토 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M2" s="90" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 사전검토 (9000-9-1) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 철도종합시험운행 시행지침 분석 및 3단계 종합시험운행 추진체계 사전 검토을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N2" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\1_철도종합시험운행 사전검토\표준서\1_철도종합시험운행 사전검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O2" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 법정 기준 및 절차 분석
+2) STEP 2: 시험운행 단계별(사전점검·시설물검증·영업시운전) 마일스톤 도출</t>
+        </is>
+      </c>
+      <c r="P2" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\1_철도종합시험운행 사전검토\수행지침\1_철도종합시험운행 사전검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q2" s="90" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 시행지침 검토 시방 및 국토교통부 고시 기준 전 조항 분석 기준을 100% 충족하였는가?
+2) 개통 목표일 역산정 공정 분석 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R2" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\1_철도종합시험운행 사전검토\체크리스트\1_철도종합시험운행 사전검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S2" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T2" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U2" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V2" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B3" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C3" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D3" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-2</t>
+        </is>
+      </c>
+      <c r="E3" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-1</t>
+        </is>
+      </c>
+      <c r="F3" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-3</t>
+        </is>
+      </c>
+      <c r="G3" s="96" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전검토 회의</t>
+        </is>
+      </c>
+      <c r="H3" s="95" t="inlineStr">
+        <is>
+          <t>D-50</t>
+        </is>
+      </c>
+      <c r="I3" s="95" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J3" s="97" t="inlineStr">
+        <is>
+          <t>사업단·감리단·협력사 합동 사전검토 회의 및 SOP 일정계획 상호 검토</t>
+        </is>
+      </c>
+      <c r="K3" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전 공종 책임자 합동 사전검토 회의 소집 (사업단 개통운영팀 주관으로 토목, 궤도, 시스템, 차량 등 전 공종 감리원 및 현장소장 합동회의를 개최합니다.)
+2) STEP 2: 분야별 잔여 공종 및 시운전 간섭 요소 검토 (전기 가압, 통신망 개통, 신호 연동시험 등 시운전 선행 필수 공종의 완료 시점을 1:1 대조합니다.)
+3) STEP 3: 사전검토 회의록 작성 및 이행 확약 (도출된 120개 필수 점검항목과 일정 조정안을 회의록에 명시하고 참석자 전원 서명 날인하여 배포합니다.)</t>
+        </is>
+      </c>
+      <c r="L3" s="97" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전검토 회의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M3" s="97" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 사전검토 회의 (9000-9-2) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 사업단·감리단·협력사 합동 사전검토 회의 및 SOP 일정계획 상호 검토을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N3" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\2_철도종합시험운행 사전검토 회의\표준서\2_철도종합시험운행 사전검토 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O3" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전 공종 책임자 합동 사전검토 회의 소집
+2) STEP 2: 분야별 잔여 공종 및 시운전 간섭 요소 검토</t>
+        </is>
+      </c>
+      <c r="P3" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\2_철도종합시험운행 사전검토 회의\수행지침\2_철도종합시험운행 사전검토 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="97" t="inlineStr">
+        <is>
+          <t>1) SOP 일정표 상호 검토 시방 및 공종별 준공 일정과 시운전 착수일 대조 기준을 100% 충족하였는가?
+2) 분야별 책임분계점 확정 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R3" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\2_철도종합시험운행 사전검토 회의\체크리스트\2_철도종합시험운행 사전검토 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S3" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T3" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U3" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V3" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B4" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C4" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D4" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-3</t>
+        </is>
+      </c>
+      <c r="E4" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-2</t>
+        </is>
+      </c>
+      <c r="F4" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-4</t>
+        </is>
+      </c>
+      <c r="G4" s="89" t="inlineStr">
+        <is>
+          <t>토목·궤도 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="H4" s="88" t="inlineStr">
+        <is>
+          <t>D-40</t>
+        </is>
+      </c>
+      <c r="I4" s="88" t="inlineStr">
+        <is>
+          <t>시스템팀</t>
+        </is>
+      </c>
+      <c r="J4" s="90" t="inlineStr">
+        <is>
+          <t>노반·궤도·분기기 시공 상태 검증 및 신호설비 설치 사전 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="K4" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 매립형 궤도 기하구조 정밀 실측 데이터 검토 (트램 본선 34.4km 전 구간의 궤간(1,435mm), 수평, 고저, 평면성 및 유간 측정 데이터를 정밀 검증합니다.)
+2) STEP 2: 선로전환기(143개소) 및 신호 검지선 인터페이스 확인 (궤도 도상 타설부와 신호 선로전환기 모터/로드 결합부의 기계적 인터페이스를 검토합니다.)
+3) STEP 3: 토목·궤도 인터페이스 관리대장 확정 (승강장 연단과 트램 차량 발판 간격(50mm 이내) 및 건축한계 침범 여부를 최종 확인 후 관리대장을 작성합니다.)</t>
+        </is>
+      </c>
+      <c r="L4" s="90" t="inlineStr">
+        <is>
+          <t>토목·궤도 인터페이스 협의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M4" s="90" t="inlineStr">
+        <is>
+          <t>1) 토목·궤도 인터페이스 협의 (9000-9-3) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 노반·궤도·분기기 시공 상태 검증 및 신호설비 설치 사전 인터페이스 협의을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N4" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\3_토목·궤도 인터페이스 협의\표준서\3_토목·궤도 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O4" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 매립형 궤도 기하구조 정밀 실측 데이터 검토
+2) STEP 2: 선로전환기(143개소) 및 신호 검지선 인터페이스 확인</t>
+        </is>
+      </c>
+      <c r="P4" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\3_토목·궤도 인터페이스 협의\수행지침\3_토목·궤도 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="90" t="inlineStr">
+        <is>
+          <t>1) 궤도 단면 및 궤간 검측 시방 및 궤간 1,435mm ±2mm 이내 확인 기준을 100% 충족하였는가?
+2) 선로전환기 취부부 검토 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R4" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\3_토목·궤도 인터페이스 협의\체크리스트\3_토목·궤도 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S4" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T4" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U4" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V4" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B5" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C5" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D5" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-4</t>
+        </is>
+      </c>
+      <c r="E5" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-3</t>
+        </is>
+      </c>
+      <c r="F5" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-5</t>
+        </is>
+      </c>
+      <c r="G5" s="96" t="inlineStr">
+        <is>
+          <t>전기·통신·신호·차량 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="H5" s="95" t="inlineStr">
+        <is>
+          <t>D-35</t>
+        </is>
+      </c>
+      <c r="I5" s="95" t="inlineStr">
+        <is>
+          <t>시스템팀</t>
+        </is>
+      </c>
+      <c r="J5" s="97" t="inlineStr">
+        <is>
+          <t>급전·LTE-R·T-ATP/ATO·차량 간 E&amp;M 복합 시스템 연동 인터페이스 조율</t>
+        </is>
+      </c>
+      <c r="K5" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전기 급전 및 배터리 급속충전 인터페이스 검토 (정거장 상부 강체 급속충전 아암(Arm)과 트램 차량 집전장치(Pantograph) 간의 접촉 압력 및 위치 정합성을 확인합니다.)
+2) STEP 2: LTE-R 통신망 및 신호 T-ATP/ATO 데이터 인터페이스 검증 (차상 단말장치(OBCU)와 지상 무선 기지국(DU/RU) 간의 무선 패킷 손실률(≤ 1%) 및 지연시간을 검증합니다.)
+3) STEP 3: PSD(스크린도어) ↔ 차량 도어 연동 시스템 확정 (트램 정위치 정차(오차 ±300mm 이내) 시 차량 도어와 승강장 PSD가 100% 동기화되어 개폐되는 인터페이스를 승인합니다.)</t>
+        </is>
+      </c>
+      <c r="L5" s="97" t="inlineStr">
+        <is>
+          <t>전기·통신·신호·차량 인터페이스 협의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M5" s="97" t="inlineStr">
+        <is>
+          <t>1) 전기·통신·신호·차량 인터페이스 협의 (9000-9-4) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 급전·LTE-R·T-ATP/ATO·차량 간 E&amp;M 복합 시스템 연동 인터페이스 조율을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N5" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\4_전기·통신·신호·차량 인터페이스 협의\표준서\4_전기·통신·신호·차량 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O5" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전기 급전 및 배터리 급속충전 인터페이스 검토
+2) STEP 2: LTE-R 통신망 및 신호 T-ATP/ATO 데이터 인터페이스 검증</t>
+        </is>
+      </c>
+      <c r="P5" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\4_전기·통신·신호·차량 인터페이스 협의\수행지침\4_전기·통신·신호·차량 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="97" t="inlineStr">
+        <is>
+          <t>1) 급속충전 시스템 연동 시방 및 정거장 강체 가선 및 집전장치 대조 기준을 100% 충족하였는가?
+2) LTE-R 무선 데이터 연동 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R5" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\4_전기·통신·신호·차량 인터페이스 협의\체크리스트\4_전기·통신·신호·차량 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S5" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T5" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U5" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V5" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B6" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C6" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D6" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-5</t>
+        </is>
+      </c>
+      <c r="E6" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-4</t>
+        </is>
+      </c>
+      <c r="F6" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-6</t>
+        </is>
+      </c>
+      <c r="G6" s="89" t="inlineStr">
+        <is>
+          <t>관제 및 운영사 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="H6" s="88" t="inlineStr">
+        <is>
+          <t>D-30</t>
+        </is>
+      </c>
+      <c r="I6" s="88" t="inlineStr">
+        <is>
+          <t>시스템팀</t>
+        </is>
+      </c>
+      <c r="J6" s="90" t="inlineStr">
+        <is>
+          <t>종합관제센터(OCC)·화성도시공사 운영사 요구사항 사전 반영 및 과업범위 최적화</t>
+        </is>
+      </c>
+      <c r="K6" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 종합관제센터 관제 설비 및 원격 감시 체계 검토 (종합관제센터 중앙 컴퓨터에 표출되는 트램 열차 위치, 변전소 전력 상태, 정거장 환기/승강기 상태 모니터링 화면을 검증합니다.)
+2) STEP 2: 화성도시공사 운영사 요구사항 수렴 및 기능 최적화 (운영 및 유지보수자 편의 향상을 위한 관제 화면 기능 추가/삭제 사항을 협의하고 불필요한 과업을 조정합니다.)
+3) STEP 3: 관제 및 운영 인터페이스 관리대장 승인 (사업단, 관제 소프트웨어 공급사, 화성도시공사 3자 서명 날인을 완료하고 시운전 연동 프로토콜을 확정합니다.)</t>
+        </is>
+      </c>
+      <c r="L6" s="90" t="inlineStr">
+        <is>
+          <t>관제 및 운영사 인터페이스 협의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M6" s="90" t="inlineStr">
+        <is>
+          <t>1) 관제 및 운영사 인터페이스 협의 (9000-9-5) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 종합관제센터(OCC)·화성도시공사 운영사 요구사항 사전 반영 및 과업범위 최적화을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N6" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\5_관제 및 운영사 인터페이스 협의\표준서\5_관제 및 운영사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O6" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 종합관제센터 관제 설비 및 원격 감시 체계 검토
+2) STEP 2: 화성도시공사 운영사 요구사항 수렴 및 기능 최적화</t>
+        </is>
+      </c>
+      <c r="P6" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\5_관제 및 운영사 인터페이스 협의\수행지침\5_관제 및 운영사 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q6" s="90" t="inlineStr">
+        <is>
+          <t>1) 종합관제 SCADA 화면 검토 시방 및 전력/신호/설비 관제 화면 검증 기준을 100% 충족하였는가?
+2) 사령-현장 비상통신 라인 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R6" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\5_관제 및 운영사 인터페이스 협의\체크리스트\5_관제 및 운영사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S6" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T6" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U6" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V6" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B7" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C7" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D7" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-6</t>
+        </is>
+      </c>
+      <c r="E7" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-5</t>
+        </is>
+      </c>
+      <c r="F7" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-7</t>
+        </is>
+      </c>
+      <c r="G7" s="96" t="inlineStr">
+        <is>
+          <t>인력·시험장비 투입계획 수립</t>
+        </is>
+      </c>
+      <c r="H7" s="95" t="inlineStr">
+        <is>
+          <t>D-30</t>
+        </is>
+      </c>
+      <c r="I7" s="95" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J7" s="97" t="inlineStr">
+        <is>
+          <t>시험운전반, 유관기관 합동 점검단 인력 배치 및 공인 시험 계측기 확보</t>
+        </is>
+      </c>
+      <c r="K7" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 5대 전문 시험운전반 조직 체계 수립 (총괄관리반, 시설검증반(토목/궤도/건축), 시스템검증반(전기/신호/통신), 차량검증반, 안전비상대응반을 편성합니다.)
+2) STEP 2: 공인 교정 시험 계측기 및 검측 장비 확보 (트램 궤도 기하구조 검측기, 레이저 트랙게이지, 전력 분석계, LTE-R 무선 전계강도 측정기의 공인 교정 유효기간을 확인합니다.)
+3) STEP 3: 인력·시험장비 종합 투입계획서 감리 승인 (시운전 기간 동안의 일일 투입 공수, 장비 가동 계획 및 비상주기 장소를 명시한 계획서를 최종 확정합니다.)</t>
+        </is>
+      </c>
+      <c r="L7" s="97" t="inlineStr">
+        <is>
+          <t>인력·시험장비 투입계획 수립 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M7" s="97" t="inlineStr">
+        <is>
+          <t>1) 인력·시험장비 투입계획 수립 (9000-9-6) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 시험운전반, 유관기관 합동 점검단 인력 배치 및 공인 시험 계측기 확보을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N7" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\6_인력·시험장비 투입계획 수립\표준서\6_인력·시험장비 투입계획 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O7" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 5대 전문 시험운전반 조직 체계 수립
+2) STEP 2: 공인 교정 시험 계측기 및 검측 장비 확보</t>
+        </is>
+      </c>
+      <c r="P7" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\6_인력·시험장비 투입계획 수립\수행지침\6_인력·시험장비 투입계획 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="97" t="inlineStr">
+        <is>
+          <t>1) 시험운전반 조직 구성표 시방 및 5개 분야 45명 전담 인력 편성 기준을 100% 충족하였는가?
+2) 시험 계측장비 목록 확정 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R7" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\6_인력·시험장비 투입계획 수립\체크리스트\6_인력·시험장비 투입계획 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S7" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T7" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U7" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V7" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B8" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C8" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D8" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-7</t>
+        </is>
+      </c>
+      <c r="E8" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-6</t>
+        </is>
+      </c>
+      <c r="F8" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-8</t>
+        </is>
+      </c>
+      <c r="G8" s="89" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전 협의사항(TS) 도출</t>
+        </is>
+      </c>
+      <c r="H8" s="88" t="inlineStr">
+        <is>
+          <t>D-25</t>
+        </is>
+      </c>
+      <c r="I8" s="88" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J8" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS) 사전 점검 항목 및 기술기준 적합성 쟁점 선제적 도출</t>
+        </is>
+      </c>
+      <c r="K8" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 도시철도건설규칙 및 철도시설 기술기준 전 조항 대조 (도시철도건설규칙 제67조(방재), 제32조(궤도), 제40조(전차선로) 등 동탄트램 해당 조항의 기술적 만족 여부를 전수 점검합니다.)
+2) STEP 2: 한국교통안전공단(TS) 주요 심사 지적사항 사전 스크리닝 (트램 승강장 연단 간격, 배터리 충전구 안전 인터록, 교차로 우선신호 연동 오류 등 예상 지적 45개 항목을 추출합니다.)
+3) STEP 3: TS 사전협의 대상 목록 보고서 완성 (사전컨설팅 회의에서 질의할 항목 및 기술 승인 요청 리스트를 정리하여 개통운영팀장 승인을 득합니다.)</t>
+        </is>
+      </c>
+      <c r="L8" s="90" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전 협의사항(TS) 도출 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M8" s="90" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 사전 협의사항(TS) 도출 (9000-9-7) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 한국교통안전공단(TS) 사전 점검 항목 및 기술기준 적합성 쟁점 선제적 도출을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N8" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\7_철도종합시험운행 사전 협의사항(TS) 도출\표준서\7_철도종합시험운행 사전 협의사항(TS) 도출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O8" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 도시철도건설규칙 및 철도시설 기술기준 전 조항 대조
+2) STEP 2: 한국교통안전공단(TS) 주요 심사 지적사항 사전 스크리닝</t>
+        </is>
+      </c>
+      <c r="P8" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\7_철도종합시험운행 사전 협의사항(TS) 도출\수행지침\7_철도종합시험운행 사전 협의사항(TS) 도출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q8" s="90" t="inlineStr">
+        <is>
+          <t>1) 철도시설 기술기준 매핑 시방 및 도시철도건설규칙 80개 조항 분석 기준을 100% 충족하였는가?
+2) TS 지적 예상 항목 검토 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R8" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\7_철도종합시험운행 사전 협의사항(TS) 도출\체크리스트\7_철도종합시험운행 사전 협의사항(TS) 도출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S8" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T8" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U8" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V8" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B9" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C9" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D9" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-8</t>
+        </is>
+      </c>
+      <c r="E9" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-7</t>
+        </is>
+      </c>
+      <c r="F9" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-9</t>
+        </is>
+      </c>
+      <c r="G9" s="96" t="inlineStr">
+        <is>
+          <t>착수 전 전공종 합동회의</t>
+        </is>
+      </c>
+      <c r="H9" s="95" t="inlineStr">
+        <is>
+          <t>D-20</t>
+        </is>
+      </c>
+      <c r="I9" s="95" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J9" s="97" t="inlineStr">
+        <is>
+          <t>8대 전 공종 단독·연동시험 결과보고서 검증 및 시운전 전제조건 100% 충족 확인</t>
+        </is>
+      </c>
+      <c r="K9" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 8대 공종별 단독·공종시험 결과보고서 전수 취합 (토목(평판재하), 궤도(기하구조), 기계(환기/소화수압), 전기(절연저항/가압), 신호(연동표검사), 통신(LTE-R 통화품질) 성적서를 심사합니다.)
+2) STEP 2: 법정 검사 필증 및 사전 승인 서류 확인 (전기안전공사 사용전검사 필증, 소방완공검사 필증, 승강기 완성검사 필증의 정식 수령 상태를 대조합니다.)
+3) STEP 3: 착수 전 합동회의 개최 및 시운전 개시 선언 (발주처, 사업단, 감리단, 운영사 전원 합의 하에 '철도종합시험운행 착수 전제조건 100% 충족'을 선언하고 회의록을 체결합니다.)</t>
+        </is>
+      </c>
+      <c r="L9" s="97" t="inlineStr">
+        <is>
+          <t>착수 전 전공종 합동회의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M9" s="97" t="inlineStr">
+        <is>
+          <t>1) 착수 전 전공종 합동회의 (9000-9-8) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 8대 전 공종 단독·연동시험 결과보고서 검증 및 시운전 전제조건 100% 충족 확인을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N9" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증\표준서\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O9" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 8대 공종별 단독·공종시험 결과보고서 전수 취합
+2) STEP 2: 법정 검사 필증 및 사전 승인 서류 확인</t>
+        </is>
+      </c>
+      <c r="P9" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증\수행지침\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q9" s="97" t="inlineStr">
+        <is>
+          <t>1) 8대 공종 시험성적서 검토 시방 및 노반 다짐, 궤도 기하, 변전소 가압 기준을 100% 충족하였는가?
+2) 신호/통신 연동시험 검증 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R9" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증\체크리스트\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S9" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T9" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U9" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V9" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B10" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C10" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D10" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-9</t>
+        </is>
+      </c>
+      <c r="E10" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-8</t>
+        </is>
+      </c>
+      <c r="F10" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-10</t>
+        </is>
+      </c>
+      <c r="G10" s="89" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 종합계획서 수립</t>
+        </is>
+      </c>
+      <c r="H10" s="88" t="inlineStr">
+        <is>
+          <t>D+0</t>
+        </is>
+      </c>
+      <c r="I10" s="88" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J10" s="90" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 표준운영절차(SOP) 및 사전점검·시설물검증·영업시운전 종합계획서 편찬</t>
+        </is>
+      </c>
+      <c r="K10" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 종합계획서(SOP) 기본 골격 수립 (동탄트램 사업 개요, 시험운행 목적, 추진 기간, 분야별 시험 조직도 및 R&amp;R을 명확히 규정합니다.)
+2) STEP 2: 단계별 세부 시험계획서(사전점검/시설물검증/영업시운전) 작성 (사전점검 12개 분야 체크리스트 및 현장 확인 항목을 편찬합니다.)
+3) STEP 3: 책임감리원 검토의견서 첨부 및 종합계획서 승인 (각 분야 책임감리원의 기술 검토 서명을 완료하고 총괄사업단장의 최종 승인을 득합니다.)</t>
+        </is>
+      </c>
+      <c r="L10" s="90" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 종합계획서 수립 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M10" s="90" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 종합계획서 수립 (9000-9-9) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 철도종합시험운행 표준운영절차(SOP) 및 사전점검·시설물검증·영업시운전 종합계획서 편찬을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N10" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\9_철도종합시험운행 종합계획서(SOP) 수립\표준서\9_철도종합시험운행 종합계획서(SOP) 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O10" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 종합계획서(SOP) 기본 골격 수립
+2) STEP 2: 단계별 세부 시험계획서(사전점검/시설물검증/영업시운전) 작성</t>
+        </is>
+      </c>
+      <c r="P10" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\9_철도종합시험운행 종합계획서(SOP) 수립\수행지침\9_철도종합시험운행 종합계획서(SOP) 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="90" t="inlineStr">
+        <is>
+          <t>1) 종합계획서(SOP) 본안 작성 시방 및 개요, 조직, 안전관리, 세부일정 기준을 100% 충족하였는가?
+2) 사전점검 계획서 수립 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R10" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\9_철도종합시험운행 종합계획서(SOP) 수립\체크리스트\9_철도종합시험운행 종합계획서(SOP) 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S10" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T10" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U10" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V10" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B11" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C11" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D11" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-10</t>
+        </is>
+      </c>
+      <c r="E11" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-9</t>
+        </is>
+      </c>
+      <c r="F11" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-11</t>
+        </is>
+      </c>
+      <c r="G11" s="96" t="inlineStr">
+        <is>
+          <t>TS 사전컨설팅 회의</t>
+        </is>
+      </c>
+      <c r="H11" s="95" t="inlineStr">
+        <is>
+          <t>D+30</t>
+        </is>
+      </c>
+      <c r="I11" s="95" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J11" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS) 합동 사전컨설팅 회의를 통한 계획서 보완 및 적합성 검증</t>
+        </is>
+      </c>
+      <c r="K11" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 한국교통안전공단(TS) 사전컨설팅 안건 상정 (종합시험운행 계획서 초안, 현장 공정 실적, 안전관리계획서 및 공종별 시험결과 요약본을 TS에 제출합니다.)
+2) STEP 2: TS 전문위원단 합동 대면 심의 회의 진행 (동탄트램 무가선 배터리 충전 안전성, 교차로 신호 우선권, 역사 승하차 안전 발판 등 특수 검증 항목을 집중 협의합니다.)
+3) STEP 3: 컨설팅 지적사항 보완 조치 및 최종본 확정 (TS 검토의견서에 명시된 권고 및 보완 사항을 계획서에 100% 반영하여 정식 제출용 최종안을 완성합니다.)</t>
+        </is>
+      </c>
+      <c r="L11" s="97" t="inlineStr">
+        <is>
+          <t>TS 사전컨설팅 회의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M11" s="97" t="inlineStr">
+        <is>
+          <t>1) TS 사전컨설팅 회의 (9000-9-10) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 한국교통안전공단(TS) 합동 사전컨설팅 회의를 통한 계획서 보완 및 적합성 검증을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N11" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\10_계획서 제출 전 TS 사전컨설팅 회의\표준서\10_계획서 제출 전 TS 사전컨설팅 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O11" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 한국교통안전공단(TS) 사전컨설팅 안건 상정
+2) STEP 2: TS 전문위원단 합동 대면 심의 회의 진행</t>
+        </is>
+      </c>
+      <c r="P11" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\10_계획서 제출 전 TS 사전컨설팅 회의\수행지침\10_계획서 제출 전 TS 사전컨설팅 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="97" t="inlineStr">
+        <is>
+          <t>1) 사전컨설팅 신청서 제출 시방 및 종합계획서 초안 및 첨부자료 기준을 100% 충족하였는가?
+2) TS 합동 컨설팅 회의 개최 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R11" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\10_계획서 제출 전 TS 사전컨설팅 회의\체크리스트\10_계획서 제출 전 TS 사전컨설팅 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S11" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T11" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U11" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V11" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B12" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C12" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D12" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-11</t>
+        </is>
+      </c>
+      <c r="E12" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-10</t>
+        </is>
+      </c>
+      <c r="F12" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-12</t>
+        </is>
+      </c>
+      <c r="G12" s="89" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 연간계획 수립/제출</t>
+        </is>
+      </c>
+      <c r="H12" s="88" t="inlineStr">
+        <is>
+          <t>D+60</t>
+        </is>
+      </c>
+      <c r="I12" s="88" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J12" s="90" t="inlineStr">
+        <is>
+          <t>국토교통부 및 한국교통안전공단(TS)에 철도종합시험운행 계획서 정식 접수 및 승인 득</t>
+        </is>
+      </c>
+      <c r="K12" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 법정 제출 서류 편철 및 사업단장 결재 (철도종합시험운행 계획서 본안 3부, 사전점검 점검표, 안전관리계획서, 공종별 시험결과보고서를 편철합니다.)
+2) STEP 2: 국토교통부 및 TS 정식 공문 접수 (전자문서유통시스템을 통해 국토교통부(철도운행안전과) 및 한국교통안전공단(철도안전처)에 정식 접수합니다.)
+3) STEP 3: 심사 대응 및 국토부 승인 공문 접수 (TS 서류 심사관의 질의에 대한 기술적 근거를 제출하고, 국토교통부 장관의 '철도종합시험운행 계획 승인' 공문을 접수합니다.)</t>
+        </is>
+      </c>
+      <c r="L12" s="90" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 연간계획 수립/제출 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M12" s="90" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 연간계획 수립/제출 (9000-9-11) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 국토교통부 및 한국교통안전공단(TS)에 철도종합시험운행 계획서 정식 접수 및 승인 득을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N12" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\11_철도종합시험운행 연간계획 수립 및 TS 제출\표준서\11_철도종합시험운행 연간계획 수립 및 TS 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O12" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 법정 제출 서류 편철 및 사업단장 결재
+2) STEP 2: 국토교통부 및 TS 정식 공문 접수</t>
+        </is>
+      </c>
+      <c r="P12" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\11_철도종합시험운행 연간계획 수립 및 TS 제출\수행지침\11_철도종합시험운행 연간계획 수립 및 TS 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="90" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 계획서 공문 발송 시방 및 국토교통부 철도안전정책과 기준을 100% 충족하였는가?
+2) 한국교통안전공단 서류 심사 대응 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R12" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\11_철도종합시험운행 연간계획 수립 및 TS 제출\체크리스트\11_철도종합시험운행 연간계획 수립 및 TS 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S12" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T12" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U12" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V12" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B13" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C13" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D13" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-12</t>
+        </is>
+      </c>
+      <c r="E13" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-11</t>
+        </is>
+      </c>
+      <c r="F13" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-13</t>
+        </is>
+      </c>
+      <c r="G13" s="96" t="inlineStr">
+        <is>
+          <t>안전관리계획서 수립 및 비상대응체계</t>
+        </is>
+      </c>
+      <c r="H13" s="95" t="inlineStr">
+        <is>
+          <t>D+80</t>
+        </is>
+      </c>
+      <c r="I13" s="95" t="inlineStr">
+        <is>
+          <t>안전품질팀</t>
+        </is>
+      </c>
+      <c r="J13" s="97" t="inlineStr">
+        <is>
+          <t>시운전 전 구간 선로 출입통제, 시험열차 안전통제관 탑승 및 관할 소방·경찰 비상연락망</t>
+        </is>
+      </c>
+      <c r="K13" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 안전관리계획서 수립 및 위험성평가 (시운전 구간 내 작업자 안전, 감전 방지, 열차 접촉 방지, 도로 교차로 보행자 통제 대책을 수립합니다.)
+2) STEP 2: 선로 출입 통제 시스템 및 안전통제관 지정 (선로 출입문 시건장치 및 출입대장을 운영하고, 시험열차 운행 시 안전통제관(2인 1조) 필수 탑승을 의무화합니다.)
+3) STEP 3: 비상연락망 구축 및 소방·경찰 합동 모의도상훈련 (화성소방서, 동탄경찰서, 응급의료센터와 24시간 비상 핫라인을 개통하고 가상 사고 대응 도상훈련을 실시합니다.)</t>
+        </is>
+      </c>
+      <c r="L13" s="97" t="inlineStr">
+        <is>
+          <t>안전관리계획서 수립 및 비상대응체계 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M13" s="97" t="inlineStr">
+        <is>
+          <t>1) 안전관리계획서 수립 및 비상대응체계 (9000-9-12) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 시운전 전 구간 선로 출입통제, 시험열차 안전통제관 탑승 및 관할 소방·경찰 비상연락망을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N13" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\12_시험운행 안전관리계획서 수립 및 비상대응체계\표준서\12_시험운행 안전관리계획서 수립 및 비상대응체계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O13" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 안전관리계획서 수립 및 위험성평가
+2) STEP 2: 선로 출입 통제 시스템 및 안전통제관 지정</t>
+        </is>
+      </c>
+      <c r="P13" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\12_시험운행 안전관리계획서 수립 및 비상대응체계\수행지침\12_시험운행 안전관리계획서 수립 및 비상대응체계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="97" t="inlineStr">
+        <is>
+          <t>1) 시운전 안전관리계획서 작성 시방 및 위험성평가 및 비상대응 매뉴얼 기준을 100% 충족하였는가?
+2) 선로 무단침입 방지 시설 점검 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R13" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\12_시험운행 안전관리계획서 수립 및 비상대응체계\체크리스트\12_시험운행 안전관리계획서 수립 및 비상대응체계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S13" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T13" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U13" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V13" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B14" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C14" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D14" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-13</t>
+        </is>
+      </c>
+      <c r="E14" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-12</t>
+        </is>
+      </c>
+      <c r="F14" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-14</t>
+        </is>
+      </c>
+      <c r="G14" s="89" t="inlineStr">
+        <is>
+          <t>사전점검 착수보고</t>
+        </is>
+      </c>
+      <c r="H14" s="88" t="inlineStr">
+        <is>
+          <t>D+120</t>
+        </is>
+      </c>
+      <c r="I14" s="88" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J14" s="90" t="inlineStr">
+        <is>
+          <t>사전점검 착수보고회(TS) 개최, 12개 분야별 정부 합동점검단 현장 정밀점검 개시</t>
+        </is>
+      </c>
+      <c r="K14" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 착수보고회(TS) 개최 및 현장 브리핑 (사업단 개통운영팀장이 TS 합동점검단에 동탄트램 시설 현황, 공종별 시험 결과 및 점검 지원 계획을 브리핑합니다.)
+2) STEP 2: 12개 분야별 합동점검단 현장 정밀 실사 수행 (토목/궤도(선로 침하, 유간), 건축(피난계단, 마감), 전기(가압, 접지), 신호(연동장치), 통신(LTE-R)을 도면과 1:1 대조합니다.)
+3) STEP 3: 일일 점검회의 및 지적사항 실시간 공유 (매일 점검 종료 후 현장 합동회의를 열어 도출된 지적사항을 즉시 공유하고 긴급 보완 지시서를 발행합니다.)</t>
+        </is>
+      </c>
+      <c r="L14" s="90" t="inlineStr">
+        <is>
+          <t>사전점검 착수보고 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M14" s="90" t="inlineStr">
+        <is>
+          <t>1) 사전점검 착수보고 (9000-9-13) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 사전점검 착수보고회(TS) 개최, 12개 분야별 정부 합동점검단 현장 정밀점검 개시을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N14" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\13_사전점검 착수보고 및 분야별 점검단 가동\표준서\13_사전점검 착수보고 및 분야별 점검단 가동_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O14" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 착수보고회(TS) 개최 및 현장 브리핑
+2) STEP 2: 12개 분야별 합동점검단 현장 정밀 실사 수행</t>
+        </is>
+      </c>
+      <c r="P14" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\13_사전점검 착수보고 및 분야별 점검단 가동\수행지침\13_사전점검 착수보고 및 분야별 점검단 가동_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="90" t="inlineStr">
+        <is>
+          <t>1) 사전점검 착수회의 개최 시방 및 TS 주관 착수보고 및 점검일정 확정 기준을 100% 충족하였는가?
+2) 12개 분야 합동 현장 점검 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R14" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\13_사전점검 착수보고 및 분야별 점검단 가동\체크리스트\13_사전점검 착수보고 및 분야별 점검단 가동_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S14" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T14" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U14" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V14" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B15" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C15" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D15" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-14</t>
+        </is>
+      </c>
+      <c r="E15" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-13</t>
+        </is>
+      </c>
+      <c r="F15" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-15</t>
+        </is>
+      </c>
+      <c r="G15" s="96" t="inlineStr">
+        <is>
+          <t>철도시설 기술기준 검토 및 조치계획</t>
+        </is>
+      </c>
+      <c r="H15" s="95" t="inlineStr">
+        <is>
+          <t>D+130</t>
+        </is>
+      </c>
+      <c r="I15" s="95" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J15" s="97" t="inlineStr">
+        <is>
+          <t>도시철도건설규칙 전 조항 대조, 사전점검 지적사항 1:1 조치계획서 수립</t>
+        </is>
+      </c>
+      <c r="K15" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 지적사항 전수 등록 및 위험도 분류 (TS로부터 통보받은 지적사항을 '중대 결함', '일반 보완', '권고'로 분류하고 관리번호를 부여합니다.)
+2) STEP 2: 공학적 원인 분석 및 재시공/보강 기술 대책 수립 (해당 공종 협력사 및 설계사와 합동으로 문제 원인을 정밀 분석하고, 기술기준을 충족하는 상세 도면 및 시방을 작성합니다.)
+3) STEP 3: 사전점검 지적사항 조치계획서 편찬 및 감리 승인 (조치 기한(D+175 이전 완료)을 명시한 조치계획서를 작성하여 책임감리단 서명을 득하고 TS에 제출합니다.)</t>
+        </is>
+      </c>
+      <c r="L15" s="97" t="inlineStr">
+        <is>
+          <t>철도시설 기술기준 검토 및 조치계획 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M15" s="97" t="inlineStr">
+        <is>
+          <t>1) 철도시설 기술기준 검토 및 조치계획 (9000-9-14) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 도시철도건설규칙 전 조항 대조, 사전점검 지적사항 1:1 조치계획서 수립을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N15" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\14_철도시설의 기술기준 검토 및 지적사항 조치계획\표준서\14_철도시설의 기술기준 검토 및 지적사항 조치계획_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O15" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 지적사항 전수 등록 및 위험도 분류
+2) STEP 2: 공학적 원인 분석 및 재시공/보강 기술 대책 수립</t>
+        </is>
+      </c>
+      <c r="P15" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\14_철도시설의 기술기준 검토 및 지적사항 조치계획\수행지침\14_철도시설의 기술기준 검토 및 지적사항 조치계획_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="97" t="inlineStr">
+        <is>
+          <t>1) 지적사항 목록 전수 분류 시방 및 구조안전, 전기절연, 신호인터록 등 기준을 100% 충족하였는가?
+2) 분야별 원인분석 및 보강안 설계 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R15" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\14_철도시설의 기술기준 검토 및 지적사항 조치계획\체크리스트\14_철도시설의 기술기준 검토 및 지적사항 조치계획_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S15" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T15" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U15" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V15" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B16" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C16" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D16" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-15</t>
+        </is>
+      </c>
+      <c r="E16" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-14</t>
+        </is>
+      </c>
+      <c r="F16" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-16</t>
+        </is>
+      </c>
+      <c r="G16" s="89" t="inlineStr">
+        <is>
+          <t>사전점검 보완조치 및 국토부 승인</t>
+        </is>
+      </c>
+      <c r="H16" s="88" t="inlineStr">
+        <is>
+          <t>D+175</t>
+        </is>
+      </c>
+      <c r="I16" s="88" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J16" s="90" t="inlineStr">
+        <is>
+          <t>지적사항 100% 현장 보강 조치 완료, 조치결과보고서 제출 및 국토교통부 적합 승인</t>
+        </is>
+      </c>
+      <c r="K16" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 분야별 사전점검 지적사항 현장 보강 공사 완료 (궤도 선형 교정, 정거장 마감 보완, 전기 절연 보강, 신호 연동 시퀀스 튜닝을 전수 완료합니다.)
+2) STEP 2: 책임감리원 전수 입회 검측 및 결과보고서 편찬 (지적 전·중·후 사진, 공인 시험성적서, 감리원 확인서를 편철한 조치결과보고서를 편찬합니다.)
+3) STEP 3: 국토교통부 및 TS 최종 심사 대응 및 승인 공문 접수 (국토부 철도운행안전과로부터 '철도시설의 기술기준 적합 및 시설물검증시험 착수 승인' 공문을 수령합니다.)</t>
+        </is>
+      </c>
+      <c r="L16" s="90" t="inlineStr">
+        <is>
+          <t>사전점검 보완조치 및 국토부 승인 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M16" s="90" t="inlineStr">
+        <is>
+          <t>1) 사전점검 보완조치 및 국토부 승인 (9000-9-15) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 지적사항 100% 현장 보강 조치 완료, 조치결과보고서 제출 및 국토교통부 적합 승인을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N16" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\15_사전점검 보완조치 및 조치결과 국토부 승인\표준서\15_사전점검 보완조치 및 조치결과 국토부 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O16" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 분야별 사전점검 지적사항 현장 보강 공사 완료
+2) STEP 2: 책임감리원 전수 입회 검측 및 결과보고서 편찬</t>
+        </is>
+      </c>
+      <c r="P16" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\15_사전점검 보완조치 및 조치결과 국토부 승인\수행지침\15_사전점검 보완조치 및 조치결과 국토부 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="90" t="inlineStr">
+        <is>
+          <t>1) 현장 재시공 및 보강 공사 시방 및 설계 변경 및 현장 보강 완료 기준을 100% 충족하였는가?
+2) 감리단 합동 검측 및 사진대지 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R16" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\15_사전점검 보완조치 및 조치결과 국토부 승인\체크리스트\15_사전점검 보완조치 및 조치결과 국토부 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S16" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T16" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U16" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V16" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B17" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C17" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D17" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-16</t>
+        </is>
+      </c>
+      <c r="E17" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-15</t>
+        </is>
+      </c>
+      <c r="F17" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-17</t>
+        </is>
+      </c>
+      <c r="G17" s="96" t="inlineStr">
+        <is>
+          <t>사전점검 종결회의 및 결과보고서 승인</t>
+        </is>
+      </c>
+      <c r="H17" s="95" t="inlineStr">
+        <is>
+          <t>D+180</t>
+        </is>
+      </c>
+      <c r="I17" s="95" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J17" s="97" t="inlineStr">
+        <is>
+          <t>사전점검 종결보고회(TS) 개최 및 1단계 사전점검 공식 종결 선언</t>
+        </is>
+      </c>
+      <c r="K17" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 종결회의 안건 브리핑 및 조치 실적 보고 (지적사항 조치 결과 및 국토부 적합 승인 공문 내용을 TS 합동점검단에 종합 보고합니다.)
+2) STEP 2: 점검단 최종 의견 수렴 및 사전점검 합격 판정 (점검단 전원 일치로 '동탄트램 사전점검 합격 및 시설물검증시험 진입 적합'을 최종 판정합니다.)
+3) STEP 3: 사전점검 종결 서명 날인 및 다음 단계 선언 (사전점검 종합결과보고서에 서명하고, 2단계 시설물검증시험 공식 개시를 선포합니다.)</t>
+        </is>
+      </c>
+      <c r="L17" s="97" t="inlineStr">
+        <is>
+          <t>사전점검 종결회의 및 결과보고서 승인 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M17" s="97" t="inlineStr">
+        <is>
+          <t>1) 사전점검 종결회의 및 결과보고서 승인 (9000-9-16) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 사전점검 종결보고회(TS) 개최 및 1단계 사전점검 공식 종결 선언을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N17" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\16_사전점검 종결회의 및 결과보고서 승인\표준서\16_사전점검 종결회의 및 결과보고서 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O17" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 종결회의 안건 브리핑 및 조치 실적 보고
+2) STEP 2: 점검단 최종 의견 수렴 및 사전점검 합격 판정</t>
+        </is>
+      </c>
+      <c r="P17" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\16_사전점검 종결회의 및 결과보고서 승인\수행지침\16_사전점검 종결회의 및 결과보고서 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="97" t="inlineStr">
+        <is>
+          <t>1) 사전점검 종결회의 개최 시방 및 TS 주관 종합 결과 브리핑 기준을 100% 충족하였는가?
+2) 사전점검 종합보고서 서명 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R17" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\16_사전점검 종결회의 및 결과보고서 승인\체크리스트\16_사전점검 종결회의 및 결과보고서 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S17" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T17" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U17" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V17" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B18" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C18" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D18" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-17</t>
+        </is>
+      </c>
+      <c r="E18" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-16</t>
+        </is>
+      </c>
+      <c r="F18" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-18</t>
+        </is>
+      </c>
+      <c r="G18" s="89" t="inlineStr">
+        <is>
+          <t>시설물검증시험 착수보고 및 안전교육</t>
+        </is>
+      </c>
+      <c r="H18" s="88" t="inlineStr">
+        <is>
+          <t>D+185</t>
+        </is>
+      </c>
+      <c r="I18" s="88" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J18" s="90" t="inlineStr">
+        <is>
+          <t>2단계 시설물검증시험 착수보고회(TS) 및 시험참여자 전원 특별안전교육</t>
+        </is>
+      </c>
+      <c r="K18" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 착수보고회(TS) 개최 (시설물검증시험 28개 검증 항목(궤도/전기/신호/통신/승강장) 및 30일간의 시험 스케줄을 브리핑합니다.)
+2) STEP 2: 시험 참여 기관사 및 기술요원 특별 안전교육 (선로 내 작업자 통제, 제한속도 엄수, 무선통신 규격, 비상 제동 체결 절차를 집중 교육합니다.)
+3) STEP 3: 시설물검증시험 종합상황실 운영 개시 (차량기지 종합관제실 내에 시운전 종합상황실을 설치하고 실시간 모니터링을 개시합니다.)</t>
+        </is>
+      </c>
+      <c r="L18" s="90" t="inlineStr">
+        <is>
+          <t>시설물검증시험 착수보고 및 안전교육 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M18" s="90" t="inlineStr">
+        <is>
+          <t>1) 시설물검증시험 착수보고 및 안전교육 (9000-9-17) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 2단계 시설물검증시험 착수보고회(TS) 및 시험참여자 전원 특별안전교육을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N18" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\17_시설물검증시험 착수보고 및 시험참여자 안전교육\표준서\17_시설물검증시험 착수보고 및 시험참여자 안전교육_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O18" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 착수보고회(TS) 개최
+2) STEP 2: 시험 참여 기관사 및 기술요원 특별 안전교육</t>
+        </is>
+      </c>
+      <c r="P18" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\17_시설물검증시험 착수보고 및 시험참여자 안전교육\수행지침\17_시설물검증시험 착수보고 및 시험참여자 안전교육_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q18" s="90" t="inlineStr">
+        <is>
+          <t>1) 시설물검증 착수보고회 시방 및 시험 항목, 일정, 조직 보고 기준을 100% 충족하였는가?
+2) 시험 참여자 안전교육 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R18" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\17_시설물검증시험 착수보고 및 시험참여자 안전교육\체크리스트\17_시설물검증시험 착수보고 및 시험참여자 안전교육_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S18" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T18" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U18" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V18" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B19" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C19" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D19" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-18</t>
+        </is>
+      </c>
+      <c r="E19" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-17</t>
+        </is>
+      </c>
+      <c r="F19" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-19</t>
+        </is>
+      </c>
+      <c r="G19" s="96" t="inlineStr">
+        <is>
+          <t>시험열차 투입 및 속도별 연동시험</t>
+        </is>
+      </c>
+      <c r="H19" s="95" t="inlineStr">
+        <is>
+          <t>D+190</t>
+        </is>
+      </c>
+      <c r="I19" s="95" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J19" s="97" t="inlineStr">
+        <is>
+          <t>본선 34.4km 시험열차 투입, 속도별(10~70km/h) 28개 항목 시설물 연동 성능 검증</t>
+        </is>
+      </c>
+      <c r="K19" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 속도 단계별 주행시험 계획 및 열차 편성 (10km/h 저속 주행부터 시작하여 30km/h, 50km/h, 설계 최고속도 70km/h까지 단계적으로 증속 주행합니다.)
+2) STEP 2: 28개 핵심 검증 항목 실시간 계측 데이터 취득 (궤도검측(동적 윤중/횡압), 전기(급속충전 아크/전압강하), 신호(ATP 차상 차단), 승차감(가속도계측) 데이터를 수집합니다.)
+3) STEP 3: 비상제동 거리 및 정위치 정차 정밀도 검증 (최고속도 주행 중 비상제동 체결 시 법정 안전거리(160m 이내) 및 정거장 정위치 정차(±300mm)를 100% 입증합니다.)</t>
+        </is>
+      </c>
+      <c r="L19" s="97" t="inlineStr">
+        <is>
+          <t>시험열차 투입 및 속도별 연동시험 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M19" s="97" t="inlineStr">
+        <is>
+          <t>1) 시험열차 투입 및 속도별 연동시험 (9000-9-18) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 본선 34.4km 시험열차 투입, 속도별(10~70km/h) 28개 항목 시설물 연동 성능 검증을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N19" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\18_시험열차 투입계획 및 본선 속도별 연동 주행시험\표준서\18_시험열차 투입계획 및 본선 속도별 연동 주행시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O19" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 속도 단계별 주행시험 계획 및 열차 편성
+2) STEP 2: 28개 핵심 검증 항목 실시간 계측 데이터 취득</t>
+        </is>
+      </c>
+      <c r="P19" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\18_시험열차 투입계획 및 본선 속도별 연동 주행시험\수행지침\18_시험열차 투입계획 및 본선 속도별 연동 주행시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="97" t="inlineStr">
+        <is>
+          <t>1) 저속 주행시험(10~30km/h) 시방 및 건축한계, 레일 조인트 통과 기준을 100% 충족하였는가?
+2) 중속 주행시험(30~50km/h) 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R19" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\18_시험열차 투입계획 및 본선 속도별 연동 주행시험\체크리스트\18_시험열차 투입계획 및 본선 속도별 연동 주행시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S19" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T19" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U19" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V19" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B20" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C20" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D20" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-19</t>
+        </is>
+      </c>
+      <c r="E20" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-18</t>
+        </is>
+      </c>
+      <c r="F20" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-20</t>
+        </is>
+      </c>
+      <c r="G20" s="89" t="inlineStr">
+        <is>
+          <t>시설물검증시험 중간점검 및 장애조치</t>
+        </is>
+      </c>
+      <c r="H20" s="88" t="inlineStr">
+        <is>
+          <t>D+195</t>
+        </is>
+      </c>
+      <c r="I20" s="88" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J20" s="90" t="inlineStr">
+        <is>
+          <t>시설물검증시험 50% 시점 중간점검, 주행 중 발생 결함 및 데이터 오차 완벽 조치</t>
+        </is>
+      </c>
+      <c r="K20" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 전반부 계측 데이터 종합 평가 (10~50km/h 주행 중 획득된 수십만 건의 계측 센서 데이터를 분석하여 허용 기준치 초과 여부를 검토합니다.)
+2) STEP 2: 도출된 미비점 및 장애 원인 공학적 분석 (곡선부 미세 레일 연마, LTE-R 기지국 지향각 조정, 차상 컴퓨터 소프트웨어 파라미터 튜닝을 실행합니다.)
+3) STEP 3: 보완 항목 재시험 실시 및 중간보고서 승인 (튜닝된 시스템에 대해 70km/h 재주행 시험을 실시하여 완전 무결함을 재확인하고 중간보고서를 작성합니다.)</t>
+        </is>
+      </c>
+      <c r="L20" s="90" t="inlineStr">
+        <is>
+          <t>시설물검증시험 중간점검 및 장애조치 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M20" s="90" t="inlineStr">
+        <is>
+          <t>1) 시설물검증시험 중간점검 및 장애조치 (9000-9-19) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 시설물검증시험 50% 시점 중간점검, 주행 중 발생 결함 및 데이터 오차 완벽 조치을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N20" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\19_시설물검증시험 중간점검 및 장애조치 회의\표준서\19_시설물검증시험 중간점검 및 장애조치 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O20" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 전반부 계측 데이터 종합 평가
+2) STEP 2: 도출된 미비점 및 장애 원인 공학적 분석</t>
+        </is>
+      </c>
+      <c r="P20" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\19_시설물검증시험 중간점검 및 장애조치 회의\수행지침\19_시설물검증시험 중간점검 및 장애조치 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="90" t="inlineStr">
+        <is>
+          <t>1) 중간 계측 데이터 종합 분석 시방 및 속도별 28개 항목 데이터 검증 기준을 100% 충족하였는가?
+2) 결함 및 이상 징후 분석 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R20" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\19_시설물검증시험 중간점검 및 장애조치 회의\체크리스트\19_시설물검증시험 중간점검 및 장애조치 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S20" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T20" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U20" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V20" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B21" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C21" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D21" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-20</t>
+        </is>
+      </c>
+      <c r="E21" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-19</t>
+        </is>
+      </c>
+      <c r="F21" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-21</t>
+        </is>
+      </c>
+      <c r="G21" s="96" t="inlineStr">
+        <is>
+          <t>시설물검증시험 종결회의 및 결과 승인</t>
+        </is>
+      </c>
+      <c r="H21" s="95" t="inlineStr">
+        <is>
+          <t>D+205</t>
+        </is>
+      </c>
+      <c r="I21" s="95" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J21" s="97" t="inlineStr">
+        <is>
+          <t>시설물검증시험 종결보고회(TS), 28개 항목 전수 합격 판정 및 결과보고서 승인 획득</t>
+        </is>
+      </c>
+      <c r="K21" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 28개 항목 최종 성적서 집대성 (궤도, 전력, 신호, 통신, 차량, 승강장 인터페이스 전 항목의 공인 시험성적서를 종합 편철합니다.)
+2) STEP 2: TS 주관 시설물검증시험 종결 심의 회의 대응 (TS 심사위원단에 종합 결과를 발표하고 질의응답을 거쳐 '전 항목 적합 판정'을 도출합니다.)
+3) STEP 3: 시설물검증시험 결과보고서 정식 획득 및 다음 단계 진입 (TS 및 국토부로부터 공인 결과보고서 및 영업시운전 착수 승인 공문을 수령합니다.)</t>
+        </is>
+      </c>
+      <c r="L21" s="97" t="inlineStr">
+        <is>
+          <t>시설물검증시험 종결회의 및 결과 승인 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M21" s="97" t="inlineStr">
+        <is>
+          <t>1) 시설물검증시험 종결회의 및 결과 승인 (9000-9-20) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 시설물검증시험 종결보고회(TS), 28개 항목 전수 합격 판정 및 결과보고서 승인 획득을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N21" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\20_시설물검증시험 종결회의 및 결과보고서 획득\표준서\20_시설물검증시험 종결회의 및 결과보고서 획득_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O21" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 28개 항목 최종 성적서 집대성
+2) STEP 2: TS 주관 시설물검증시험 종결 심의 회의 대응</t>
+        </is>
+      </c>
+      <c r="P21" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\20_시설물검증시험 종결회의 및 결과보고서 획득\수행지침\20_시설물검증시험 종결회의 및 결과보고서 획득_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="97" t="inlineStr">
+        <is>
+          <t>1) 시설물검증시험 종결회의 시방 및 TS 주관 최종 결과 심의 기준을 100% 충족하였는가?
+2) 공인 결과보고서 편찬 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R21" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\20_시설물검증시험 종결회의 및 결과보고서 획득\체크리스트\20_시설물검증시험 종결회의 및 결과보고서 획득_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S21" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T21" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U21" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V21" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B22" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C22" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D22" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-21</t>
+        </is>
+      </c>
+      <c r="E22" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-20</t>
+        </is>
+      </c>
+      <c r="F22" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-22</t>
+        </is>
+      </c>
+      <c r="G22" s="89" t="inlineStr">
+        <is>
+          <t>영업시운전 계획 수립 및 착수보고</t>
+        </is>
+      </c>
+      <c r="H22" s="88" t="inlineStr">
+        <is>
+          <t>D+210</t>
+        </is>
+      </c>
+      <c r="I22" s="88" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J22" s="90" t="inlineStr">
+        <is>
+          <t>3단계 영업시운전 계획서 수립, TS 착수보고회 개최 및 실제 영업 다이아 운행 체계 개시</t>
+        </is>
+      </c>
+      <c r="K22" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 실제 영업 다이아(시각표) 및 배차간격 편성 (출퇴근 첨두시간(RH 4분) 및 평시(NH 8분) 배차간격에 맞춘 일일 120회 이상 영업 운행 다이아를 수립합니다.)
+2) STEP 2: 운영사(화성도시공사) 종사자 실전 투입 및 숙달 계획 (트램 기관사, 관제사, 역무원, 유지보수 요원이 실제 개통과 동일한 근무 교대조로 전면 투입됩니다.)
+3) STEP 3: 영업시운전 착수보고회(TS) 개최 및 시험 개시 (TS 및 관할 지자체 관계자가 참석한 착수보고회를 열고 30일간의 영업시운전을 본격 개시합니다.)</t>
+        </is>
+      </c>
+      <c r="L22" s="90" t="inlineStr">
+        <is>
+          <t>영업시운전 계획 수립 및 착수보고 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M22" s="90" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 계획 수립 및 착수보고 (9000-9-21) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 3단계 영업시운전 계획서 수립, TS 착수보고회 개최 및 실제 영업 다이아 운행 체계 개시을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N22" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\21_영업시운전 계획 수립 및 착수보고(TS)\표준서\21_영업시운전 계획 수립 및 착수보고(TS)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O22" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 실제 영업 다이아(시각표) 및 배차간격 편성
+2) STEP 2: 운영사(화성도시공사) 종사자 실전 투입 및 숙달 계획</t>
+        </is>
+      </c>
+      <c r="P22" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\21_영업시운전 계획 수립 및 착수보고(TS)\수행지침\21_영업시운전 계획 수립 및 착수보고(TS)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="90" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 종합계획서 편찬 시방 및 열차다이아, 인력배치, 비상훈련 기준을 100% 충족하였는가?
+2) 영업시운전 착수보고회 개최 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R22" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\21_영업시운전 계획 수립 및 착수보고(TS)\체크리스트\21_영업시운전 계획 수립 및 착수보고(TS)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S22" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T22" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U22" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V22" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B23" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C23" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D23" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-22</t>
+        </is>
+      </c>
+      <c r="E23" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-21</t>
+        </is>
+      </c>
+      <c r="F23" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-23</t>
+        </is>
+      </c>
+      <c r="G23" s="96" t="inlineStr">
+        <is>
+          <t>영업 다이아 운행 및 비상대응훈련</t>
+        </is>
+      </c>
+      <c r="H23" s="95" t="inlineStr">
+        <is>
+          <t>D+215</t>
+        </is>
+      </c>
+      <c r="I23" s="95" t="inlineStr">
+        <is>
+          <t>화성도시공사</t>
+        </is>
+      </c>
+      <c r="J23" s="97" t="inlineStr">
+        <is>
+          <t>30일간 무사고 영업 다이아 주행(정시율 ≥ 99%), 화재·탈선·단전 8대 비상대응훈련</t>
+        </is>
+      </c>
+      <c r="K23" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 30일간 실전 영업 다이아 연속 무사고 운행 (매일 아침 05:30 첫차부터 익일 00:30 막차까지 실제 운행 시각표에 따라 정속 주행 및 승강장 정차를 수행합니다.)
+2) STEP 2: 열차 운행 정시율(≥ 99%) 및 고장률(Zero) 관리 (출발, 통과, 도착 시각을 1초 단위로 기록하여 정시율 99.0% 이상을 유지하고 장애 발생 시 즉시 원인을 제거합니다.)
+3) STEP 3: 소방·경찰·지자체 합동 8대 비상대응 실전 훈련 (트램 화재 발생 시 승객 비상탈출, 터널 제연팬 가동, 도로 교통사고 연쇄 충돌 등 실전 모의훈련을 완수합니다.)</t>
+        </is>
+      </c>
+      <c r="L23" s="97" t="inlineStr">
+        <is>
+          <t>영업 다이아 운행 및 비상대응훈련 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M23" s="97" t="inlineStr">
+        <is>
+          <t>1) 영업 다이아 운행 및 비상대응훈련 (9000-9-22) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 30일간 무사고 영업 다이아 주행(정시율 ≥ 99%), 화재·탈선·단전 8대 비상대응훈련을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N23" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련\표준서\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O23" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 30일간 실전 영업 다이아 연속 무사고 운행
+2) STEP 2: 열차 운행 정시율(≥ 99%) 및 고장률(Zero) 관리</t>
+        </is>
+      </c>
+      <c r="P23" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련\수행지침\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="97" t="inlineStr">
+        <is>
+          <t>1) 영업 다이아 연속 운행 시방 및 1일 120회, 30일간 3,600회 주행 기준을 100% 충족하였는가?
+2) 열차 정시율 및 지연 분석 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R23" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련\체크리스트\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S23" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T23" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U23" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V23" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B24" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C24" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D24" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-23</t>
+        </is>
+      </c>
+      <c r="E24" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-22</t>
+        </is>
+      </c>
+      <c r="F24" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-24</t>
+        </is>
+      </c>
+      <c r="G24" s="89" t="inlineStr">
+        <is>
+          <t>영업시운전 중간점검 및 조치</t>
+        </is>
+      </c>
+      <c r="H24" s="88" t="inlineStr">
+        <is>
+          <t>D+220</t>
+        </is>
+      </c>
+      <c r="I24" s="88" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J24" s="90" t="inlineStr">
+        <is>
+          <t>영업시운전 15일 차 중간점검 회의, 운행 중 발생 이례상황 및 설비 오작동 100% 조치</t>
+        </is>
+      </c>
+      <c r="K24" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 15일간 누적 영업시운전 데이터 종합 분석 (총 1,800회 주행 데이터, 전력 소비 패턴, 정차 시간 준수율, 차내 소음도를 전수 분석합니다.)
+2) STEP 2: 운전 취급 및 승강장 설비 미세 이상 징후 조치 (승하차 도어 센서 민감도 조정, 안내방송 음압 레벨 보정, 교차로 신호 연동 지연시간을 0.1초 단위로 최적화합니다.)
+3) STEP 3: 영업시운전 중간점검 보고서 편찬 및 승인 (조치 결과를 포함한 중간보고서를 TS에 제출하여 후반부 영업시운전의 연속성을 확보합니다.)</t>
+        </is>
+      </c>
+      <c r="L24" s="90" t="inlineStr">
+        <is>
+          <t>영업시운전 중간점검 및 조치 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M24" s="90" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 중간점검 및 조치 (9000-9-23) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 영업시운전 15일 차 중간점검 회의, 운행 중 발생 이례상황 및 설비 오작동 100% 조치을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N24" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\23_영업시운전 중간점검 및 이례상황 조치결과 검토\표준서\23_영업시운전 중간점검 및 이례상황 조치결과 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O24" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 15일간 누적 영업시운전 데이터 종합 분석
+2) STEP 2: 운전 취급 및 승강장 설비 미세 이상 징후 조치</t>
+        </is>
+      </c>
+      <c r="P24" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\23_영업시운전 중간점검 및 이례상황 조치결과 검토\수행지침\23_영업시운전 중간점검 및 이례상황 조치결과 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="90" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 15일 누적 데이터 분석 시방 및 운행 횟수, 정시율, 전력소비량 기준을 100% 충족하였는가?
+2) 이례상황 및 미세 오류 분석 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R24" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\23_영업시운전 중간점검 및 이례상황 조치결과 검토\체크리스트\23_영업시운전 중간점검 및 이례상황 조치결과 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S24" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T24" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U24" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V24" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B25" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C25" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D25" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-24</t>
+        </is>
+      </c>
+      <c r="E25" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-23</t>
+        </is>
+      </c>
+      <c r="F25" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-25</t>
+        </is>
+      </c>
+      <c r="G25" s="96" t="inlineStr">
+        <is>
+          <t>영업시운전 종결회의 및 결과보고서 승인</t>
+        </is>
+      </c>
+      <c r="H25" s="95" t="inlineStr">
+        <is>
+          <t>D+225</t>
+        </is>
+      </c>
+      <c r="I25" s="95" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J25" s="97" t="inlineStr">
+        <is>
+          <t>영업시운전 최종 종결보고회(TS), 3단계 종합시험운행 전 과정 완벽 합격 판정</t>
+        </is>
+      </c>
+      <c r="K25" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 영업시운전 30일간 전 운행 실적 종합 집계 (총 주행거리, 정시 운행률, 비상훈련 성과, 종사자 직무 평가표를 집대성한 결과보고서를 편찬합니다.)
+2) STEP 2: TS 합동 영업시운전 종결 심의 회의 대응 (TS 및 전문가 심사위원단의 최종 심의를 거쳐 '동탄트램 영업시운전 무결점 합격'을 공식 의결합니다.)
+3) STEP 3: 영업시운전 결과보고서 승인 및 종결 선언 (국토부 및 TS로부터 공인 영업시운전 결과보고서를 수령하고 3단계 종합시험운행의 공식 종결을 선포합니다.)</t>
+        </is>
+      </c>
+      <c r="L25" s="97" t="inlineStr">
+        <is>
+          <t>영업시운전 종결회의 및 결과보고서 승인 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M25" s="97" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 종결회의 및 결과보고서 승인 (9000-9-24) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 영업시운전 최종 종결보고회(TS), 3단계 종합시험운행 전 과정 완벽 합격 판정을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N25" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\24_영업시운전 종결회의 및 결과보고서 승인\표준서\24_영업시운전 종결회의 및 결과보고서 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O25" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 영업시운전 30일간 전 운행 실적 종합 집계
+2) STEP 2: TS 합동 영업시운전 종결 심의 회의 대응</t>
+        </is>
+      </c>
+      <c r="P25" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\24_영업시운전 종결회의 및 결과보고서 승인\수행지침\24_영업시운전 종결회의 및 결과보고서 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q25" s="97" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 종결회의 개최 시방 및 TS 주관 종합 평가 보고 기준을 100% 충족하였는가?
+2) 영업시운전 결과보고서 편찬 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R25" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\24_영업시운전 종결회의 및 결과보고서 승인\체크리스트\24_영업시운전 종결회의 및 결과보고서 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S25" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T25" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U25" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V25" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B26" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C26" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D26" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-25</t>
+        </is>
+      </c>
+      <c r="E26" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-24</t>
+        </is>
+      </c>
+      <c r="F26" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-26</t>
+        </is>
+      </c>
+      <c r="G26" s="89" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 종합결과보고서 제출</t>
+        </is>
+      </c>
+      <c r="H26" s="88" t="inlineStr">
+        <is>
+          <t>D+230</t>
+        </is>
+      </c>
+      <c r="I26" s="88" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J26" s="90" t="inlineStr">
+        <is>
+          <t>사전점검·시설물검증·영업시운전 3단계 총괄 종합결과보고서 국토교통부 제출</t>
+        </is>
+      </c>
+      <c r="K26" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검·시설물검증·영업시운전 성과 종합 편철 (3단계 전 시험 과정의 측정 데이터, 사진대지, 필증, TS 합격증명서를 마스터 종합보고서로 바인딩합니다.)
+2) STEP 2: 총괄사업단장 및 책임감리원 최종 서명 날인 (발주처, 감리단, 시공사 3자 대표자가 서명 날인하여 기술적 무결성을 최종 보증합니다.)
+3) STEP 3: 국토교통부 정식 제출 및 정부 적합 승인 통보 수령 (국토교통부에 정식 공문으로 접수하고 최종 '철도종합시험운행 적합 승인' 공문을 수령합니다.)</t>
+        </is>
+      </c>
+      <c r="L26" s="90" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 종합결과보고서 제출 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M26" s="90" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 종합결과보고서 제출 (9000-9-25) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 사전점검·시설물검증·영업시운전 3단계 총괄 종합결과보고서 국토교통부 제출을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N26" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\25_철도종합시험운행 종합결과보고서 작성 및 제출\표준서\25_철도종합시험운행 종합결과보고서 작성 및 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O26" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검·시설물검증·영업시운전 성과 종합 편철
+2) STEP 2: 총괄사업단장 및 책임감리원 최종 서명 날인</t>
+        </is>
+      </c>
+      <c r="P26" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\25_철도종합시험운행 종합결과보고서 작성 및 제출\수행지침\25_철도종합시험운행 종합결과보고서 작성 및 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="90" t="inlineStr">
+        <is>
+          <t>1) 3단계 종합결과보고서 편찬 시방 및 사전점검+시설물검증+영업시운전 기준을 100% 충족하였는가?
+2) 사업단장 및 책임감리원 서명 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R26" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\25_철도종합시험운행 종합결과보고서 작성 및 제출\체크리스트\25_철도종합시험운행 종합결과보고서 작성 및 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S26" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T26" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U26" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V26" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B27" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C27" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D27" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-26</t>
+        </is>
+      </c>
+      <c r="E27" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-25</t>
+        </is>
+      </c>
+      <c r="F27" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-27</t>
+        </is>
+      </c>
+      <c r="G27" s="96" t="inlineStr">
+        <is>
+          <t>철도운영자 안전관리체계 변경승인</t>
+        </is>
+      </c>
+      <c r="H27" s="95" t="inlineStr">
+        <is>
+          <t>D+235</t>
+        </is>
+      </c>
+      <c r="I27" s="95" t="inlineStr">
+        <is>
+          <t>화성도시공사</t>
+        </is>
+      </c>
+      <c r="J27" s="97" t="inlineStr">
+        <is>
+          <t>화성도시공사(철도운영자) 철도안전관리체계 변경승인 신청 및 TS 현장 검사 합격</t>
+        </is>
+      </c>
+      <c r="K27" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도안전관리체계 변경승인 신청 서류 작성 (안전경영 목표, 철도비상대응계획, 철도종사자 자격관리, 시설 및 차량 유지관리 규정 42종을 편찬합니다.)
+2) STEP 2: 한국교통안전공단(TS) 현장 실사 수검 (TS 심사위원단의 현장 실사 시 화성도시공사의 관제, 운전, 유지보수 조직의 실질적 이행 능력을 입증합니다.)
+3) STEP 3: 국토교통부 철도안전관리체계 변경승인증명서 획득 (국토교통부 장관 명의의 정식 승인증명서를 획득하여 영업 개통을 위한 법적 자격을 100% 완비합니다.)</t>
+        </is>
+      </c>
+      <c r="L27" s="97" t="inlineStr">
+        <is>
+          <t>철도운영자 안전관리체계 변경승인 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M27" s="97" t="inlineStr">
+        <is>
+          <t>1) 철도운영자 안전관리체계 변경승인 (9000-9-26) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 화성도시공사(철도운영자) 철도안전관리체계 변경승인 신청 및 TS 현장 검사 합격을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N27" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\26_철도운영자 안전관리체계 변경승인(TS)\표준서\26_철도운영자 안전관리체계 변경승인(TS)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O27" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도안전관리체계 변경승인 신청 서류 작성
+2) STEP 2: 한국교통안전공단(TS) 현장 실사 수검</t>
+        </is>
+      </c>
+      <c r="P27" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\26_철도운영자 안전관리체계 변경승인(TS)\수행지침\26_철도운영자 안전관리체계 변경승인(TS)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q27" s="97" t="inlineStr">
+        <is>
+          <t>1) 안전관리체계 변경승인 신청서 제출 시방 및 국토교통부 및 TS 기준을 100% 충족하였는가?
+2) TS 안전관리체계 현장 실사 대응 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R27" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\26_철도운영자 안전관리체계 변경승인(TS)\체크리스트\26_철도운영자 안전관리체계 변경승인(TS)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S27" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T27" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U27" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V27" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="87" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B28" s="87" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C28" s="87" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D28" s="87" t="inlineStr">
+        <is>
+          <t>9000-9-27</t>
+        </is>
+      </c>
+      <c r="E28" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-26</t>
+        </is>
+      </c>
+      <c r="F28" s="88" t="inlineStr">
+        <is>
+          <t>9000-9-28</t>
+        </is>
+      </c>
+      <c r="G28" s="89" t="inlineStr">
+        <is>
+          <t>공사목적물 및 시설물 최종 인수인계</t>
+        </is>
+      </c>
+      <c r="H28" s="88" t="inlineStr">
+        <is>
+          <t>D+238</t>
+        </is>
+      </c>
+      <c r="I28" s="88" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J28" s="90" t="inlineStr">
+        <is>
+          <t>36개 정거장, 본선, 차량기지 시설물 및 2D/3D 준공도서·예비품 화성도시공사 합동 인수인계</t>
+        </is>
+      </c>
+      <c r="K28" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전 역사 및 시설물 합동 정밀 인수인계 실사 (건축 마감, 기계 배관, 전기 수전반, 신호 기계실, 궤도 레일의 상태를 합동 점검하고 인수인계 목록을 작성합니다.)
+2) STEP 2: 준공도서, 운용 매뉴얼 및 유지보수 예비품 인계 (3D BIM 기반 As-Built 최종 준공도면, 장비별 정비 지침서 및 2년분 유지보수 예비품을 운영사에 공식 전달합니다.)
+3) STEP 3: 공사목적물 인수인계서 최종 체결 (화성시, 화성도시공사, 시공사업단 3자 대표자가 서명 날인하여 시설물 관리권을 공식 이관합니다.)</t>
+        </is>
+      </c>
+      <c r="L28" s="90" t="inlineStr">
+        <is>
+          <t>공사목적물 및 시설물 최종 인수인계 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M28" s="90" t="inlineStr">
+        <is>
+          <t>1) 공사목적물 및 시설물 최종 인수인계 (9000-9-27) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 36개 정거장, 본선, 차량기지 시설물 및 2D/3D 준공도서·예비품 화성도시공사 합동 인수인계을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N28" s="91">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\27_공사목적물 및 시설물 운영사 최종 인수인계\표준서\27_공사목적물 및 시설물 운영사 최종 인수인계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O28" s="90" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전 역사 및 시설물 합동 정밀 인수인계 실사
+2) STEP 2: 준공도서, 운용 매뉴얼 및 유지보수 예비품 인계</t>
+        </is>
+      </c>
+      <c r="P28" s="92">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\27_공사목적물 및 시설물 운영사 최종 인수인계\수행지침\27_공사목적물 및 시설물 운영사 최종 인수인계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="90" t="inlineStr">
+        <is>
+          <t>1) 시설물 합동 실사 및 검측 시방 및 전 역사/차량기지/변전소 실사 기준을 100% 충족하였는가?
+2) 준공도서 및 매뉴얼 인계 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R28" s="93">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\27_공사목적물 및 시설물 운영사 최종 인수인계\체크리스트\27_공사목적물 및 시설물 운영사 최종 인수인계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S28" s="88" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T28" s="90" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U28" s="87" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V28" s="90" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="94" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B29" s="94" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C29" s="94" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D29" s="94" t="inlineStr">
+        <is>
+          <t>9000-9-28</t>
+        </is>
+      </c>
+      <c r="E29" s="95" t="inlineStr">
+        <is>
+          <t>9000-9-27</t>
+        </is>
+      </c>
+      <c r="F29" s="95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="96" t="inlineStr">
+        <is>
+          <t>종합시험운행 종결 및 영업 개통</t>
+        </is>
+      </c>
+      <c r="H29" s="95" t="inlineStr">
+        <is>
+          <t>D+240</t>
+        </is>
+      </c>
+      <c r="I29" s="95" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J29" s="97" t="inlineStr">
+        <is>
+          <t>국토교통부 영업개통 승인 획득, 동탄트램 공식 개통식 거행 및 대시민 상업운전 개시</t>
+        </is>
+      </c>
+      <c r="K29" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 국토교통부 영업개통 최종 승인 공문 접수 (철도종합시험운행 및 안전관리체계 승인 성과를 바탕으로 국토교통부 장관의 정식 '영업개통 승인'을 수령합니다.)
+2) STEP 2: 동탄도시철도 개통 기념식 및 테이프 커팅 (화성시장, 국회의원, 시민대표, 사업단 관계자가 참석한 가운데 개통식을 개최하고 1호 열차 시승을 진행합니다.)
+3) STEP 3: 동탄트램 1·2호선 전 구간 대시민 상업운전 개시 (34.4km 36개 정거장 전 노선에서 시민 탑승 상업운전을 시작하여 동탄 트램 프로젝트를 성공적으로 완수합니다.)</t>
+        </is>
+      </c>
+      <c r="L29" s="97" t="inlineStr">
+        <is>
+          <t>종합시험운행 종결 및 영업 개통 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M29" s="97" t="inlineStr">
+        <is>
+          <t>1) 종합시험운행 종결 및 영업 개통 (9000-9-28) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 국토교통부 영업개통 승인 획득, 동탄트램 공식 개통식 거행 및 대시민 상업운전 개시을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N29" s="98">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통\표준서\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O29" s="97" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 국토교통부 영업개통 최종 승인 공문 접수
+2) STEP 2: 동탄도시철도 개통 기념식 및 테이프 커팅</t>
+        </is>
+      </c>
+      <c r="P29" s="99">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통\수행지침\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q29" s="97" t="inlineStr">
+        <is>
+          <t>1) 국토교통부 영업개통 승인 신청 시방 및 종합결과보고서 및 안전관리체계 기준을 100% 충족하였는가?
+2) 국토교통부 영업개통 정식 승인 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R29" s="100">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"11.철도종합시운전\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통\체크리스트\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S29" s="95" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T29" s="97" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U29" s="94" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V29" s="97" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
